--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BCBC1-3E4C-4F41-B84C-32F4E357BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAED1C6E-12AD-4A04-A773-BFAB253A1EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listado_ons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$125</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="221">
   <si>
     <t>name</t>
   </si>
@@ -68,9 +68,6 @@
     <t>rate</t>
   </si>
   <si>
-    <t>BF35D</t>
-  </si>
-  <si>
     <t>BBVA</t>
   </si>
   <si>
@@ -80,240 +77,60 @@
     <t>ARG</t>
   </si>
   <si>
-    <t>ZZC1D</t>
-  </si>
-  <si>
     <t>Camuzzi Gas Pampeana</t>
   </si>
   <si>
-    <t>NPCAD</t>
-  </si>
-  <si>
     <t>CEPU</t>
   </si>
   <si>
     <t>CCL</t>
   </si>
   <si>
-    <t>CS38D</t>
-  </si>
-  <si>
     <t>CRESUD</t>
   </si>
   <si>
-    <t>CS44D</t>
-  </si>
-  <si>
-    <t>CS47D</t>
-  </si>
-  <si>
-    <t>DNC8D</t>
-  </si>
-  <si>
     <t>EDENOR</t>
   </si>
   <si>
-    <t>DNC3D</t>
-  </si>
-  <si>
-    <t>DNC5D</t>
-  </si>
-  <si>
-    <t>DNC7D</t>
-  </si>
-  <si>
-    <t>GNCXD</t>
-  </si>
-  <si>
     <t>GENNEIA</t>
   </si>
   <si>
-    <t>GN48D</t>
-  </si>
-  <si>
-    <t>GN47D</t>
-  </si>
-  <si>
-    <t>IRCID</t>
-  </si>
-  <si>
     <t>IRSA</t>
   </si>
   <si>
-    <t>IRCLD</t>
-  </si>
-  <si>
-    <t>IRCJD</t>
-  </si>
-  <si>
-    <t>IRCFD</t>
-  </si>
-  <si>
-    <t>IRCND</t>
-  </si>
-  <si>
-    <t>IRCPD</t>
-  </si>
-  <si>
-    <t>IRCOD</t>
-  </si>
-  <si>
-    <t>LOC2D</t>
-  </si>
-  <si>
     <t>LOMA</t>
   </si>
   <si>
-    <t>LOC3D</t>
-  </si>
-  <si>
-    <t>LOC5D</t>
-  </si>
-  <si>
-    <t>PN38D</t>
-  </si>
-  <si>
     <t>PAE</t>
   </si>
   <si>
-    <t>PN35D</t>
-  </si>
-  <si>
-    <t>PN34D</t>
-  </si>
-  <si>
-    <t>PN36D</t>
-  </si>
-  <si>
-    <t>PN37D</t>
-  </si>
-  <si>
-    <t>PNDCD</t>
-  </si>
-  <si>
-    <t>PNXCD</t>
-  </si>
-  <si>
-    <t>MGCND</t>
-  </si>
-  <si>
     <t>PAMPA</t>
   </si>
   <si>
-    <t>MGCHD</t>
-  </si>
-  <si>
-    <t>MGCMD</t>
-  </si>
-  <si>
-    <t>MGCOD</t>
-  </si>
-  <si>
-    <t>TTC7D</t>
-  </si>
-  <si>
     <t>TECPETROL</t>
   </si>
   <si>
-    <t>TTC9D</t>
-  </si>
-  <si>
-    <t>TTC8D</t>
-  </si>
-  <si>
-    <t>TTCAD</t>
-  </si>
-  <si>
-    <t>TLC1D</t>
-  </si>
-  <si>
     <t>TELECOM</t>
   </si>
   <si>
-    <t>TLCQD</t>
-  </si>
-  <si>
-    <t>TLCOD</t>
-  </si>
-  <si>
-    <t>TLCMD</t>
-  </si>
-  <si>
-    <t>TSC3D</t>
-  </si>
-  <si>
     <t>TGS</t>
   </si>
   <si>
-    <t>VSCPD</t>
-  </si>
-  <si>
     <t>VISTA</t>
   </si>
   <si>
-    <t>VSCUD</t>
-  </si>
-  <si>
-    <t>VSCRD</t>
-  </si>
-  <si>
-    <t>VSCVD</t>
-  </si>
-  <si>
-    <t>VSCTD</t>
-  </si>
-  <si>
     <t>YPF</t>
   </si>
   <si>
-    <t>YMCQD</t>
-  </si>
-  <si>
-    <t>YMCVD</t>
-  </si>
-  <si>
-    <t>YM35D</t>
-  </si>
-  <si>
-    <t>YM37D</t>
-  </si>
-  <si>
-    <t>YM38D</t>
-  </si>
-  <si>
-    <t>YMCID</t>
-  </si>
-  <si>
-    <t>YMCYD</t>
-  </si>
-  <si>
-    <t>YM39D</t>
-  </si>
-  <si>
-    <t>YMCXD</t>
-  </si>
-  <si>
-    <t>YM34D</t>
-  </si>
-  <si>
-    <t>YMCJD</t>
-  </si>
-  <si>
     <t>17/01/2032;17/01/2033;17/01/2034</t>
   </si>
   <si>
     <t>33;33;34</t>
   </si>
   <si>
-    <t>MGC9D</t>
-  </si>
-  <si>
     <t>8/12/2024;8/12/2025;8/12/2026</t>
   </si>
   <si>
-    <t>BF37D</t>
-  </si>
-  <si>
     <t>24/10/2028;24/10/2029;24/10/2030</t>
   </si>
   <si>
@@ -392,30 +209,15 @@
     <t>AA+</t>
   </si>
   <si>
-    <t>LMS7D</t>
-  </si>
-  <si>
-    <t>LMS9D</t>
-  </si>
-  <si>
     <t>ALUAR</t>
   </si>
   <si>
     <t>12/10/2025;12/1/2026;12/4/2026;12/7/2026;12/10/2026;12/1/2027;12/4/2027;12/7/2027;12/10/2027;12/1/2028;12/4/2028;12/7/2028;12/10/2028</t>
   </si>
   <si>
-    <t>RC1CD</t>
-  </si>
-  <si>
-    <t>RCCRD</t>
-  </si>
-  <si>
     <t>ARCOR</t>
   </si>
   <si>
-    <t>RCCJD</t>
-  </si>
-  <si>
     <t>31/7/2031;31/7/2032;31/7/2033</t>
   </si>
   <si>
@@ -431,24 +233,12 @@
     <t>14,285;14,285;14,285;14,285;14,285;14,285;14,29</t>
   </si>
   <si>
-    <t>BYCHD</t>
-  </si>
-  <si>
-    <t>BYCTD</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>BYCVD</t>
-  </si>
-  <si>
     <t>MACRO</t>
   </si>
   <si>
-    <t>BPCPD</t>
-  </si>
-  <si>
     <t>SUPERVIELLE</t>
   </si>
   <si>
@@ -458,51 +248,9 @@
     <t>JOHN DEERE</t>
   </si>
   <si>
-    <t>HJCFD</t>
-  </si>
-  <si>
-    <t>HJCGD</t>
-  </si>
-  <si>
-    <t>HJCHD</t>
-  </si>
-  <si>
-    <t>HJCID</t>
-  </si>
-  <si>
-    <t>HJCJD</t>
-  </si>
-  <si>
     <t>MSU</t>
   </si>
   <si>
-    <t>MSSED</t>
-  </si>
-  <si>
-    <t>MSSFD</t>
-  </si>
-  <si>
-    <t>YFC2D</t>
-  </si>
-  <si>
-    <t>YFCGD</t>
-  </si>
-  <si>
-    <t>YFCID</t>
-  </si>
-  <si>
-    <t>YFCJD</t>
-  </si>
-  <si>
-    <t>YFCKD</t>
-  </si>
-  <si>
-    <t>YFCLD</t>
-  </si>
-  <si>
-    <t>YFCMD</t>
-  </si>
-  <si>
     <t>YPF LUZ</t>
   </si>
   <si>
@@ -515,18 +263,9 @@
     <t>16/10/2030;16/10/2031;16/10/2032</t>
   </si>
   <si>
-    <t>T641D</t>
-  </si>
-  <si>
     <t>TARJETA NARANJA</t>
   </si>
   <si>
-    <t>RUCAD</t>
-  </si>
-  <si>
-    <t>RUCDD</t>
-  </si>
-  <si>
     <t>MSU ENERGY</t>
   </si>
   <si>
@@ -536,48 +275,21 @@
     <t>5/12/2028;5/12/2029;5/12/2030</t>
   </si>
   <si>
-    <t>AERBD</t>
-  </si>
-  <si>
     <t>AEROPUERTOS ARGENTINA</t>
   </si>
   <si>
-    <t>HVS1D</t>
-  </si>
-  <si>
     <t>HAVANNA</t>
   </si>
   <si>
-    <t>GYC4D</t>
-  </si>
-  <si>
-    <t>GYC5D</t>
-  </si>
-  <si>
     <t>360 ENERGY</t>
   </si>
   <si>
-    <t>BACGD</t>
-  </si>
-  <si>
-    <t>LMS8D</t>
-  </si>
-  <si>
     <t>21/6/2026;21/9/2026;21/12/2026;21/3/2027</t>
   </si>
   <si>
-    <t>BYCRD</t>
-  </si>
-  <si>
-    <t>PLC4D</t>
-  </si>
-  <si>
     <t>PLUSPETROL</t>
   </si>
   <si>
-    <t>HBCAD</t>
-  </si>
-  <si>
     <t>HIPOTECARIO</t>
   </si>
   <si>
@@ -587,12 +299,6 @@
     <t>NY</t>
   </si>
   <si>
-    <t>CAC5D</t>
-  </si>
-  <si>
-    <t>CAC8D</t>
-  </si>
-  <si>
     <t>CAPEX</t>
   </si>
   <si>
@@ -602,94 +308,397 @@
     <t>12,5;12,5;12,5;12,5;12,5;12,5;12,5;12,5;12,5</t>
   </si>
   <si>
-    <t>TLCPD</t>
-  </si>
-  <si>
     <t>28/5/2032;28/5/2033</t>
   </si>
   <si>
-    <t>RC2CD</t>
-  </si>
-  <si>
-    <t>YM41D</t>
-  </si>
-  <si>
-    <t>BPCSD</t>
-  </si>
-  <si>
-    <t>PQCRD</t>
-  </si>
-  <si>
     <t>Petroquímica Comodoro Rivadavia</t>
   </si>
   <si>
-    <t>PQCTD</t>
-  </si>
-  <si>
-    <t>PQCSD</t>
-  </si>
-  <si>
-    <t>TTCBD</t>
-  </si>
-  <si>
-    <t>YMCZD</t>
-  </si>
-  <si>
-    <t>MGCQD</t>
-  </si>
-  <si>
-    <t>MGCRD</t>
-  </si>
-  <si>
-    <t>TTCDD</t>
-  </si>
-  <si>
-    <t>TSC4D</t>
-  </si>
-  <si>
-    <t>VSCWD</t>
-  </si>
-  <si>
-    <t>LMS6D</t>
-  </si>
-  <si>
     <t>DLK</t>
   </si>
   <si>
-    <t>BFCYD</t>
-  </si>
-  <si>
-    <t>NPCCD</t>
-  </si>
-  <si>
-    <t>CS48D</t>
-  </si>
-  <si>
-    <t>CS49D</t>
-  </si>
-  <si>
-    <t>CS45D</t>
-  </si>
-  <si>
     <t>2/12/2031;2/12/2032;2/12/2033</t>
   </si>
   <si>
-    <t>GN49D</t>
-  </si>
-  <si>
-    <t>YFCOD</t>
-  </si>
-  <si>
-    <t>YM42D</t>
-  </si>
-  <si>
-    <t>PN41D</t>
-  </si>
-  <si>
-    <t>PN42D</t>
-  </si>
-  <si>
-    <t>CS50D</t>
+    <t>20/01/2035;20/01/2036</t>
+  </si>
+  <si>
+    <t>Oleoductos del Valle</t>
+  </si>
+  <si>
+    <t>15/01/2035;15/01/2036;15/01/2037</t>
+  </si>
+  <si>
+    <t>GYC4O</t>
+  </si>
+  <si>
+    <t>GYC5O</t>
+  </si>
+  <si>
+    <t>AERBO</t>
+  </si>
+  <si>
+    <t>LMS6O</t>
+  </si>
+  <si>
+    <t>LMS7O</t>
+  </si>
+  <si>
+    <t>LMS8O</t>
+  </si>
+  <si>
+    <t>LMS9O</t>
+  </si>
+  <si>
+    <t>RC1CO</t>
+  </si>
+  <si>
+    <t>RC2CO</t>
+  </si>
+  <si>
+    <t>RCCJO</t>
+  </si>
+  <si>
+    <t>RCCRO</t>
+  </si>
+  <si>
+    <t>BF35O</t>
+  </si>
+  <si>
+    <t>BF37O</t>
+  </si>
+  <si>
+    <t>ZZC1O</t>
+  </si>
+  <si>
+    <t>CAC5O</t>
+  </si>
+  <si>
+    <t>CAC8O</t>
+  </si>
+  <si>
+    <t>NPCAO</t>
+  </si>
+  <si>
+    <t>NPCCO</t>
+  </si>
+  <si>
+    <t>CS38O</t>
+  </si>
+  <si>
+    <t>CS44O</t>
+  </si>
+  <si>
+    <t>CS45O</t>
+  </si>
+  <si>
+    <t>CS47O</t>
+  </si>
+  <si>
+    <t>CS48O</t>
+  </si>
+  <si>
+    <t>CS49O</t>
+  </si>
+  <si>
+    <t>CS50O</t>
+  </si>
+  <si>
+    <t>BYCHO</t>
+  </si>
+  <si>
+    <t>BYCVO</t>
+  </si>
+  <si>
+    <t>GN47O</t>
+  </si>
+  <si>
+    <t>GN48O</t>
+  </si>
+  <si>
+    <t>GN49O</t>
+  </si>
+  <si>
+    <t>GNCXO</t>
+  </si>
+  <si>
+    <t>HVS1O</t>
+  </si>
+  <si>
+    <t>HBCAO</t>
+  </si>
+  <si>
+    <t>IRCFO</t>
+  </si>
+  <si>
+    <t>IRCJO</t>
+  </si>
+  <si>
+    <t>IRCLO</t>
+  </si>
+  <si>
+    <t>IRCNO</t>
+  </si>
+  <si>
+    <t>IRCOO</t>
+  </si>
+  <si>
+    <t>IRCPO</t>
+  </si>
+  <si>
+    <t>HJCFO</t>
+  </si>
+  <si>
+    <t>HJCGO</t>
+  </si>
+  <si>
+    <t>HJCHO</t>
+  </si>
+  <si>
+    <t>HJCIO</t>
+  </si>
+  <si>
+    <t>HJCJO</t>
+  </si>
+  <si>
+    <t>LOC3O</t>
+  </si>
+  <si>
+    <t>LOC5O</t>
+  </si>
+  <si>
+    <t>BACGO</t>
+  </si>
+  <si>
+    <t>BACHO</t>
+  </si>
+  <si>
+    <t>MSSEO</t>
+  </si>
+  <si>
+    <t>MSSFO</t>
+  </si>
+  <si>
+    <t>RUCAO</t>
+  </si>
+  <si>
+    <t>RUCOO</t>
+  </si>
+  <si>
+    <t>OLC5O</t>
+  </si>
+  <si>
+    <t>OLC6O</t>
+  </si>
+  <si>
+    <t>PN34O</t>
+  </si>
+  <si>
+    <t>PN35O</t>
+  </si>
+  <si>
+    <t>PN36O</t>
+  </si>
+  <si>
+    <t>PN37O</t>
+  </si>
+  <si>
+    <t>PN38O</t>
+  </si>
+  <si>
+    <t>PN41O</t>
+  </si>
+  <si>
+    <t>PN42O</t>
+  </si>
+  <si>
+    <t>PN43O</t>
+  </si>
+  <si>
+    <t>PNOCO</t>
+  </si>
+  <si>
+    <t>PNXCO</t>
+  </si>
+  <si>
+    <t>MGC9O</t>
+  </si>
+  <si>
+    <t>MGCMO</t>
+  </si>
+  <si>
+    <t>MGCNO</t>
+  </si>
+  <si>
+    <t>MGCOO</t>
+  </si>
+  <si>
+    <t>MGCQO</t>
+  </si>
+  <si>
+    <t>MGCRO</t>
+  </si>
+  <si>
+    <t>PQCRO</t>
+  </si>
+  <si>
+    <t>PQCSO</t>
+  </si>
+  <si>
+    <t>PQCTO</t>
+  </si>
+  <si>
+    <t>PLC4O</t>
+  </si>
+  <si>
+    <t>BPCSO</t>
+  </si>
+  <si>
+    <t>T641O</t>
+  </si>
+  <si>
+    <t>TTC7O</t>
+  </si>
+  <si>
+    <t>TTC8O</t>
+  </si>
+  <si>
+    <t>TTC9O</t>
+  </si>
+  <si>
+    <t>TTCAO</t>
+  </si>
+  <si>
+    <t>TTCBO</t>
+  </si>
+  <si>
+    <t>TLC1O</t>
+  </si>
+  <si>
+    <t>TLCMO</t>
+  </si>
+  <si>
+    <t>TLCOO</t>
+  </si>
+  <si>
+    <t>TLCPO</t>
+  </si>
+  <si>
+    <t>TLCQO</t>
+  </si>
+  <si>
+    <t>TLCTO</t>
+  </si>
+  <si>
+    <t>TSC3O</t>
+  </si>
+  <si>
+    <t>TSC4O</t>
+  </si>
+  <si>
+    <t>VSCPO</t>
+  </si>
+  <si>
+    <t>VSCRO</t>
+  </si>
+  <si>
+    <t>VSCTO</t>
+  </si>
+  <si>
+    <t>VSCUO</t>
+  </si>
+  <si>
+    <t>VSCVO</t>
+  </si>
+  <si>
+    <t>VSCWO</t>
+  </si>
+  <si>
+    <t>YM34O</t>
+  </si>
+  <si>
+    <t>YM35O</t>
+  </si>
+  <si>
+    <t>YM37O</t>
+  </si>
+  <si>
+    <t>YM38O</t>
+  </si>
+  <si>
+    <t>YM39O</t>
+  </si>
+  <si>
+    <t>YM41O</t>
+  </si>
+  <si>
+    <t>YM42O</t>
+  </si>
+  <si>
+    <t>YMCIO</t>
+  </si>
+  <si>
+    <t>YMCJO</t>
+  </si>
+  <si>
+    <t>YMCQO</t>
+  </si>
+  <si>
+    <t>YMCVO</t>
+  </si>
+  <si>
+    <t>YMCXO</t>
+  </si>
+  <si>
+    <t>YMCYO</t>
+  </si>
+  <si>
+    <t>YMCZO</t>
+  </si>
+  <si>
+    <t>YFC2O</t>
+  </si>
+  <si>
+    <t>YFCGO</t>
+  </si>
+  <si>
+    <t>YFCIO</t>
+  </si>
+  <si>
+    <t>YFCJO</t>
+  </si>
+  <si>
+    <t>YFCKO</t>
+  </si>
+  <si>
+    <t>YFCLO</t>
+  </si>
+  <si>
+    <t>YFCMO</t>
+  </si>
+  <si>
+    <t>YFCOO</t>
+  </si>
+  <si>
+    <t>DNC3O</t>
+  </si>
+  <si>
+    <t>DNC5O</t>
+  </si>
+  <si>
+    <t>DNC7O</t>
+  </si>
+  <si>
+    <t>DNC8O</t>
+  </si>
+  <si>
+    <t>VSCXO</t>
+  </si>
+  <si>
+    <t>08/4/2036;08/4/2037;08/4/2038</t>
+  </si>
+  <si>
+    <t>MGCTO</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1176,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1182,6 +1191,7 @@
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1538,15 +1548,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
     <col min="2" max="2" width="26.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="11" style="1"/>
     <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="76.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="59.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="55.125" style="1" customWidth="1"/>
     <col min="10" max="11" width="11" style="1"/>
     <col min="12" max="12" width="12.375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="1"/>
@@ -1554,7 +1564,7 @@
     <col min="15" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1586,24 +1596,24 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3">
         <v>45595</v>
@@ -1627,21 +1637,21 @@
         <v>22</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3">
         <v>45721</v>
@@ -1665,21 +1675,22 @@
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3">
         <v>45639</v>
@@ -1703,21 +1714,21 @@
         <v>28</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>205</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3">
         <v>45043</v>
@@ -1741,21 +1752,21 @@
         <v>100</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3">
         <v>45211</v>
@@ -1767,10 +1778,10 @@
         <v>3</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="J6" s="2">
         <v>7.0000000000000007E-2</v>
@@ -1779,21 +1790,21 @@
         <v>137</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3">
         <v>45372</v>
@@ -1805,10 +1816,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="J7" s="2">
         <v>6.25E-2</v>
@@ -1817,21 +1828,21 @@
         <v>100</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3">
         <v>45456</v>
@@ -1855,21 +1866,21 @@
         <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3">
         <v>45869</v>
@@ -1881,10 +1892,10 @@
         <v>6</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="J9" s="2">
         <v>7.5999999999999998E-2</v>
@@ -1893,21 +1904,22 @@
         <v>350</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="3">
         <v>45936</v>
@@ -1931,21 +1943,21 @@
         <v>100</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3">
         <v>44874</v>
@@ -1957,10 +1969,10 @@
         <v>6</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="J11" s="2">
         <v>8.2500000000000004E-2</v>
@@ -1969,21 +1981,21 @@
         <v>151</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="3">
         <v>45786</v>
@@ -2007,21 +2019,21 @@
         <v>68</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
         <v>45811</v>
@@ -2045,97 +2057,98 @@
         <v>62</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>206</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>45891</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46256</v>
+      </c>
+      <c r="G14" s="2">
+        <v>6</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46256</v>
+      </c>
+      <c r="I14" s="2">
+        <v>100</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K14" s="2">
+        <v>43</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="3">
-        <v>45715</v>
-      </c>
-      <c r="F14" s="3">
-        <v>46080</v>
-      </c>
-      <c r="G14" s="2">
-        <v>6</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46080</v>
-      </c>
-      <c r="I14" s="2">
-        <v>100</v>
-      </c>
-      <c r="J14" s="2">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="K14" s="2">
-        <v>16</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="3">
-        <v>45891</v>
+        <v>45709</v>
       </c>
       <c r="F15" s="3">
-        <v>46256</v>
+        <v>46439</v>
       </c>
       <c r="G15" s="2">
         <v>6</v>
       </c>
       <c r="H15" s="3">
-        <v>46256</v>
+        <v>46439</v>
       </c>
       <c r="I15" s="2">
         <v>100</v>
       </c>
       <c r="J15" s="2">
-        <v>0.06</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K15" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3">
         <v>45163</v>
@@ -2147,10 +2160,10 @@
         <v>6</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="J16" s="2">
         <v>9.2499999999999999E-2</v>
@@ -2159,21 +2172,21 @@
         <v>141</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="3">
         <v>45411</v>
@@ -2197,109 +2210,109 @@
         <v>47</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3">
+        <v>45183</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46095</v>
+      </c>
+      <c r="I18" s="2">
+        <v>100</v>
+      </c>
+      <c r="J18" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>47</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="3">
+        <v>45894</v>
+      </c>
+      <c r="F19" s="3">
+        <v>47355</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
+      </c>
+      <c r="H19" s="3">
+        <v>47355</v>
+      </c>
+      <c r="I19" s="2">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="K19" s="2">
+        <v>89</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="3">
-        <v>45709</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46439</v>
-      </c>
-      <c r="G18" s="2">
-        <v>6</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46439</v>
-      </c>
-      <c r="I18" s="2">
-        <v>100</v>
-      </c>
-      <c r="J18" s="2">
-        <v>7.9500000000000001E-2</v>
-      </c>
-      <c r="K18" s="2">
-        <v>70</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="3">
-        <v>45183</v>
-      </c>
-      <c r="F19" s="3">
-        <v>46095</v>
-      </c>
-      <c r="G19" s="2">
-        <v>6</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46095</v>
-      </c>
-      <c r="I19" s="2">
-        <v>100</v>
-      </c>
-      <c r="J19" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K19" s="2">
-        <v>47</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3">
-        <v>45894</v>
+        <v>44750</v>
       </c>
       <c r="F20" s="3">
-        <v>47355</v>
+        <v>46084</v>
       </c>
       <c r="G20" s="2">
         <v>6</v>
       </c>
       <c r="H20" s="3">
-        <v>47355</v>
+        <v>46084</v>
       </c>
       <c r="I20" s="2">
         <v>100</v>
@@ -2308,74 +2321,74 @@
         <v>0.08</v>
       </c>
       <c r="K20" s="2">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E21" s="3">
-        <v>44750</v>
+        <v>45308</v>
       </c>
       <c r="F21" s="3">
-        <v>46084</v>
+        <v>46404</v>
       </c>
       <c r="G21" s="2">
         <v>6</v>
       </c>
       <c r="H21" s="3">
-        <v>46084</v>
+        <v>46404</v>
       </c>
       <c r="I21" s="2">
         <v>100</v>
       </c>
       <c r="J21" s="2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="K21" s="2">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="3">
-        <v>45308</v>
+        <v>45404</v>
       </c>
       <c r="F22" s="3">
-        <v>46404</v>
+        <v>46256</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" s="3">
-        <v>46404</v>
+        <v>46256</v>
       </c>
       <c r="I22" s="2">
         <v>100</v>
@@ -2384,150 +2397,150 @@
         <v>0.06</v>
       </c>
       <c r="K22" s="2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="3">
-        <v>45404</v>
+        <v>45611</v>
       </c>
       <c r="F23" s="3">
-        <v>46256</v>
+        <v>47072</v>
       </c>
       <c r="G23" s="2">
         <v>6</v>
       </c>
       <c r="H23" s="3">
-        <v>46256</v>
+        <v>47072</v>
       </c>
       <c r="I23" s="2">
         <v>100</v>
       </c>
       <c r="J23" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K23" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="3">
-        <v>45611</v>
+        <v>45849</v>
       </c>
       <c r="F24" s="3">
-        <v>47072</v>
+        <v>46945</v>
       </c>
       <c r="G24" s="2">
         <v>6</v>
       </c>
       <c r="H24" s="3">
-        <v>47072</v>
+        <v>46945</v>
       </c>
       <c r="I24" s="2">
         <v>100</v>
       </c>
       <c r="J24" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K24" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="3">
-        <v>45849</v>
+        <v>45902</v>
       </c>
       <c r="F25" s="3">
-        <v>46945</v>
+        <v>46632</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" s="3">
-        <v>46945</v>
+        <v>46632</v>
       </c>
       <c r="I25" s="2">
         <v>100</v>
       </c>
       <c r="J25" s="2">
-        <v>0.08</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K25" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="3">
-        <v>45902</v>
+        <v>46001</v>
       </c>
       <c r="F26" s="3">
-        <v>46632</v>
+        <v>47187</v>
       </c>
       <c r="G26" s="2">
         <v>6</v>
       </c>
       <c r="H26" s="3">
-        <v>46632</v>
+        <v>47187</v>
       </c>
       <c r="I26" s="2">
         <v>100</v>
@@ -2536,290 +2549,291 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="K26" s="2">
+        <v>29</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="3">
+        <v>45358</v>
+      </c>
+      <c r="F27" s="3">
+        <v>46348</v>
+      </c>
+      <c r="G27" s="2">
+        <v>6</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46348</v>
+      </c>
+      <c r="I27" s="2">
+        <v>100</v>
+      </c>
+      <c r="J27" s="2">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="K27" s="2">
+        <v>95</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="3">
+        <v>45509</v>
+      </c>
+      <c r="F28" s="3">
+        <v>46970</v>
+      </c>
+      <c r="G28" s="2">
+        <v>6</v>
+      </c>
+      <c r="H28" s="3">
+        <v>46970</v>
+      </c>
+      <c r="I28" s="2">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>81</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="3">
+        <v>45589</v>
+      </c>
+      <c r="F29" s="3">
+        <v>47780</v>
+      </c>
+      <c r="G29" s="2">
+        <v>6</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="3">
-        <v>46001</v>
-      </c>
-      <c r="F27" s="3">
-        <v>47187</v>
-      </c>
-      <c r="G27" s="2">
-        <v>6</v>
-      </c>
-      <c r="H27" s="3">
-        <v>47187</v>
-      </c>
-      <c r="I27" s="2">
-        <v>100</v>
-      </c>
-      <c r="J27" s="2">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K27" s="2">
+      <c r="I29" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="3">
-        <v>45876</v>
-      </c>
-      <c r="F28" s="3">
-        <v>46241</v>
-      </c>
-      <c r="G28" s="2">
-        <v>6</v>
-      </c>
-      <c r="H28" s="3">
-        <v>46241</v>
-      </c>
-      <c r="I28" s="2">
-        <v>100</v>
-      </c>
-      <c r="J28" s="2">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="K28" s="2">
-        <v>80</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="3">
-        <v>45358</v>
-      </c>
-      <c r="F29" s="3">
-        <v>46348</v>
-      </c>
-      <c r="G29" s="2">
-        <v>6</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46348</v>
-      </c>
-      <c r="I29" s="2">
-        <v>100</v>
       </c>
       <c r="J29" s="2">
         <v>9.7500000000000003E-2</v>
       </c>
       <c r="K29" s="2">
-        <v>95</v>
+        <v>385</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30" s="3">
-        <v>45509</v>
+        <v>45876</v>
       </c>
       <c r="F30" s="3">
-        <v>46970</v>
+        <v>46241</v>
       </c>
       <c r="G30" s="2">
         <v>6</v>
       </c>
       <c r="H30" s="3">
-        <v>46970</v>
+        <v>46241</v>
       </c>
       <c r="I30" s="2">
         <v>100</v>
       </c>
       <c r="J30" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K30" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E31" s="3">
-        <v>45589</v>
+        <v>45575</v>
       </c>
       <c r="F31" s="3">
-        <v>47780</v>
+        <v>47036</v>
       </c>
       <c r="G31" s="2">
         <v>6</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>88</v>
+      <c r="H31" s="3">
+        <v>47036</v>
+      </c>
+      <c r="I31" s="2">
+        <v>100</v>
       </c>
       <c r="J31" s="2">
-        <v>9.7500000000000003E-2</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="K31" s="2">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E32" s="3">
-        <v>44441</v>
+        <v>45883</v>
       </c>
       <c r="F32" s="3">
-        <v>46632</v>
+        <v>46265</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>93</v>
+      <c r="H32" s="3">
+        <v>46265</v>
+      </c>
+      <c r="I32" s="2">
+        <v>100</v>
       </c>
       <c r="J32" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K32" s="2">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E33" s="3">
-        <v>45993</v>
+        <v>45582</v>
       </c>
       <c r="F33" s="3">
-        <v>48915</v>
+        <v>47043</v>
       </c>
       <c r="G33" s="2">
         <v>6</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>88</v>
+      <c r="H33" s="3">
+        <v>47043</v>
+      </c>
+      <c r="I33" s="2">
+        <v>100</v>
       </c>
       <c r="J33" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K33" s="2">
-        <v>400</v>
+        <v>48</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="3">
         <v>45721</v>
@@ -2843,539 +2857,539 @@
         <v>27</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="3">
+        <v>45993</v>
+      </c>
+      <c r="F35" s="3">
+        <v>48915</v>
+      </c>
+      <c r="G35" s="2">
+        <v>6</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="3">
-        <v>45582</v>
-      </c>
-      <c r="F35" s="3">
-        <v>47043</v>
-      </c>
-      <c r="G35" s="2">
-        <v>6</v>
-      </c>
-      <c r="H35" s="3">
-        <v>47043</v>
-      </c>
-      <c r="I35" s="2">
-        <v>100</v>
-      </c>
       <c r="J35" s="2">
-        <v>0.06</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="K35" s="2">
-        <v>48</v>
+        <v>400</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E36" s="3">
-        <v>45575</v>
+        <v>44441</v>
       </c>
       <c r="F36" s="3">
-        <v>47036</v>
+        <v>46632</v>
       </c>
       <c r="G36" s="2">
         <v>6</v>
       </c>
-      <c r="H36" s="3">
-        <v>47036</v>
-      </c>
-      <c r="I36" s="2">
-        <v>100</v>
+      <c r="H36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J36" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K36" s="2">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" s="3">
-        <v>45883</v>
+        <v>45846</v>
       </c>
       <c r="F37" s="3">
-        <v>46265</v>
+        <v>46942</v>
       </c>
       <c r="G37" s="2">
         <v>6</v>
       </c>
       <c r="H37" s="3">
-        <v>46265</v>
+        <v>46942</v>
       </c>
       <c r="I37" s="2">
         <v>100</v>
       </c>
       <c r="J37" s="2">
-        <v>6.25E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K37" s="2">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" s="3">
-        <v>45804</v>
+        <v>45891</v>
       </c>
       <c r="F38" s="3">
-        <v>46021</v>
+        <v>46256</v>
       </c>
       <c r="G38" s="2">
         <v>6</v>
       </c>
       <c r="H38" s="3">
-        <v>46021</v>
+        <v>46256</v>
       </c>
       <c r="I38" s="2">
         <v>100</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K38" s="2">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E39" s="3">
-        <v>45785</v>
+        <v>44720</v>
       </c>
       <c r="F39" s="3">
-        <v>45989</v>
+        <v>46926</v>
       </c>
       <c r="G39" s="2">
         <v>6</v>
       </c>
-      <c r="H39" s="3">
-        <v>45989</v>
-      </c>
-      <c r="I39" s="2">
-        <v>100</v>
+      <c r="H39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J39" s="2">
-        <v>0</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K39" s="2">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="3">
-        <v>45846</v>
+        <v>45350</v>
       </c>
       <c r="F40" s="3">
-        <v>46942</v>
+        <v>46446</v>
       </c>
       <c r="G40" s="2">
         <v>6</v>
       </c>
       <c r="H40" s="3">
-        <v>46942</v>
+        <v>46446</v>
       </c>
       <c r="I40" s="2">
         <v>100</v>
       </c>
       <c r="J40" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K40" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" s="3">
-        <v>45891</v>
+        <v>45453</v>
       </c>
       <c r="F41" s="3">
-        <v>46256</v>
+        <v>46183</v>
       </c>
       <c r="G41" s="2">
         <v>6</v>
       </c>
       <c r="H41" s="3">
-        <v>46256</v>
+        <v>46183</v>
       </c>
       <c r="I41" s="2">
         <v>100</v>
       </c>
       <c r="J41" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K41" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42" s="3">
-        <v>45084</v>
+        <v>45588</v>
       </c>
       <c r="F42" s="3">
-        <v>45998</v>
+        <v>46683</v>
       </c>
       <c r="G42" s="2">
         <v>6</v>
       </c>
       <c r="H42" s="3">
-        <v>45998</v>
+        <v>46683</v>
       </c>
       <c r="I42" s="2">
         <v>100</v>
       </c>
       <c r="J42" s="2">
-        <v>0.05</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K42" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="3">
-        <v>45453</v>
+        <v>45588</v>
       </c>
       <c r="F43" s="3">
-        <v>46183</v>
+        <v>47414</v>
       </c>
       <c r="G43" s="2">
         <v>6</v>
       </c>
       <c r="H43" s="3">
-        <v>46183</v>
+        <v>47414</v>
       </c>
       <c r="I43" s="2">
         <v>100</v>
       </c>
       <c r="J43" s="2">
-        <v>0.06</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K43" s="2">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E44" s="3">
-        <v>45350</v>
+        <v>45747</v>
       </c>
       <c r="F44" s="3">
-        <v>46446</v>
+        <v>49399</v>
       </c>
       <c r="G44" s="2">
         <v>6</v>
       </c>
-      <c r="H44" s="3">
-        <v>46446</v>
-      </c>
-      <c r="I44" s="2">
-        <v>100</v>
+      <c r="H44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J44" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K44" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E45" s="3">
-        <v>44720</v>
+        <v>45586</v>
       </c>
       <c r="F45" s="3">
-        <v>46926</v>
+        <v>46316</v>
       </c>
       <c r="G45" s="2">
         <v>6</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>96</v>
+      <c r="H45" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I45" s="2">
+        <v>100</v>
       </c>
       <c r="J45" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K45" s="2">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46" s="3">
-        <v>45588</v>
+        <v>45586</v>
       </c>
       <c r="F46" s="3">
-        <v>46683</v>
+        <v>47047</v>
       </c>
       <c r="G46" s="2">
         <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>46683</v>
+        <v>47047</v>
       </c>
       <c r="I46" s="2">
         <v>100</v>
       </c>
       <c r="J46" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K46" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E47" s="3">
-        <v>45747</v>
+        <v>45674</v>
       </c>
       <c r="F47" s="3">
-        <v>49399</v>
+        <v>46769</v>
       </c>
       <c r="G47" s="2">
         <v>6</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>88</v>
+      <c r="H47" s="3">
+        <v>46769</v>
+      </c>
+      <c r="I47" s="2">
+        <v>100</v>
       </c>
       <c r="J47" s="2">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K47" s="2">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" s="3">
-        <v>45588</v>
+        <v>45804</v>
       </c>
       <c r="F48" s="3">
-        <v>47414</v>
+        <v>46534</v>
       </c>
       <c r="G48" s="2">
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>47414</v>
+        <v>46534</v>
       </c>
       <c r="I48" s="2">
         <v>100</v>
       </c>
       <c r="J48" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K48" s="2">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
@@ -3383,37 +3397,37 @@
         <v>140</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49" s="3">
-        <v>45586</v>
+        <v>45863</v>
       </c>
       <c r="F49" s="3">
-        <v>46316</v>
+        <v>46593</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>46316</v>
+        <v>46593</v>
       </c>
       <c r="I49" s="2">
         <v>100</v>
       </c>
       <c r="J49" s="2">
-        <v>0.05</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K49" s="2">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
@@ -3421,37 +3435,37 @@
         <v>141</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E50" s="3">
-        <v>45586</v>
+        <v>45180</v>
       </c>
       <c r="F50" s="3">
-        <v>47047</v>
+        <v>46092</v>
       </c>
       <c r="G50" s="2">
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>47047</v>
+        <v>46092</v>
       </c>
       <c r="I50" s="2">
         <v>100</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K50" s="2">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
@@ -3459,37 +3473,37 @@
         <v>142</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3">
-        <v>45674</v>
+        <v>45862</v>
       </c>
       <c r="F51" s="3">
-        <v>46769</v>
+        <v>46592</v>
       </c>
       <c r="G51" s="2">
         <v>6</v>
       </c>
       <c r="H51" s="3">
-        <v>46769</v>
+        <v>46592</v>
       </c>
       <c r="I51" s="2">
         <v>100</v>
       </c>
       <c r="J51" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K51" s="2">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
@@ -3497,37 +3511,37 @@
         <v>143</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E52" s="3">
-        <v>45804</v>
+        <v>45831</v>
       </c>
       <c r="F52" s="3">
-        <v>46534</v>
+        <v>47292</v>
       </c>
       <c r="G52" s="2">
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>46534</v>
+        <v>47292</v>
       </c>
       <c r="I52" s="2">
         <v>100</v>
       </c>
       <c r="J52" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K52" s="2">
-        <v>42</v>
+        <v>530</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
@@ -3535,63 +3549,63 @@
         <v>144</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E53" s="3">
-        <v>45863</v>
+        <v>46050</v>
       </c>
       <c r="F53" s="3">
-        <v>46593</v>
+        <v>47876</v>
       </c>
       <c r="G53" s="2">
         <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>46593</v>
+        <v>47876</v>
       </c>
       <c r="I53" s="2">
         <v>100</v>
       </c>
       <c r="J53" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K53" s="2">
+        <v>400</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" s="3">
-        <v>45098</v>
+        <v>45124</v>
       </c>
       <c r="F54" s="3">
-        <v>46012</v>
+        <v>46220</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
       </c>
       <c r="H54" s="3">
-        <v>46012</v>
+        <v>46220</v>
       </c>
       <c r="I54" s="2">
         <v>100</v>
@@ -3600,36 +3614,36 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="K54" s="2">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" s="3">
-        <v>45180</v>
+        <v>45496</v>
       </c>
       <c r="F55" s="3">
-        <v>46092</v>
+        <v>46591</v>
       </c>
       <c r="G55" s="2">
         <v>6</v>
       </c>
       <c r="H55" s="3">
-        <v>46092</v>
+        <v>46591</v>
       </c>
       <c r="I55" s="2">
         <v>100</v>
@@ -3638,328 +3652,328 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K55" s="2">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="3">
+        <v>45363</v>
+      </c>
+      <c r="F56" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G56" s="2">
+        <v>6</v>
+      </c>
+      <c r="H56" s="3">
+        <v>46093</v>
+      </c>
+      <c r="I56" s="2">
+        <v>100</v>
+      </c>
+      <c r="J56" s="2">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="K56" s="2">
         <v>13</v>
       </c>
-      <c r="E56" s="3">
-        <v>45862</v>
-      </c>
-      <c r="F56" s="3">
-        <v>46592</v>
-      </c>
-      <c r="G56" s="2">
-        <v>6</v>
-      </c>
-      <c r="H56" s="3">
-        <v>46592</v>
-      </c>
-      <c r="I56" s="2">
-        <v>100</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="K56" s="2">
-        <v>112</v>
-      </c>
       <c r="L56" s="2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E57" s="3">
-        <v>45831</v>
+        <v>45631</v>
       </c>
       <c r="F57" s="3">
-        <v>47292</v>
+        <v>47822</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
       </c>
-      <c r="H57" s="3">
-        <v>47292</v>
-      </c>
-      <c r="I57" s="2">
-        <v>100</v>
+      <c r="H57" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="K57" s="2">
-        <v>530</v>
+        <v>400</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>163</v>
+        <v>95</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="3">
-        <v>45363</v>
+        <v>45820</v>
       </c>
       <c r="F58" s="3">
-        <v>46093</v>
+        <v>46916</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
       </c>
       <c r="H58" s="3">
-        <v>46093</v>
+        <v>46916</v>
       </c>
       <c r="I58" s="2">
         <v>100</v>
       </c>
       <c r="J58" s="2">
-        <v>8.2500000000000004E-2</v>
-      </c>
-      <c r="K58" s="2">
-        <v>13</v>
+        <v>7.8899999999999998E-2</v>
+      </c>
+      <c r="K58" s="5">
+        <v>85</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>163</v>
+        <v>95</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E59" s="3">
-        <v>45631</v>
+        <v>45996</v>
       </c>
       <c r="F59" s="3">
-        <v>47822</v>
+        <v>47274</v>
       </c>
       <c r="G59" s="2">
         <v>6</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>164</v>
+      <c r="H59" s="3">
+        <v>47274</v>
+      </c>
+      <c r="I59" s="2">
+        <v>100</v>
       </c>
       <c r="J59" s="2">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="K59" s="2">
-        <v>400</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K59" s="5">
+        <v>115</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60" s="3">
-        <v>45124</v>
+        <v>45562</v>
       </c>
       <c r="F60" s="3">
-        <v>46220</v>
+        <v>46657</v>
       </c>
       <c r="G60" s="2">
         <v>6</v>
       </c>
       <c r="H60" s="3">
-        <v>46220</v>
+        <v>46657</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
       </c>
       <c r="J60" s="2">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="K60" s="2">
-        <v>25</v>
+        <v>0.05</v>
+      </c>
+      <c r="K60" s="5">
+        <v>23</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" s="3">
-        <v>45496</v>
+        <v>45562</v>
       </c>
       <c r="F61" s="3">
-        <v>46591</v>
+        <v>47388</v>
       </c>
       <c r="G61" s="2">
         <v>6</v>
       </c>
       <c r="H61" s="3">
-        <v>46591</v>
+        <v>47388</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
       </c>
       <c r="J61" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="K61" s="2">
-        <v>33</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K61" s="5">
+        <v>176</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62" s="3">
-        <v>45947</v>
+        <v>45609</v>
       </c>
       <c r="F62" s="3">
-        <v>46494</v>
+        <v>48165</v>
       </c>
       <c r="G62" s="2">
         <v>6</v>
       </c>
       <c r="H62" s="3">
-        <v>46494</v>
+        <v>48165</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
       </c>
       <c r="J62" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="K62" s="2">
-        <v>56</v>
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="K62" s="5">
+        <v>78</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63" s="3">
-        <v>45896</v>
+        <v>45609</v>
       </c>
       <c r="F63" s="3">
-        <v>47357</v>
+        <v>47070</v>
       </c>
       <c r="G63" s="2">
         <v>6</v>
       </c>
       <c r="H63" s="3">
-        <v>47357</v>
+        <v>47070</v>
       </c>
       <c r="I63" s="2">
         <v>100</v>
       </c>
       <c r="J63" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="K63" s="2">
-        <v>85</v>
+        <v>6.25E-2</v>
+      </c>
+      <c r="K63" s="5">
+        <v>74</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E64" s="3">
         <v>45699</v>
@@ -3983,401 +3997,401 @@
         <v>120</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E65" s="3">
-        <v>45562</v>
+        <v>45896</v>
       </c>
       <c r="F65" s="3">
-        <v>47388</v>
+        <v>47357</v>
       </c>
       <c r="G65" s="2">
         <v>6</v>
       </c>
       <c r="H65" s="3">
-        <v>47388</v>
+        <v>47357</v>
       </c>
       <c r="I65" s="2">
         <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K65" s="5">
-        <v>176</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K65" s="2">
+        <v>85</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66" s="3">
-        <v>45562</v>
+        <v>45947</v>
       </c>
       <c r="F66" s="3">
-        <v>46657</v>
+        <v>46494</v>
       </c>
       <c r="G66" s="2">
         <v>6</v>
       </c>
       <c r="H66" s="3">
-        <v>46657</v>
+        <v>46494</v>
       </c>
       <c r="I66" s="2">
         <v>100</v>
       </c>
       <c r="J66" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="K66" s="5">
-        <v>23</v>
+        <v>0.06</v>
+      </c>
+      <c r="K66" s="2">
+        <v>56</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E67" s="3">
-        <v>45609</v>
+        <v>46037</v>
       </c>
       <c r="F67" s="3">
-        <v>48165</v>
+        <v>50055</v>
       </c>
       <c r="G67" s="2">
         <v>6</v>
       </c>
-      <c r="H67" s="3">
-        <v>48165</v>
-      </c>
-      <c r="I67" s="2">
-        <v>100</v>
+      <c r="H67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J67" s="2">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K67" s="5">
-        <v>78</v>
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="K67" s="2">
+        <v>375</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68" s="3">
-        <v>45609</v>
+        <v>44316</v>
       </c>
       <c r="F68" s="3">
-        <v>47070</v>
+        <v>46507</v>
       </c>
       <c r="G68" s="2">
         <v>6</v>
       </c>
-      <c r="H68" s="3">
-        <v>47070</v>
-      </c>
-      <c r="I68" s="2">
-        <v>100</v>
+      <c r="H68" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J68" s="2">
-        <v>6.25E-2</v>
+        <v>9.1249999999999998E-2</v>
       </c>
       <c r="K68" s="5">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E69" s="3">
-        <v>44316</v>
+        <v>45412</v>
       </c>
       <c r="F69" s="3">
-        <v>46507</v>
+        <v>48334</v>
       </c>
       <c r="G69" s="2">
         <v>6</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="J69" s="2">
-        <v>9.1249999999999998E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K69" s="5">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E70" s="3">
-        <v>45412</v>
+        <v>44903</v>
       </c>
       <c r="F70" s="3">
-        <v>48334</v>
+        <v>46364</v>
       </c>
       <c r="G70" s="2">
         <v>6</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="J70" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K70" s="5">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E71" s="3">
-        <v>45569</v>
+        <v>45545</v>
       </c>
       <c r="F71" s="3">
-        <v>47030</v>
+        <v>48101</v>
       </c>
       <c r="G71" s="2">
         <v>6</v>
       </c>
       <c r="H71" s="3">
-        <v>47030</v>
+        <v>48101</v>
       </c>
       <c r="I71" s="2">
         <v>100</v>
       </c>
       <c r="J71" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K71" s="5">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E72" s="3">
-        <v>45050</v>
+        <v>45569</v>
       </c>
       <c r="F72" s="3">
-        <v>45965</v>
+        <v>47030</v>
       </c>
       <c r="G72" s="2">
         <v>6</v>
       </c>
       <c r="H72" s="3">
-        <v>45965</v>
+        <v>47030</v>
       </c>
       <c r="I72" s="2">
         <v>100</v>
       </c>
       <c r="J72" s="2">
-        <v>0.05</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K72" s="5">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E73" s="3">
-        <v>45545</v>
+        <v>45642</v>
       </c>
       <c r="F73" s="3">
-        <v>48101</v>
+        <v>49294</v>
       </c>
       <c r="G73" s="2">
         <v>6</v>
       </c>
       <c r="H73" s="3">
-        <v>48101</v>
+        <v>49294</v>
       </c>
       <c r="I73" s="2">
         <v>100</v>
       </c>
       <c r="J73" s="2">
-        <v>7.9500000000000001E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K73" s="5">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E74" s="3">
-        <v>45642</v>
+        <v>45875</v>
       </c>
       <c r="F74" s="3">
-        <v>49294</v>
+        <v>46971</v>
       </c>
       <c r="G74" s="2">
         <v>6</v>
       </c>
       <c r="H74" s="3">
-        <v>49294</v>
+        <v>46971</v>
       </c>
       <c r="I74" s="2">
         <v>100</v>
       </c>
       <c r="J74" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K74" s="5">
-        <v>700</v>
+        <v>83</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E75" s="3">
         <v>45975</v>
@@ -4401,136 +4415,137 @@
         <v>450</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E76" s="3">
-        <v>45875</v>
+        <v>46113</v>
       </c>
       <c r="F76" s="3">
-        <v>46971</v>
+        <v>47209</v>
       </c>
       <c r="G76" s="2">
         <v>6</v>
       </c>
       <c r="H76" s="3">
-        <v>46971</v>
+        <v>47209</v>
       </c>
       <c r="I76" s="2">
         <v>100</v>
       </c>
       <c r="J76" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K76" s="5">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E77" s="3">
-        <v>44903</v>
+        <v>45587</v>
       </c>
       <c r="F77" s="3">
-        <v>46364</v>
+        <v>47048</v>
       </c>
       <c r="G77" s="2">
         <v>6</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>88</v>
+      <c r="H77" s="3">
+        <f>F77</f>
+        <v>47048</v>
+      </c>
+      <c r="I77" s="2">
+        <v>100</v>
       </c>
       <c r="J77" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K77" s="5">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78" s="3">
-        <v>45587</v>
+        <v>45705</v>
       </c>
       <c r="F78" s="3">
-        <v>47048</v>
+        <v>47896</v>
       </c>
       <c r="G78" s="2">
         <v>6</v>
       </c>
       <c r="H78" s="3">
         <f>F78</f>
-        <v>47048</v>
+        <v>47896</v>
       </c>
       <c r="I78" s="2">
         <v>100</v>
       </c>
       <c r="J78" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K78" s="5">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E79" s="3">
         <v>45859</v>
@@ -4555,98 +4570,97 @@
         <v>38</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E80" s="3">
-        <v>45705</v>
+        <v>45838</v>
       </c>
       <c r="F80" s="3">
-        <v>47896</v>
+        <v>48364</v>
       </c>
       <c r="G80" s="2">
         <v>6</v>
       </c>
       <c r="H80" s="3">
-        <f>F80</f>
-        <v>47896</v>
+        <v>48364</v>
       </c>
       <c r="I80" s="2">
         <v>100</v>
       </c>
       <c r="J80" s="2">
-        <v>0.08</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K80" s="5">
-        <v>65</v>
+        <v>650</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E81" s="3">
-        <v>45838</v>
+        <v>45895</v>
       </c>
       <c r="F81" s="3">
-        <v>48364</v>
+        <v>46260</v>
       </c>
       <c r="G81" s="2">
         <v>6</v>
       </c>
       <c r="H81" s="3">
-        <v>48364</v>
+        <v>46260</v>
       </c>
       <c r="I81" s="2">
         <v>100</v>
       </c>
       <c r="J81" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K81" s="5">
-        <v>650</v>
+        <v>16</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E82" s="3">
         <v>45412</v>
@@ -4670,21 +4684,21 @@
         <v>32</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E83" s="3">
         <v>45404</v>
@@ -4708,97 +4722,97 @@
         <v>120</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E84" s="3">
         <v>45589</v>
       </c>
       <c r="F84" s="3">
-        <v>47415</v>
+        <v>46684</v>
       </c>
       <c r="G84" s="2">
         <v>6</v>
       </c>
       <c r="H84" s="3">
-        <v>47415</v>
+        <v>46684</v>
       </c>
       <c r="I84" s="2">
         <v>100</v>
       </c>
       <c r="J84" s="2">
-        <v>6.8000000000000005E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K84" s="5">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E85" s="3">
         <v>45589</v>
       </c>
       <c r="F85" s="3">
-        <v>46684</v>
+        <v>47415</v>
       </c>
       <c r="G85" s="2">
         <v>6</v>
       </c>
       <c r="H85" s="3">
-        <v>46684</v>
+        <v>47415</v>
       </c>
       <c r="I85" s="2">
         <v>100</v>
       </c>
       <c r="J85" s="2">
-        <v>0.05</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="K85" s="5">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E86" s="3">
         <v>45679</v>
@@ -4810,10 +4824,10 @@
         <v>6</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="J86" s="2">
         <v>7.6249999999999998E-2</v>
@@ -4822,21 +4836,21 @@
         <v>400</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E87" s="3">
         <v>45946</v>
@@ -4861,21 +4875,21 @@
         <v>67</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E88" s="3">
         <v>45964</v>
@@ -4899,21 +4913,21 @@
         <v>750</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E89" s="3">
         <v>45309</v>
@@ -4937,59 +4951,59 @@
         <v>284</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E90" s="3">
-        <v>45840</v>
+        <v>45491</v>
       </c>
       <c r="F90" s="3">
-        <v>46570</v>
+        <v>48047</v>
       </c>
       <c r="G90" s="2">
-        <v>3</v>
-      </c>
-      <c r="H90" s="3">
-        <v>46570</v>
-      </c>
-      <c r="I90" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J90" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K90" s="5">
-        <v>50</v>
+        <v>817</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E91" s="3">
         <v>45624</v>
@@ -5013,363 +5027,363 @@
         <v>75</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E92" s="3">
-        <v>45491</v>
+        <v>45805</v>
       </c>
       <c r="F92" s="3">
-        <v>48047</v>
+        <v>48727</v>
       </c>
       <c r="G92" s="2">
         <v>6</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="J92" s="2">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="K92" s="5">
-        <v>817</v>
+        <v>1000</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E93" s="3">
-        <v>45805</v>
+        <v>45840</v>
       </c>
       <c r="F93" s="3">
-        <v>48727</v>
+        <v>46570</v>
       </c>
       <c r="G93" s="2">
-        <v>6</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>157</v>
+        <v>3</v>
+      </c>
+      <c r="H93" s="3">
+        <v>46570</v>
+      </c>
+      <c r="I93" s="2">
+        <v>100</v>
       </c>
       <c r="J93" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K93" s="5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E94" s="3">
-        <v>45497</v>
+        <v>46042</v>
       </c>
       <c r="F94" s="3">
-        <v>48053</v>
+        <v>49694</v>
       </c>
       <c r="G94" s="2">
         <v>6</v>
       </c>
-      <c r="H94" s="3">
-        <v>48053</v>
-      </c>
-      <c r="I94" s="2">
-        <v>100</v>
+      <c r="H94" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J94" s="2">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="K94" s="5">
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E95" s="3">
-        <v>45981</v>
+        <v>45497</v>
       </c>
       <c r="F95" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="G95" s="2">
         <v>6</v>
       </c>
       <c r="H95" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="I95" s="2">
         <v>100</v>
       </c>
       <c r="J95" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K95" s="5">
-        <v>1030</v>
+        <v>490</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E96" s="3">
-        <v>45803</v>
+        <v>45981</v>
       </c>
       <c r="F96" s="3">
-        <v>45987</v>
+        <v>49633</v>
       </c>
       <c r="G96" s="2">
         <v>6</v>
       </c>
       <c r="H96" s="3">
-        <v>45987</v>
+        <v>49633</v>
       </c>
       <c r="I96" s="2">
         <v>100</v>
       </c>
       <c r="J96" s="2">
-        <v>4.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K96" s="5">
-        <v>59</v>
+        <v>1030</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E97" s="3">
-        <v>45895</v>
+        <v>45415</v>
       </c>
       <c r="F97" s="3">
-        <v>46260</v>
+        <v>47241</v>
       </c>
       <c r="G97" s="2">
         <v>6</v>
       </c>
-      <c r="H97" s="3">
-        <v>46260</v>
-      </c>
-      <c r="I97" s="2">
-        <v>100</v>
+      <c r="H97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J97" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K97" s="5">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>45415</v>
+        <v>45575</v>
       </c>
       <c r="F98" s="3">
-        <v>47241</v>
+        <v>48131</v>
       </c>
       <c r="G98" s="2">
         <v>6</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="J98" s="2">
-        <v>0.08</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K98" s="5">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E99" s="3">
-        <v>45723</v>
+        <v>45636</v>
       </c>
       <c r="F99" s="3">
-        <v>47549</v>
+        <v>49653</v>
       </c>
       <c r="G99" s="2">
         <v>6</v>
       </c>
-      <c r="H99" s="3">
-        <v>47549</v>
-      </c>
-      <c r="I99" s="2">
-        <v>100</v>
+      <c r="H99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J99" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K99" s="5">
-        <v>92</v>
+        <v>600</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E100" s="3">
-        <v>45575</v>
+        <v>45723</v>
       </c>
       <c r="F100" s="3">
-        <v>48131</v>
+        <v>47549</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>88</v>
+      <c r="H100" s="3">
+        <v>47549</v>
+      </c>
+      <c r="I100" s="2">
+        <v>100</v>
       </c>
       <c r="J100" s="2">
-        <v>7.6499999999999999E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K100" s="5">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E101" s="3">
         <v>45818</v>
@@ -5390,141 +5404,141 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K101" s="5">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E102" s="3">
-        <v>45636</v>
+        <v>45945</v>
       </c>
       <c r="F102" s="3">
-        <v>49653</v>
+        <v>46492</v>
       </c>
       <c r="G102" s="2">
         <v>6</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>88</v>
+      <c r="H102" s="3">
+        <v>46492</v>
+      </c>
+      <c r="I102" s="2">
+        <v>100</v>
       </c>
       <c r="J102" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K102" s="5">
-        <v>600</v>
+        <v>73</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E103" s="3">
-        <v>45945</v>
+        <v>46120</v>
       </c>
       <c r="F103" s="3">
-        <v>46492</v>
+        <v>50503</v>
       </c>
       <c r="G103" s="2">
         <v>6</v>
       </c>
-      <c r="H103" s="3">
-        <v>46492</v>
-      </c>
-      <c r="I103" s="2">
-        <v>100</v>
+      <c r="H103" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J103" s="2">
-        <v>0.06</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K103" s="5">
-        <v>73</v>
+        <v>500</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E104" s="3">
-        <v>43671</v>
+        <v>45674</v>
       </c>
       <c r="F104" s="3">
-        <v>46228</v>
+        <v>48961</v>
       </c>
       <c r="G104" s="2">
         <v>6</v>
       </c>
-      <c r="H104" s="3">
-        <v>46228</v>
-      </c>
-      <c r="I104" s="2">
-        <v>100</v>
+      <c r="H104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J104" s="2">
-        <v>0.1</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K104" s="5">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E105" s="3">
-        <v>45349</v>
+        <v>45715</v>
       </c>
       <c r="F105" s="3">
         <v>46445</v>
@@ -5539,293 +5553,293 @@
         <v>100</v>
       </c>
       <c r="J105" s="2">
-        <v>0.06</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K105" s="5">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E106" s="3">
-        <v>45456</v>
+        <v>45784</v>
       </c>
       <c r="F106" s="3">
-        <v>46551</v>
+        <v>46514</v>
       </c>
       <c r="G106" s="2">
         <v>3</v>
       </c>
-      <c r="H106" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>157</v>
+      <c r="H106" s="3">
+        <v>46514</v>
+      </c>
+      <c r="I106" s="2">
+        <v>100</v>
       </c>
       <c r="J106" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K106" s="5">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E107" s="3">
-        <v>45581</v>
+        <v>45860</v>
       </c>
       <c r="F107" s="3">
-        <v>48503</v>
+        <v>46590</v>
       </c>
       <c r="G107" s="2">
-        <v>6</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>88</v>
+        <v>3</v>
+      </c>
+      <c r="H107" s="3">
+        <v>46590</v>
+      </c>
+      <c r="I107" s="2">
+        <v>100</v>
       </c>
       <c r="J107" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K107" s="5">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E108" s="3">
-        <v>45618</v>
+        <v>45860</v>
       </c>
       <c r="F108" s="3">
-        <v>46348</v>
+        <v>47686</v>
       </c>
       <c r="G108" s="2">
         <v>6</v>
       </c>
       <c r="H108" s="3">
-        <v>46348</v>
+        <v>47686</v>
       </c>
       <c r="I108" s="2">
         <v>100</v>
       </c>
       <c r="J108" s="2">
-        <v>5.2499999999999998E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K108" s="5">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E109" s="3">
-        <v>45618</v>
+        <v>45938</v>
       </c>
       <c r="F109" s="3">
-        <v>47079</v>
+        <v>46454</v>
       </c>
       <c r="G109" s="2">
         <v>3</v>
       </c>
       <c r="H109" s="3">
-        <v>47079</v>
+        <v>46454</v>
       </c>
       <c r="I109" s="2">
         <v>100</v>
       </c>
       <c r="J109" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K109" s="5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E110" s="3">
-        <v>45797</v>
+        <v>45993</v>
       </c>
       <c r="F110" s="3">
-        <v>46527</v>
+        <v>47179</v>
       </c>
       <c r="G110" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H110" s="3">
-        <v>46527</v>
+        <v>47179</v>
       </c>
       <c r="I110" s="2">
         <v>100</v>
       </c>
       <c r="J110" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K110" s="5">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E111" s="3">
-        <v>46006</v>
+        <v>44239</v>
       </c>
       <c r="F111" s="3">
-        <v>47102</v>
+        <v>47299</v>
       </c>
       <c r="G111" s="2">
-        <v>3</v>
-      </c>
-      <c r="H111" s="3">
-        <v>47102</v>
-      </c>
-      <c r="I111" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J111" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.09</v>
       </c>
       <c r="K111" s="5">
-        <v>45</v>
+        <v>747</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E112" s="3">
-        <v>45575</v>
+        <v>45199</v>
       </c>
       <c r="F112" s="3">
-        <v>47036</v>
+        <v>48852</v>
       </c>
       <c r="G112" s="2">
         <v>6</v>
       </c>
-      <c r="H112" s="3">
-        <v>47036</v>
-      </c>
-      <c r="I112" s="2">
-        <v>100</v>
+      <c r="H112" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J112" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K112" s="5">
-        <v>25</v>
+        <v>575</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>76</v>
+        <v>201</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E113" s="3">
         <v>45090</v>
@@ -5849,21 +5863,21 @@
         <v>263</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E114" s="3">
         <v>45624</v>
@@ -5887,429 +5901,436 @@
         <v>177</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E115" s="3">
-        <v>45715</v>
+        <v>45546</v>
       </c>
       <c r="F115" s="3">
-        <v>46445</v>
+        <v>48102</v>
       </c>
       <c r="G115" s="2">
         <v>6</v>
       </c>
-      <c r="H115" s="3">
-        <v>46445</v>
-      </c>
-      <c r="I115" s="2">
-        <v>100</v>
+      <c r="H115" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J115" s="2">
-        <v>6.25E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K115" s="5">
-        <v>139</v>
+        <v>1000</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E116" s="3">
-        <v>45784</v>
+        <v>45575</v>
       </c>
       <c r="F116" s="3">
-        <v>46514</v>
+        <v>47036</v>
       </c>
       <c r="G116" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H116" s="3">
-        <v>46514</v>
+        <v>47036</v>
       </c>
       <c r="I116" s="2">
         <v>100</v>
       </c>
       <c r="J116" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K116" s="5">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E117" s="3">
-        <v>45860</v>
+        <v>45575</v>
       </c>
       <c r="F117" s="3">
-        <v>46590</v>
+        <v>47036</v>
       </c>
       <c r="G117" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H117" s="3">
-        <v>46590</v>
+        <v>47036</v>
       </c>
       <c r="I117" s="2">
         <v>100</v>
       </c>
       <c r="J117" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K117" s="5">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="E118" s="3">
-        <v>44239</v>
+        <v>43671</v>
       </c>
       <c r="F118" s="3">
-        <v>47299</v>
+        <v>46228</v>
       </c>
       <c r="G118" s="2">
         <v>6</v>
       </c>
-      <c r="H118" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>108</v>
+      <c r="H118" s="3">
+        <v>46228</v>
+      </c>
+      <c r="I118" s="2">
+        <v>100</v>
       </c>
       <c r="J118" s="2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K118" s="5">
-        <v>747</v>
+        <v>400</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E119" s="3">
-        <v>45575</v>
+        <v>45349</v>
       </c>
       <c r="F119" s="3">
-        <v>47036</v>
+        <v>46445</v>
       </c>
       <c r="G119" s="2">
         <v>6</v>
       </c>
       <c r="H119" s="3">
-        <v>47036</v>
+        <v>46445</v>
       </c>
       <c r="I119" s="2">
         <v>100</v>
       </c>
       <c r="J119" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K119" s="5">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E120" s="3">
-        <v>45860</v>
+        <v>45456</v>
       </c>
       <c r="F120" s="3">
-        <v>47686</v>
+        <v>46551</v>
       </c>
       <c r="G120" s="2">
-        <v>6</v>
-      </c>
-      <c r="H120" s="3">
-        <v>47686</v>
-      </c>
-      <c r="I120" s="2">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J120" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K120" s="5">
-        <v>224</v>
+        <v>10</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E121" s="3">
-        <v>45938</v>
+        <v>45581</v>
       </c>
       <c r="F121" s="3">
-        <v>46454</v>
+        <v>48503</v>
       </c>
       <c r="G121" s="2">
-        <v>3</v>
-      </c>
-      <c r="H121" s="3">
-        <v>46454</v>
-      </c>
-      <c r="I121" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J121" s="2">
-        <v>0.06</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K121" s="5">
-        <v>1000</v>
+        <v>123</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E122" s="3">
-        <v>45993</v>
+        <v>45618</v>
       </c>
       <c r="F122" s="3">
-        <v>47179</v>
+        <v>46348</v>
       </c>
       <c r="G122" s="2">
         <v>6</v>
       </c>
       <c r="H122" s="3">
-        <v>47179</v>
+        <v>46348</v>
       </c>
       <c r="I122" s="2">
         <v>100</v>
       </c>
       <c r="J122" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="K122" s="5">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E123" s="3">
-        <v>47372</v>
+        <v>45618</v>
       </c>
       <c r="F123" s="3">
-        <v>48102</v>
+        <v>47079</v>
       </c>
       <c r="G123" s="2">
-        <v>6</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>88</v>
+        <v>3</v>
+      </c>
+      <c r="H123" s="3">
+        <v>47079</v>
+      </c>
+      <c r="I123" s="2">
+        <v>100</v>
       </c>
       <c r="J123" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K123" s="5">
-        <v>540</v>
+        <v>50</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E124" s="3">
-        <v>45674</v>
+        <v>45797</v>
       </c>
       <c r="F124" s="3">
-        <v>48961</v>
+        <v>46527</v>
       </c>
       <c r="G124" s="2">
-        <v>6</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>88</v>
+        <v>3</v>
+      </c>
+      <c r="H124" s="3">
+        <v>46527</v>
+      </c>
+      <c r="I124" s="2">
+        <v>100</v>
       </c>
       <c r="J124" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K124" s="5">
-        <v>1100</v>
+        <v>53</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E125" s="3">
-        <v>45199</v>
+        <v>46006</v>
       </c>
       <c r="F125" s="3">
-        <v>48852</v>
+        <v>47102</v>
       </c>
       <c r="G125" s="2">
-        <v>6</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>104</v>
+        <v>3</v>
+      </c>
+      <c r="H125" s="3">
+        <v>47102</v>
+      </c>
+      <c r="I125" s="2">
+        <v>100</v>
       </c>
       <c r="J125" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K125" s="5">
-        <v>575</v>
+        <v>45</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="130" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H130" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L125" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L125">
+      <sortCondition ref="B1:B125"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAED1C6E-12AD-4A04-A773-BFAB253A1EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE29E89F-562C-4878-9F8D-BEA7B920F7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="listado_ons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$126</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="221">
   <si>
     <t>name</t>
   </si>
@@ -314,9 +314,6 @@
     <t>Petroquímica Comodoro Rivadavia</t>
   </si>
   <si>
-    <t>DLK</t>
-  </si>
-  <si>
     <t>2/12/2031;2/12/2032;2/12/2033</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>AERBO</t>
   </si>
   <si>
-    <t>LMS6O</t>
-  </si>
-  <si>
     <t>LMS7O</t>
   </si>
   <si>
@@ -699,6 +693,12 @@
   </si>
   <si>
     <t>MGCTO</t>
+  </si>
+  <si>
+    <t>TLCUO</t>
+  </si>
+  <si>
+    <t>PLC6O</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N130"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>81</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>81</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
@@ -1719,37 +1719,37 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
-        <v>45043</v>
+        <v>45211</v>
       </c>
       <c r="F5" s="3">
-        <v>46870</v>
+        <v>47038</v>
       </c>
       <c r="G5" s="2">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46870</v>
-      </c>
-      <c r="I5" s="2">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K5" s="2">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>52</v>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>57</v>
@@ -1769,25 +1769,25 @@
         <v>12</v>
       </c>
       <c r="E6" s="3">
-        <v>45211</v>
+        <v>45372</v>
       </c>
       <c r="F6" s="3">
-        <v>47038</v>
+        <v>46467</v>
       </c>
       <c r="G6" s="2">
         <v>3</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="J6" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K6" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>52</v>
@@ -1795,37 +1795,37 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="3">
-        <v>45372</v>
+        <v>45456</v>
       </c>
       <c r="F7" s="3">
-        <v>46467</v>
+        <v>46186</v>
       </c>
       <c r="G7" s="2">
         <v>3</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>43</v>
+      <c r="H7" s="3">
+        <v>46186</v>
+      </c>
+      <c r="I7" s="2">
+        <v>100</v>
       </c>
       <c r="J7" s="2">
-        <v>6.25E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K7" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>52</v>
@@ -1833,114 +1833,114 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E8" s="3">
-        <v>45456</v>
+        <v>45869</v>
       </c>
       <c r="F8" s="3">
-        <v>46186</v>
+        <v>48791</v>
       </c>
       <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46186</v>
-      </c>
-      <c r="I8" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J8" s="2">
-        <v>0.06</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="K8" s="2">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3">
-        <v>45869</v>
+        <v>45936</v>
       </c>
       <c r="F9" s="3">
-        <v>48791</v>
+        <v>46301</v>
       </c>
       <c r="G9" s="2">
         <v>6</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>61</v>
+      <c r="H9" s="3">
+        <v>46301</v>
+      </c>
+      <c r="I9" s="2">
+        <v>100</v>
       </c>
       <c r="J9" s="2">
-        <v>7.5999999999999998E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="K9" s="2">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="3">
-        <v>45936</v>
+        <v>44874</v>
       </c>
       <c r="F10" s="3">
-        <v>46301</v>
+        <v>46669</v>
       </c>
       <c r="G10" s="2">
         <v>6</v>
       </c>
-      <c r="H10" s="3">
-        <v>46301</v>
-      </c>
-      <c r="I10" s="2">
-        <v>100</v>
+      <c r="H10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="J10" s="2">
-        <v>5.8999999999999997E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K10" s="2">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>52</v>
@@ -1948,37 +1948,37 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3">
-        <v>44874</v>
+        <v>45786</v>
       </c>
       <c r="F11" s="3">
-        <v>46669</v>
+        <v>46516</v>
       </c>
       <c r="G11" s="2">
         <v>6</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>64</v>
+      <c r="H11" s="3">
+        <v>46516</v>
+      </c>
+      <c r="I11" s="2">
+        <v>100</v>
       </c>
       <c r="J11" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K11" s="2">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>52</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
@@ -1998,25 +1998,25 @@
         <v>12</v>
       </c>
       <c r="E12" s="3">
-        <v>45786</v>
+        <v>45811</v>
       </c>
       <c r="F12" s="3">
-        <v>46516</v>
+        <v>46176</v>
       </c>
       <c r="G12" s="2">
         <v>6</v>
       </c>
       <c r="H12" s="3">
-        <v>46516</v>
+        <v>46176</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
       </c>
       <c r="J12" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K12" s="2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>52</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
@@ -2036,36 +2036,37 @@
         <v>12</v>
       </c>
       <c r="E13" s="3">
-        <v>45811</v>
+        <v>45891</v>
       </c>
       <c r="F13" s="3">
-        <v>46176</v>
+        <v>46256</v>
       </c>
       <c r="G13" s="2">
         <v>6</v>
       </c>
       <c r="H13" s="3">
-        <v>46176</v>
+        <v>46256</v>
       </c>
       <c r="I13" s="2">
         <v>100</v>
       </c>
       <c r="J13" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K13" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
@@ -2074,72 +2075,71 @@
         <v>12</v>
       </c>
       <c r="E14" s="3">
-        <v>45891</v>
+        <v>45709</v>
       </c>
       <c r="F14" s="3">
-        <v>46256</v>
+        <v>46439</v>
       </c>
       <c r="G14" s="2">
         <v>6</v>
       </c>
       <c r="H14" s="3">
-        <v>46256</v>
+        <v>46439</v>
       </c>
       <c r="I14" s="2">
         <v>100</v>
       </c>
       <c r="J14" s="2">
-        <v>0.06</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K14" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14" s="6"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E15" s="3">
-        <v>45709</v>
+        <v>45163</v>
       </c>
       <c r="F15" s="3">
-        <v>46439</v>
+        <v>46990</v>
       </c>
       <c r="G15" s="2">
         <v>6</v>
       </c>
-      <c r="H15" s="3">
-        <v>46439</v>
-      </c>
-      <c r="I15" s="2">
-        <v>100</v>
+      <c r="H15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="J15" s="2">
-        <v>7.9500000000000001E-2</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="K15" s="2">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>87</v>
@@ -2148,28 +2148,28 @@
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3">
-        <v>45163</v>
+        <v>45411</v>
       </c>
       <c r="F16" s="3">
-        <v>46990</v>
+        <v>46202</v>
       </c>
       <c r="G16" s="2">
-        <v>6</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>89</v>
+        <v>3</v>
+      </c>
+      <c r="H16" s="4">
+        <v>46202</v>
+      </c>
+      <c r="I16" s="2">
+        <v>100</v>
       </c>
       <c r="J16" s="2">
-        <v>9.2499999999999999E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="K16" s="2">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>54</v>
@@ -2177,34 +2177,34 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="3">
-        <v>45411</v>
+        <v>45183</v>
       </c>
       <c r="F17" s="3">
-        <v>46202</v>
+        <v>46095</v>
       </c>
       <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="H17" s="4">
-        <v>46202</v>
+        <v>6</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46095</v>
       </c>
       <c r="I17" s="2">
         <v>100</v>
       </c>
       <c r="J17" s="2">
-        <v>5.9499999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K17" s="2">
         <v>47</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
@@ -2227,25 +2227,25 @@
         <v>12</v>
       </c>
       <c r="E18" s="3">
-        <v>45183</v>
+        <v>45894</v>
       </c>
       <c r="F18" s="3">
-        <v>46095</v>
+        <v>47355</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" s="3">
-        <v>46095</v>
+        <v>47355</v>
       </c>
       <c r="I18" s="2">
         <v>100</v>
       </c>
       <c r="J18" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K18" s="2">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>54</v>
@@ -2253,28 +2253,28 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E19" s="3">
-        <v>45894</v>
+        <v>44750</v>
       </c>
       <c r="F19" s="3">
-        <v>47355</v>
+        <v>46084</v>
       </c>
       <c r="G19" s="2">
         <v>6</v>
       </c>
       <c r="H19" s="3">
-        <v>47355</v>
+        <v>46084</v>
       </c>
       <c r="I19" s="2">
         <v>100</v>
@@ -2283,45 +2283,45 @@
         <v>0.08</v>
       </c>
       <c r="K19" s="2">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E20" s="3">
-        <v>44750</v>
+        <v>45308</v>
       </c>
       <c r="F20" s="3">
-        <v>46084</v>
+        <v>46404</v>
       </c>
       <c r="G20" s="2">
         <v>6</v>
       </c>
       <c r="H20" s="3">
-        <v>46084</v>
+        <v>46404</v>
       </c>
       <c r="I20" s="2">
         <v>100</v>
       </c>
       <c r="J20" s="2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="K20" s="2">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>52</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2341,16 +2341,16 @@
         <v>12</v>
       </c>
       <c r="E21" s="3">
-        <v>45308</v>
+        <v>45404</v>
       </c>
       <c r="F21" s="3">
-        <v>46404</v>
+        <v>46256</v>
       </c>
       <c r="G21" s="2">
         <v>6</v>
       </c>
       <c r="H21" s="3">
-        <v>46404</v>
+        <v>46256</v>
       </c>
       <c r="I21" s="2">
         <v>100</v>
@@ -2359,7 +2359,7 @@
         <v>0.06</v>
       </c>
       <c r="K21" s="2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>52</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2379,25 +2379,25 @@
         <v>12</v>
       </c>
       <c r="E22" s="3">
-        <v>45404</v>
+        <v>45611</v>
       </c>
       <c r="F22" s="3">
-        <v>46256</v>
+        <v>47072</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" s="3">
-        <v>46256</v>
+        <v>47072</v>
       </c>
       <c r="I22" s="2">
         <v>100</v>
       </c>
       <c r="J22" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K22" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>52</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2417,25 +2417,25 @@
         <v>12</v>
       </c>
       <c r="E23" s="3">
-        <v>45611</v>
+        <v>45849</v>
       </c>
       <c r="F23" s="3">
-        <v>47072</v>
+        <v>46945</v>
       </c>
       <c r="G23" s="2">
         <v>6</v>
       </c>
       <c r="H23" s="3">
-        <v>47072</v>
+        <v>46945</v>
       </c>
       <c r="I23" s="2">
         <v>100</v>
       </c>
       <c r="J23" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K23" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>52</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2455,25 +2455,25 @@
         <v>12</v>
       </c>
       <c r="E24" s="3">
-        <v>45849</v>
+        <v>45902</v>
       </c>
       <c r="F24" s="3">
-        <v>46945</v>
+        <v>46632</v>
       </c>
       <c r="G24" s="2">
         <v>6</v>
       </c>
       <c r="H24" s="3">
-        <v>46945</v>
+        <v>46632</v>
       </c>
       <c r="I24" s="2">
         <v>100</v>
       </c>
       <c r="J24" s="2">
-        <v>0.08</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K24" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>52</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2493,16 +2493,16 @@
         <v>12</v>
       </c>
       <c r="E25" s="3">
-        <v>45902</v>
+        <v>46001</v>
       </c>
       <c r="F25" s="3">
-        <v>46632</v>
+        <v>47187</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" s="3">
-        <v>46632</v>
+        <v>47187</v>
       </c>
       <c r="I25" s="2">
         <v>100</v>
@@ -2511,7 +2511,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="K25" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>52</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>121</v>
+        <v>212</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
@@ -2531,33 +2531,33 @@
         <v>12</v>
       </c>
       <c r="E26" s="3">
-        <v>46001</v>
+        <v>45358</v>
       </c>
       <c r="F26" s="3">
-        <v>47187</v>
+        <v>46348</v>
       </c>
       <c r="G26" s="2">
         <v>6</v>
       </c>
       <c r="H26" s="3">
-        <v>47187</v>
+        <v>46348</v>
       </c>
       <c r="I26" s="2">
         <v>100</v>
       </c>
       <c r="J26" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="K26" s="2">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>17</v>
@@ -2569,25 +2569,25 @@
         <v>12</v>
       </c>
       <c r="E27" s="3">
-        <v>45358</v>
+        <v>45509</v>
       </c>
       <c r="F27" s="3">
-        <v>46348</v>
+        <v>46970</v>
       </c>
       <c r="G27" s="2">
         <v>6</v>
       </c>
       <c r="H27" s="3">
-        <v>46348</v>
+        <v>46970</v>
       </c>
       <c r="I27" s="2">
         <v>100</v>
       </c>
       <c r="J27" s="2">
-        <v>9.7500000000000003E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K27" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>55</v>
@@ -2595,37 +2595,37 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E28" s="3">
-        <v>45509</v>
+        <v>45589</v>
       </c>
       <c r="F28" s="3">
-        <v>46970</v>
+        <v>47780</v>
       </c>
       <c r="G28" s="2">
         <v>6</v>
       </c>
-      <c r="H28" s="3">
-        <v>46970</v>
-      </c>
-      <c r="I28" s="2">
-        <v>100</v>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J28" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="K28" s="2">
-        <v>81</v>
+        <v>385</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>55</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>17</v>
@@ -2642,28 +2642,28 @@
         <v>15</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E29" s="3">
-        <v>45589</v>
+        <v>45876</v>
       </c>
       <c r="F29" s="3">
-        <v>47780</v>
+        <v>46241</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>29</v>
+      <c r="H29" s="3">
+        <v>46241</v>
+      </c>
+      <c r="I29" s="2">
+        <v>100</v>
       </c>
       <c r="J29" s="2">
-        <v>9.7500000000000003E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K29" s="2">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>55</v>
@@ -2671,87 +2671,87 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>120</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E30" s="3">
-        <v>45876</v>
+        <v>45575</v>
       </c>
       <c r="F30" s="3">
-        <v>46241</v>
+        <v>47036</v>
       </c>
       <c r="G30" s="2">
         <v>6</v>
       </c>
       <c r="H30" s="3">
-        <v>46241</v>
+        <v>47036</v>
       </c>
       <c r="I30" s="2">
         <v>100</v>
       </c>
       <c r="J30" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="K30" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E31" s="3">
-        <v>45575</v>
+        <v>45883</v>
       </c>
       <c r="F31" s="3">
-        <v>47036</v>
+        <v>46265</v>
       </c>
       <c r="G31" s="2">
         <v>6</v>
       </c>
       <c r="H31" s="3">
-        <v>47036</v>
+        <v>46265</v>
       </c>
       <c r="I31" s="2">
         <v>100</v>
       </c>
       <c r="J31" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K31" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
@@ -2760,33 +2760,33 @@
         <v>12</v>
       </c>
       <c r="E32" s="3">
-        <v>45883</v>
+        <v>45582</v>
       </c>
       <c r="F32" s="3">
-        <v>46265</v>
+        <v>47043</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
       </c>
       <c r="H32" s="3">
-        <v>46265</v>
+        <v>47043</v>
       </c>
       <c r="I32" s="2">
         <v>100</v>
       </c>
       <c r="J32" s="2">
-        <v>6.25E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K32" s="2">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>18</v>
@@ -2798,25 +2798,25 @@
         <v>12</v>
       </c>
       <c r="E33" s="3">
-        <v>45582</v>
+        <v>45721</v>
       </c>
       <c r="F33" s="3">
-        <v>47043</v>
+        <v>46817</v>
       </c>
       <c r="G33" s="2">
         <v>6</v>
       </c>
       <c r="H33" s="3">
-        <v>47043</v>
+        <v>46817</v>
       </c>
       <c r="I33" s="2">
         <v>100</v>
       </c>
       <c r="J33" s="2">
-        <v>0.06</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K33" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>56</v>
@@ -2824,37 +2824,37 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E34" s="3">
-        <v>45721</v>
+        <v>45993</v>
       </c>
       <c r="F34" s="3">
-        <v>46817</v>
+        <v>48915</v>
       </c>
       <c r="G34" s="2">
         <v>6</v>
       </c>
-      <c r="H34" s="3">
-        <v>46817</v>
-      </c>
-      <c r="I34" s="2">
-        <v>100</v>
+      <c r="H34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J34" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="K34" s="2">
-        <v>27</v>
+        <v>400</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>56</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>18</v>
@@ -2874,25 +2874,25 @@
         <v>86</v>
       </c>
       <c r="E35" s="3">
-        <v>45993</v>
+        <v>44441</v>
       </c>
       <c r="F35" s="3">
-        <v>48915</v>
+        <v>46632</v>
       </c>
       <c r="G35" s="2">
         <v>6</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J35" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K35" s="2">
-        <v>400</v>
+        <v>146</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>56</v>
@@ -2900,48 +2900,48 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E36" s="3">
-        <v>44441</v>
+        <v>45846</v>
       </c>
       <c r="F36" s="3">
-        <v>46632</v>
+        <v>46942</v>
       </c>
       <c r="G36" s="2">
         <v>6</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>32</v>
+      <c r="H36" s="3">
+        <v>46942</v>
+      </c>
+      <c r="I36" s="2">
+        <v>100</v>
       </c>
       <c r="J36" s="2">
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="K36" s="2">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
@@ -2950,101 +2950,101 @@
         <v>12</v>
       </c>
       <c r="E37" s="3">
-        <v>45846</v>
+        <v>45891</v>
       </c>
       <c r="F37" s="3">
-        <v>46942</v>
+        <v>46256</v>
       </c>
       <c r="G37" s="2">
         <v>6</v>
       </c>
       <c r="H37" s="3">
-        <v>46942</v>
+        <v>46256</v>
       </c>
       <c r="I37" s="2">
         <v>100</v>
       </c>
       <c r="J37" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K37" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E38" s="3">
-        <v>45891</v>
+        <v>44720</v>
       </c>
       <c r="F38" s="3">
-        <v>46256</v>
+        <v>46926</v>
       </c>
       <c r="G38" s="2">
         <v>6</v>
       </c>
-      <c r="H38" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I38" s="2">
-        <v>100</v>
+      <c r="H38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J38" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K38" s="2">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E39" s="3">
-        <v>44720</v>
+        <v>45350</v>
       </c>
       <c r="F39" s="3">
-        <v>46926</v>
+        <v>46446</v>
       </c>
       <c r="G39" s="2">
         <v>6</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>35</v>
+      <c r="H39" s="3">
+        <v>46446</v>
+      </c>
+      <c r="I39" s="2">
+        <v>100</v>
       </c>
       <c r="J39" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K39" s="2">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>52</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>19</v>
@@ -3064,25 +3064,25 @@
         <v>12</v>
       </c>
       <c r="E40" s="3">
-        <v>45350</v>
+        <v>45453</v>
       </c>
       <c r="F40" s="3">
-        <v>46446</v>
+        <v>46183</v>
       </c>
       <c r="G40" s="2">
         <v>6</v>
       </c>
       <c r="H40" s="3">
-        <v>46446</v>
+        <v>46183</v>
       </c>
       <c r="I40" s="2">
         <v>100</v>
       </c>
       <c r="J40" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K40" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>52</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>19</v>
@@ -3102,25 +3102,25 @@
         <v>12</v>
       </c>
       <c r="E41" s="3">
-        <v>45453</v>
+        <v>45588</v>
       </c>
       <c r="F41" s="3">
-        <v>46183</v>
+        <v>46683</v>
       </c>
       <c r="G41" s="2">
         <v>6</v>
       </c>
       <c r="H41" s="3">
-        <v>46183</v>
+        <v>46683</v>
       </c>
       <c r="I41" s="2">
         <v>100</v>
       </c>
       <c r="J41" s="2">
-        <v>0.06</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K41" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>52</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>19</v>
@@ -3143,22 +3143,22 @@
         <v>45588</v>
       </c>
       <c r="F42" s="3">
-        <v>46683</v>
+        <v>47414</v>
       </c>
       <c r="G42" s="2">
         <v>6</v>
       </c>
       <c r="H42" s="3">
-        <v>46683</v>
+        <v>47414</v>
       </c>
       <c r="I42" s="2">
         <v>100</v>
       </c>
       <c r="J42" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K42" s="2">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>52</v>
@@ -3166,37 +3166,37 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E43" s="3">
-        <v>45588</v>
+        <v>45747</v>
       </c>
       <c r="F43" s="3">
-        <v>47414</v>
+        <v>49399</v>
       </c>
       <c r="G43" s="2">
         <v>6</v>
       </c>
-      <c r="H43" s="3">
-        <v>47414</v>
-      </c>
-      <c r="I43" s="2">
-        <v>100</v>
+      <c r="H43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J43" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K43" s="2">
-        <v>51</v>
+        <v>300</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>52</v>
@@ -3204,45 +3204,45 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E44" s="3">
-        <v>45747</v>
+        <v>45586</v>
       </c>
       <c r="F44" s="3">
-        <v>49399</v>
+        <v>46316</v>
       </c>
       <c r="G44" s="2">
         <v>6</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>29</v>
+      <c r="H44" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I44" s="2">
+        <v>100</v>
       </c>
       <c r="J44" s="2">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="K44" s="2">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>69</v>
@@ -3257,22 +3257,22 @@
         <v>45586</v>
       </c>
       <c r="F45" s="3">
-        <v>46316</v>
+        <v>47047</v>
       </c>
       <c r="G45" s="2">
         <v>6</v>
       </c>
       <c r="H45" s="3">
-        <v>46316</v>
+        <v>47047</v>
       </c>
       <c r="I45" s="2">
         <v>100</v>
       </c>
       <c r="J45" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K45" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>54</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>69</v>
@@ -3292,25 +3292,25 @@
         <v>12</v>
       </c>
       <c r="E46" s="3">
-        <v>45586</v>
+        <v>45674</v>
       </c>
       <c r="F46" s="3">
-        <v>47047</v>
+        <v>46769</v>
       </c>
       <c r="G46" s="2">
         <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>47047</v>
+        <v>46769</v>
       </c>
       <c r="I46" s="2">
         <v>100</v>
       </c>
       <c r="J46" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K46" s="2">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>54</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>69</v>
@@ -3330,25 +3330,25 @@
         <v>12</v>
       </c>
       <c r="E47" s="3">
-        <v>45674</v>
+        <v>45804</v>
       </c>
       <c r="F47" s="3">
-        <v>46769</v>
+        <v>46534</v>
       </c>
       <c r="G47" s="2">
         <v>6</v>
       </c>
       <c r="H47" s="3">
-        <v>46769</v>
+        <v>46534</v>
       </c>
       <c r="I47" s="2">
         <v>100</v>
       </c>
       <c r="J47" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K47" s="2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>54</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>69</v>
@@ -3368,25 +3368,25 @@
         <v>12</v>
       </c>
       <c r="E48" s="3">
-        <v>45804</v>
+        <v>45863</v>
       </c>
       <c r="F48" s="3">
-        <v>46534</v>
+        <v>46593</v>
       </c>
       <c r="G48" s="2">
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>46534</v>
+        <v>46593</v>
       </c>
       <c r="I48" s="2">
         <v>100</v>
       </c>
       <c r="J48" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K48" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>54</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
@@ -3406,33 +3406,33 @@
         <v>12</v>
       </c>
       <c r="E49" s="3">
-        <v>45863</v>
+        <v>45180</v>
       </c>
       <c r="F49" s="3">
-        <v>46593</v>
+        <v>46092</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>46593</v>
+        <v>46092</v>
       </c>
       <c r="I49" s="2">
         <v>100</v>
       </c>
       <c r="J49" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K49" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>20</v>
@@ -3444,25 +3444,25 @@
         <v>12</v>
       </c>
       <c r="E50" s="3">
-        <v>45180</v>
+        <v>45862</v>
       </c>
       <c r="F50" s="3">
-        <v>46092</v>
+        <v>46592</v>
       </c>
       <c r="G50" s="2">
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>46092</v>
+        <v>46592</v>
       </c>
       <c r="I50" s="2">
         <v>100</v>
       </c>
       <c r="J50" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K50" s="2">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>52</v>
@@ -3470,28 +3470,28 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E51" s="3">
-        <v>45862</v>
+        <v>45831</v>
       </c>
       <c r="F51" s="3">
-        <v>46592</v>
+        <v>47292</v>
       </c>
       <c r="G51" s="2">
         <v>6</v>
       </c>
       <c r="H51" s="3">
-        <v>46592</v>
+        <v>47292</v>
       </c>
       <c r="I51" s="2">
         <v>100</v>
@@ -3500,15 +3500,15 @@
         <v>0.08</v>
       </c>
       <c r="K51" s="2">
-        <v>112</v>
+        <v>530</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>66</v>
@@ -3520,16 +3520,16 @@
         <v>86</v>
       </c>
       <c r="E52" s="3">
-        <v>45831</v>
+        <v>46050</v>
       </c>
       <c r="F52" s="3">
-        <v>47292</v>
+        <v>47876</v>
       </c>
       <c r="G52" s="2">
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>47292</v>
+        <v>47876</v>
       </c>
       <c r="I52" s="2">
         <v>100</v>
@@ -3538,7 +3538,7 @@
         <v>0.08</v>
       </c>
       <c r="K52" s="2">
-        <v>530</v>
+        <v>400</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>56</v>
@@ -3546,45 +3546,45 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E53" s="3">
-        <v>46050</v>
+        <v>45124</v>
       </c>
       <c r="F53" s="3">
-        <v>47876</v>
+        <v>46220</v>
       </c>
       <c r="G53" s="2">
         <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>47876</v>
+        <v>46220</v>
       </c>
       <c r="I53" s="2">
         <v>100</v>
       </c>
       <c r="J53" s="2">
-        <v>0.08</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K53" s="2">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>70</v>
@@ -3596,25 +3596,25 @@
         <v>12</v>
       </c>
       <c r="E54" s="3">
-        <v>45124</v>
+        <v>45496</v>
       </c>
       <c r="F54" s="3">
-        <v>46220</v>
+        <v>46591</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
       </c>
       <c r="H54" s="3">
-        <v>46220</v>
+        <v>46591</v>
       </c>
       <c r="I54" s="2">
         <v>100</v>
       </c>
       <c r="J54" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K54" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>53</v>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
@@ -3634,25 +3634,25 @@
         <v>12</v>
       </c>
       <c r="E55" s="3">
-        <v>45496</v>
+        <v>45363</v>
       </c>
       <c r="F55" s="3">
-        <v>46591</v>
+        <v>46093</v>
       </c>
       <c r="G55" s="2">
         <v>6</v>
       </c>
       <c r="H55" s="3">
-        <v>46591</v>
+        <v>46093</v>
       </c>
       <c r="I55" s="2">
         <v>100</v>
       </c>
       <c r="J55" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K55" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>53</v>
@@ -3660,37 +3660,37 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E56" s="3">
-        <v>45363</v>
+        <v>45631</v>
       </c>
       <c r="F56" s="3">
-        <v>46093</v>
+        <v>47822</v>
       </c>
       <c r="G56" s="2">
         <v>6</v>
       </c>
-      <c r="H56" s="3">
-        <v>46093</v>
-      </c>
-      <c r="I56" s="2">
-        <v>100</v>
+      <c r="H56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="J56" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="K56" s="2">
-        <v>13</v>
+        <v>400</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>53</v>
@@ -3698,48 +3698,48 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E57" s="3">
-        <v>45631</v>
+        <v>45820</v>
       </c>
       <c r="F57" s="3">
-        <v>47822</v>
+        <v>46916</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>77</v>
+      <c r="H57" s="3">
+        <v>46916</v>
+      </c>
+      <c r="I57" s="2">
+        <v>100</v>
       </c>
       <c r="J57" s="2">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="K57" s="2">
-        <v>400</v>
+        <v>7.8899999999999998E-2</v>
+      </c>
+      <c r="K57" s="5">
+        <v>85</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
@@ -3748,25 +3748,25 @@
         <v>12</v>
       </c>
       <c r="E58" s="3">
-        <v>45820</v>
+        <v>45996</v>
       </c>
       <c r="F58" s="3">
-        <v>46916</v>
+        <v>47274</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
       </c>
       <c r="H58" s="3">
-        <v>46916</v>
+        <v>47274</v>
       </c>
       <c r="I58" s="2">
         <v>100</v>
       </c>
       <c r="J58" s="2">
-        <v>7.8899999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K58" s="5">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>52</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
@@ -3786,25 +3786,25 @@
         <v>12</v>
       </c>
       <c r="E59" s="3">
-        <v>45996</v>
+        <v>45562</v>
       </c>
       <c r="F59" s="3">
-        <v>47274</v>
+        <v>46657</v>
       </c>
       <c r="G59" s="2">
         <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>47274</v>
+        <v>46657</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
       </c>
       <c r="J59" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K59" s="5">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>52</v>
@@ -3812,7 +3812,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
@@ -3827,22 +3827,22 @@
         <v>45562</v>
       </c>
       <c r="F60" s="3">
-        <v>46657</v>
+        <v>47388</v>
       </c>
       <c r="G60" s="2">
         <v>6</v>
       </c>
       <c r="H60" s="3">
-        <v>46657</v>
+        <v>47388</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
       </c>
       <c r="J60" s="2">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K60" s="5">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>52</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
@@ -3862,25 +3862,25 @@
         <v>12</v>
       </c>
       <c r="E61" s="3">
-        <v>45562</v>
+        <v>45609</v>
       </c>
       <c r="F61" s="3">
-        <v>47388</v>
+        <v>48165</v>
       </c>
       <c r="G61" s="2">
         <v>6</v>
       </c>
       <c r="H61" s="3">
-        <v>47388</v>
+        <v>48165</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
       </c>
       <c r="J61" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K61" s="5">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>52</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
@@ -3903,22 +3903,22 @@
         <v>45609</v>
       </c>
       <c r="F62" s="3">
-        <v>48165</v>
+        <v>47070</v>
       </c>
       <c r="G62" s="2">
         <v>6</v>
       </c>
       <c r="H62" s="3">
-        <v>48165</v>
+        <v>47070</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
       </c>
       <c r="J62" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K62" s="5">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>52</v>
@@ -3926,37 +3926,37 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="3">
-        <v>45609</v>
+        <v>45699</v>
       </c>
       <c r="F63" s="3">
-        <v>47070</v>
+        <v>46610</v>
       </c>
       <c r="G63" s="2">
         <v>6</v>
       </c>
       <c r="H63" s="3">
-        <v>47070</v>
+        <v>46610</v>
       </c>
       <c r="I63" s="2">
         <v>100</v>
       </c>
       <c r="J63" s="2">
-        <v>6.25E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K63" s="5">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>52</v>
@@ -3964,37 +3964,37 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="3">
-        <v>45699</v>
+        <v>45896</v>
       </c>
       <c r="F64" s="3">
-        <v>46610</v>
+        <v>47357</v>
       </c>
       <c r="G64" s="2">
         <v>6</v>
       </c>
       <c r="H64" s="3">
-        <v>46610</v>
+        <v>47357</v>
       </c>
       <c r="I64" s="2">
         <v>100</v>
       </c>
       <c r="J64" s="2">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="K64" s="5">
-        <v>120</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K64" s="2">
+        <v>85</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>52</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>21</v>
@@ -4014,25 +4014,25 @@
         <v>12</v>
       </c>
       <c r="E65" s="3">
-        <v>45896</v>
+        <v>45947</v>
       </c>
       <c r="F65" s="3">
-        <v>47357</v>
+        <v>46494</v>
       </c>
       <c r="G65" s="2">
         <v>6</v>
       </c>
       <c r="H65" s="3">
-        <v>47357</v>
+        <v>46494</v>
       </c>
       <c r="I65" s="2">
         <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K65" s="2">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>52</v>
@@ -4040,37 +4040,37 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E66" s="3">
-        <v>45947</v>
+        <v>46037</v>
       </c>
       <c r="F66" s="3">
-        <v>46494</v>
+        <v>50055</v>
       </c>
       <c r="G66" s="2">
         <v>6</v>
       </c>
-      <c r="H66" s="3">
-        <v>46494</v>
-      </c>
-      <c r="I66" s="2">
-        <v>100</v>
+      <c r="H66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J66" s="2">
-        <v>0.06</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="K66" s="2">
-        <v>56</v>
+        <v>375</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>52</v>
@@ -4078,37 +4078,37 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E67" s="3">
-        <v>46037</v>
+        <v>44316</v>
       </c>
       <c r="F67" s="3">
-        <v>50055</v>
+        <v>46507</v>
       </c>
       <c r="G67" s="2">
         <v>6</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J67" s="2">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="K67" s="2">
-        <v>375</v>
+        <v>9.1249999999999998E-2</v>
+      </c>
+      <c r="K67" s="5">
+        <v>180</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>52</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>21</v>
@@ -4128,25 +4128,25 @@
         <v>12</v>
       </c>
       <c r="E68" s="3">
-        <v>44316</v>
+        <v>45412</v>
       </c>
       <c r="F68" s="3">
-        <v>46507</v>
+        <v>48334</v>
       </c>
       <c r="G68" s="2">
         <v>6</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J68" s="2">
-        <v>9.1249999999999998E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K68" s="5">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>52</v>
@@ -4154,37 +4154,37 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E69" s="3">
-        <v>45412</v>
+        <v>44903</v>
       </c>
       <c r="F69" s="3">
-        <v>48334</v>
+        <v>46364</v>
       </c>
       <c r="G69" s="2">
         <v>6</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J69" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K69" s="5">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>52</v>
@@ -4192,37 +4192,37 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E70" s="3">
-        <v>44903</v>
+        <v>45545</v>
       </c>
       <c r="F70" s="3">
-        <v>46364</v>
+        <v>48101</v>
       </c>
       <c r="G70" s="2">
         <v>6</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>29</v>
+      <c r="H70" s="3">
+        <v>48101</v>
+      </c>
+      <c r="I70" s="2">
+        <v>100</v>
       </c>
       <c r="J70" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K70" s="5">
-        <v>196</v>
+        <v>410</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>52</v>
@@ -4230,37 +4230,37 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E71" s="3">
-        <v>45545</v>
+        <v>45569</v>
       </c>
       <c r="F71" s="3">
-        <v>48101</v>
+        <v>47030</v>
       </c>
       <c r="G71" s="2">
         <v>6</v>
       </c>
       <c r="H71" s="3">
-        <v>48101</v>
+        <v>47030</v>
       </c>
       <c r="I71" s="2">
         <v>100</v>
       </c>
       <c r="J71" s="2">
-        <v>7.9500000000000001E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K71" s="5">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>52</v>
@@ -4268,37 +4268,37 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E72" s="3">
-        <v>45569</v>
+        <v>45642</v>
       </c>
       <c r="F72" s="3">
-        <v>47030</v>
+        <v>49294</v>
       </c>
       <c r="G72" s="2">
         <v>6</v>
       </c>
       <c r="H72" s="3">
-        <v>47030</v>
+        <v>49294</v>
       </c>
       <c r="I72" s="2">
         <v>100</v>
       </c>
       <c r="J72" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K72" s="5">
-        <v>83</v>
+        <v>700</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>52</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>22</v>
@@ -4318,25 +4318,25 @@
         <v>86</v>
       </c>
       <c r="E73" s="3">
-        <v>45642</v>
+        <v>45875</v>
       </c>
       <c r="F73" s="3">
-        <v>49294</v>
+        <v>46971</v>
       </c>
       <c r="G73" s="2">
         <v>6</v>
       </c>
       <c r="H73" s="3">
-        <v>49294</v>
+        <v>46971</v>
       </c>
       <c r="I73" s="2">
         <v>100</v>
       </c>
       <c r="J73" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K73" s="5">
-        <v>700</v>
+        <v>83</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>52</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>22</v>
@@ -4356,25 +4356,25 @@
         <v>86</v>
       </c>
       <c r="E74" s="3">
-        <v>45875</v>
+        <v>45975</v>
       </c>
       <c r="F74" s="3">
-        <v>46971</v>
+        <v>50358</v>
       </c>
       <c r="G74" s="2">
         <v>6</v>
       </c>
       <c r="H74" s="3">
-        <v>46971</v>
+        <v>50358</v>
       </c>
       <c r="I74" s="2">
         <v>100</v>
       </c>
       <c r="J74" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K74" s="5">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>52</v>
@@ -4382,37 +4382,37 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E75" s="3">
-        <v>45975</v>
+        <v>46113</v>
       </c>
       <c r="F75" s="3">
-        <v>50358</v>
+        <v>47209</v>
       </c>
       <c r="G75" s="2">
         <v>6</v>
       </c>
       <c r="H75" s="3">
-        <v>50358</v>
+        <v>47209</v>
       </c>
       <c r="I75" s="2">
         <v>100</v>
       </c>
       <c r="J75" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K75" s="5">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>52</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
@@ -4432,33 +4432,34 @@
         <v>12</v>
       </c>
       <c r="E76" s="3">
-        <v>46113</v>
+        <v>45587</v>
       </c>
       <c r="F76" s="3">
-        <v>47209</v>
+        <v>47048</v>
       </c>
       <c r="G76" s="2">
         <v>6</v>
       </c>
       <c r="H76" s="3">
-        <v>47209</v>
+        <f>F76</f>
+        <v>47048</v>
       </c>
       <c r="I76" s="2">
         <v>100</v>
       </c>
       <c r="J76" s="2">
-        <v>5.5E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K76" s="5">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>91</v>
@@ -4470,26 +4471,26 @@
         <v>12</v>
       </c>
       <c r="E77" s="3">
-        <v>45587</v>
+        <v>45705</v>
       </c>
       <c r="F77" s="3">
-        <v>47048</v>
+        <v>47896</v>
       </c>
       <c r="G77" s="2">
         <v>6</v>
       </c>
       <c r="H77" s="3">
         <f>F77</f>
-        <v>47048</v>
+        <v>47896</v>
       </c>
       <c r="I77" s="2">
         <v>100</v>
       </c>
       <c r="J77" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K77" s="5">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>54</v>
@@ -4497,7 +4498,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>91</v>
@@ -4509,26 +4510,26 @@
         <v>12</v>
       </c>
       <c r="E78" s="3">
-        <v>45705</v>
+        <v>45859</v>
       </c>
       <c r="F78" s="3">
-        <v>47896</v>
+        <v>46955</v>
       </c>
       <c r="G78" s="2">
         <v>6</v>
       </c>
       <c r="H78" s="3">
         <f>F78</f>
-        <v>47896</v>
+        <v>46955</v>
       </c>
       <c r="I78" s="2">
         <v>100</v>
       </c>
       <c r="J78" s="2">
-        <v>0.08</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K78" s="5">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>54</v>
@@ -4536,29 +4537,28 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E79" s="3">
-        <v>45859</v>
+        <v>45838</v>
       </c>
       <c r="F79" s="3">
-        <v>46955</v>
+        <v>48364</v>
       </c>
       <c r="G79" s="2">
         <v>6</v>
       </c>
       <c r="H79" s="3">
-        <f>F79</f>
-        <v>46955</v>
+        <v>48364</v>
       </c>
       <c r="I79" s="2">
         <v>100</v>
@@ -4567,45 +4567,45 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="K79" s="5">
-        <v>38</v>
+        <v>650</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E80" s="3">
-        <v>45838</v>
+        <v>46080</v>
       </c>
       <c r="F80" s="3">
-        <v>48364</v>
+        <v>47176</v>
       </c>
       <c r="G80" s="2">
         <v>6</v>
       </c>
       <c r="H80" s="3">
-        <v>48364</v>
+        <v>47176</v>
       </c>
       <c r="I80" s="2">
         <v>100</v>
       </c>
       <c r="J80" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K80" s="5">
-        <v>650</v>
+        <v>167</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>52</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>67</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>75</v>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>23</v>
@@ -4727,7 +4727,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
@@ -4765,7 +4765,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>23</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>23</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>23</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>23</v>
@@ -4918,13 +4918,13 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>86</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>24</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>24</v>
@@ -5032,7 +5032,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>24</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
@@ -5129,7 +5129,7 @@
         <v>6</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>73</v>
@@ -5146,45 +5146,45 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E95" s="3">
-        <v>45497</v>
+        <v>46117</v>
       </c>
       <c r="F95" s="3">
-        <v>48053</v>
+        <v>47213</v>
       </c>
       <c r="G95" s="2">
         <v>6</v>
       </c>
       <c r="H95" s="3">
-        <v>48053</v>
+        <v>47213</v>
       </c>
       <c r="I95" s="2">
         <v>100</v>
       </c>
       <c r="J95" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K95" s="5">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>25</v>
@@ -5196,25 +5196,25 @@
         <v>86</v>
       </c>
       <c r="E96" s="3">
-        <v>45981</v>
+        <v>45497</v>
       </c>
       <c r="F96" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="G96" s="2">
         <v>6</v>
       </c>
       <c r="H96" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="I96" s="2">
         <v>100</v>
       </c>
       <c r="J96" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K96" s="5">
-        <v>1030</v>
+        <v>490</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>53</v>
@@ -5222,45 +5222,45 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E97" s="3">
-        <v>45415</v>
+        <v>45981</v>
       </c>
       <c r="F97" s="3">
-        <v>47241</v>
+        <v>49633</v>
       </c>
       <c r="G97" s="2">
         <v>6</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>43</v>
+      <c r="H97" s="3">
+        <v>49633</v>
+      </c>
+      <c r="I97" s="2">
+        <v>100</v>
       </c>
       <c r="J97" s="2">
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K97" s="5">
-        <v>46</v>
+        <v>1030</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>26</v>
@@ -5272,25 +5272,25 @@
         <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>45575</v>
+        <v>45415</v>
       </c>
       <c r="F98" s="3">
-        <v>48131</v>
+        <v>47241</v>
       </c>
       <c r="G98" s="2">
         <v>6</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J98" s="2">
-        <v>7.6499999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K98" s="5">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>52</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>26</v>
@@ -5307,28 +5307,28 @@
         <v>15</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E99" s="3">
-        <v>45636</v>
+        <v>45575</v>
       </c>
       <c r="F99" s="3">
-        <v>49653</v>
+        <v>48131</v>
       </c>
       <c r="G99" s="2">
         <v>6</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J99" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K99" s="5">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>52</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>26</v>
@@ -5345,28 +5345,28 @@
         <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E100" s="3">
-        <v>45723</v>
+        <v>45636</v>
       </c>
       <c r="F100" s="3">
-        <v>47549</v>
+        <v>49653</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
       </c>
-      <c r="H100" s="3">
-        <v>47549</v>
-      </c>
-      <c r="I100" s="2">
-        <v>100</v>
+      <c r="H100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J100" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K100" s="5">
-        <v>92</v>
+        <v>600</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>52</v>
@@ -5374,7 +5374,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>26</v>
@@ -5383,19 +5383,19 @@
         <v>15</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E101" s="3">
-        <v>45818</v>
+        <v>45723</v>
       </c>
       <c r="F101" s="3">
-        <v>48740</v>
+        <v>47549</v>
       </c>
       <c r="G101" s="2">
         <v>6</v>
       </c>
       <c r="H101" s="3">
-        <v>48740</v>
+        <v>47549</v>
       </c>
       <c r="I101" s="2">
         <v>100</v>
@@ -5404,7 +5404,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K101" s="5">
-        <v>900</v>
+        <v>92</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>52</v>
@@ -5412,37 +5412,37 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E102" s="3">
-        <v>45945</v>
+        <v>45818</v>
       </c>
       <c r="F102" s="3">
-        <v>46492</v>
+        <v>48740</v>
       </c>
       <c r="G102" s="2">
         <v>6</v>
       </c>
       <c r="H102" s="3">
-        <v>46492</v>
+        <v>48740</v>
       </c>
       <c r="I102" s="2">
         <v>100</v>
       </c>
       <c r="J102" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K102" s="5">
-        <v>73</v>
+        <v>900</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>52</v>
@@ -5450,37 +5450,37 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E103" s="3">
-        <v>46120</v>
+        <v>45945</v>
       </c>
       <c r="F103" s="3">
-        <v>50503</v>
+        <v>46492</v>
       </c>
       <c r="G103" s="2">
         <v>6</v>
       </c>
-      <c r="H103" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>29</v>
+      <c r="H103" s="3">
+        <v>46492</v>
+      </c>
+      <c r="I103" s="2">
+        <v>100</v>
       </c>
       <c r="J103" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K103" s="5">
-        <v>500</v>
+        <v>73</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>52</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>15</v>
@@ -5500,25 +5500,25 @@
         <v>86</v>
       </c>
       <c r="E104" s="3">
-        <v>45674</v>
+        <v>46120</v>
       </c>
       <c r="F104" s="3">
-        <v>48961</v>
+        <v>50503</v>
       </c>
       <c r="G104" s="2">
         <v>6</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J104" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K104" s="5">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>52</v>
@@ -5526,37 +5526,37 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E105" s="3">
-        <v>45715</v>
+        <v>45674</v>
       </c>
       <c r="F105" s="3">
-        <v>46445</v>
+        <v>48961</v>
       </c>
       <c r="G105" s="2">
         <v>6</v>
       </c>
-      <c r="H105" s="3">
-        <v>46445</v>
-      </c>
-      <c r="I105" s="2">
-        <v>100</v>
+      <c r="H105" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J105" s="2">
-        <v>6.25E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K105" s="5">
-        <v>139</v>
+        <v>1100</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>52</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>27</v>
@@ -5576,22 +5576,22 @@
         <v>12</v>
       </c>
       <c r="E106" s="3">
-        <v>45784</v>
+        <v>45715</v>
       </c>
       <c r="F106" s="3">
-        <v>46514</v>
+        <v>46445</v>
       </c>
       <c r="G106" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H106" s="3">
-        <v>46514</v>
+        <v>46445</v>
       </c>
       <c r="I106" s="2">
         <v>100</v>
       </c>
       <c r="J106" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K106" s="5">
         <v>139</v>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>27</v>
@@ -5614,25 +5614,25 @@
         <v>12</v>
       </c>
       <c r="E107" s="3">
-        <v>45860</v>
+        <v>45784</v>
       </c>
       <c r="F107" s="3">
-        <v>46590</v>
+        <v>46514</v>
       </c>
       <c r="G107" s="2">
         <v>3</v>
       </c>
       <c r="H107" s="3">
-        <v>46590</v>
+        <v>46514</v>
       </c>
       <c r="I107" s="2">
         <v>100</v>
       </c>
       <c r="J107" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K107" s="5">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -5640,13 +5640,13 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>12</v>
@@ -5655,22 +5655,22 @@
         <v>45860</v>
       </c>
       <c r="F108" s="3">
-        <v>47686</v>
+        <v>46590</v>
       </c>
       <c r="G108" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3">
-        <v>47686</v>
+        <v>46590</v>
       </c>
       <c r="I108" s="2">
         <v>100</v>
       </c>
       <c r="J108" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K108" s="5">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>52</v>
@@ -5678,37 +5678,37 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E109" s="3">
-        <v>45938</v>
+        <v>45860</v>
       </c>
       <c r="F109" s="3">
-        <v>46454</v>
+        <v>47686</v>
       </c>
       <c r="G109" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H109" s="3">
-        <v>46454</v>
+        <v>47686</v>
       </c>
       <c r="I109" s="2">
         <v>100</v>
       </c>
       <c r="J109" s="2">
-        <v>0.06</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K109" s="5">
-        <v>1000</v>
+        <v>224</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>52</v>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>27</v>
@@ -5728,25 +5728,25 @@
         <v>12</v>
       </c>
       <c r="E110" s="3">
-        <v>45993</v>
+        <v>45938</v>
       </c>
       <c r="F110" s="3">
-        <v>47179</v>
+        <v>46454</v>
       </c>
       <c r="G110" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H110" s="3">
-        <v>47179</v>
+        <v>46454</v>
       </c>
       <c r="I110" s="2">
         <v>100</v>
       </c>
       <c r="J110" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K110" s="5">
-        <v>194</v>
+        <v>1000</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>52</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>27</v>
@@ -5763,28 +5763,28 @@
         <v>11</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E111" s="3">
-        <v>44239</v>
+        <v>45993</v>
       </c>
       <c r="F111" s="3">
-        <v>47299</v>
+        <v>47179</v>
       </c>
       <c r="G111" s="2">
         <v>6</v>
       </c>
-      <c r="H111" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>47</v>
+      <c r="H111" s="3">
+        <v>47179</v>
+      </c>
+      <c r="I111" s="2">
+        <v>100</v>
       </c>
       <c r="J111" s="2">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K111" s="5">
-        <v>747</v>
+        <v>194</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>52</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -5804,25 +5804,25 @@
         <v>86</v>
       </c>
       <c r="E112" s="3">
-        <v>45199</v>
+        <v>44239</v>
       </c>
       <c r="F112" s="3">
-        <v>48852</v>
+        <v>47299</v>
       </c>
       <c r="G112" s="2">
         <v>6</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J112" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="K112" s="5">
-        <v>575</v>
+        <v>747</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>52</v>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>27</v>
@@ -5839,28 +5839,28 @@
         <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E113" s="3">
-        <v>45090</v>
+        <v>45199</v>
       </c>
       <c r="F113" s="3">
-        <v>46066</v>
+        <v>48852</v>
       </c>
       <c r="G113" s="2">
         <v>6</v>
       </c>
-      <c r="H113" s="3">
-        <v>46066</v>
-      </c>
-      <c r="I113" s="2">
-        <v>100</v>
+      <c r="H113" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J113" s="2">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K113" s="5">
-        <v>263</v>
+        <v>575</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>52</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>27</v>
@@ -5880,25 +5880,25 @@
         <v>12</v>
       </c>
       <c r="E114" s="3">
-        <v>45624</v>
+        <v>45090</v>
       </c>
       <c r="F114" s="3">
-        <v>46170</v>
+        <v>46066</v>
       </c>
       <c r="G114" s="2">
         <v>6</v>
       </c>
       <c r="H114" s="3">
-        <v>46170</v>
+        <v>46066</v>
       </c>
       <c r="I114" s="2">
         <v>100</v>
       </c>
       <c r="J114" s="2">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K114" s="5">
-        <v>177</v>
+        <v>263</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>52</v>
@@ -5906,37 +5906,37 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E115" s="3">
-        <v>45546</v>
+        <v>45624</v>
       </c>
       <c r="F115" s="3">
-        <v>48102</v>
+        <v>46170</v>
       </c>
       <c r="G115" s="2">
         <v>6</v>
       </c>
-      <c r="H115" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>29</v>
+      <c r="H115" s="3">
+        <v>46170</v>
+      </c>
+      <c r="I115" s="2">
+        <v>100</v>
       </c>
       <c r="J115" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K115" s="5">
-        <v>1000</v>
+        <v>177</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>52</v>
@@ -5944,37 +5944,37 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E116" s="3">
-        <v>45575</v>
+        <v>45546</v>
       </c>
       <c r="F116" s="3">
-        <v>47036</v>
+        <v>48102</v>
       </c>
       <c r="G116" s="2">
         <v>6</v>
       </c>
-      <c r="H116" s="3">
-        <v>47036</v>
-      </c>
-      <c r="I116" s="2">
-        <v>100</v>
+      <c r="H116" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J116" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K116" s="5">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>52</v>
@@ -5982,16 +5982,16 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E117" s="3">
         <v>45575</v>
@@ -6009,10 +6009,10 @@
         <v>100</v>
       </c>
       <c r="J117" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K117" s="5">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>52</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>15</v>
@@ -6032,25 +6032,25 @@
         <v>86</v>
       </c>
       <c r="E118" s="3">
-        <v>43671</v>
+        <v>45575</v>
       </c>
       <c r="F118" s="3">
-        <v>46228</v>
+        <v>47036</v>
       </c>
       <c r="G118" s="2">
         <v>6</v>
       </c>
       <c r="H118" s="3">
-        <v>46228</v>
+        <v>47036</v>
       </c>
       <c r="I118" s="2">
         <v>100</v>
       </c>
       <c r="J118" s="2">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K118" s="5">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>52</v>
@@ -6058,37 +6058,37 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E119" s="3">
-        <v>45349</v>
+        <v>43671</v>
       </c>
       <c r="F119" s="3">
-        <v>46445</v>
+        <v>46228</v>
       </c>
       <c r="G119" s="2">
         <v>6</v>
       </c>
       <c r="H119" s="3">
-        <v>46445</v>
+        <v>46228</v>
       </c>
       <c r="I119" s="2">
         <v>100</v>
       </c>
       <c r="J119" s="2">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K119" s="5">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>52</v>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>71</v>
@@ -6108,25 +6108,25 @@
         <v>12</v>
       </c>
       <c r="E120" s="3">
-        <v>45456</v>
+        <v>45349</v>
       </c>
       <c r="F120" s="3">
-        <v>46551</v>
+        <v>46445</v>
       </c>
       <c r="G120" s="2">
-        <v>3</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>73</v>
+        <v>6</v>
+      </c>
+      <c r="H120" s="3">
+        <v>46445</v>
+      </c>
+      <c r="I120" s="2">
+        <v>100</v>
       </c>
       <c r="J120" s="2">
         <v>0.06</v>
       </c>
       <c r="K120" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>52</v>
@@ -6134,37 +6134,37 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E121" s="3">
-        <v>45581</v>
+        <v>45456</v>
       </c>
       <c r="F121" s="3">
-        <v>48503</v>
+        <v>46551</v>
       </c>
       <c r="G121" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J121" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K121" s="5">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>52</v>
@@ -6172,37 +6172,37 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E122" s="3">
-        <v>45618</v>
+        <v>45581</v>
       </c>
       <c r="F122" s="3">
-        <v>46348</v>
+        <v>48503</v>
       </c>
       <c r="G122" s="2">
         <v>6</v>
       </c>
-      <c r="H122" s="3">
-        <v>46348</v>
-      </c>
-      <c r="I122" s="2">
-        <v>100</v>
+      <c r="H122" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J122" s="2">
-        <v>5.2499999999999998E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K122" s="5">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>52</v>
@@ -6210,7 +6210,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>71</v>
@@ -6225,22 +6225,22 @@
         <v>45618</v>
       </c>
       <c r="F123" s="3">
-        <v>47079</v>
+        <v>46348</v>
       </c>
       <c r="G123" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H123" s="3">
-        <v>47079</v>
+        <v>46348</v>
       </c>
       <c r="I123" s="2">
         <v>100</v>
       </c>
       <c r="J123" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="K123" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>52</v>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>71</v>
@@ -6260,25 +6260,25 @@
         <v>12</v>
       </c>
       <c r="E124" s="3">
-        <v>45797</v>
+        <v>45618</v>
       </c>
       <c r="F124" s="3">
-        <v>46527</v>
+        <v>47079</v>
       </c>
       <c r="G124" s="2">
         <v>3</v>
       </c>
       <c r="H124" s="3">
-        <v>46527</v>
+        <v>47079</v>
       </c>
       <c r="I124" s="2">
         <v>100</v>
       </c>
       <c r="J124" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K124" s="5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>52</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>71</v>
@@ -6298,37 +6298,75 @@
         <v>12</v>
       </c>
       <c r="E125" s="3">
-        <v>46006</v>
+        <v>45797</v>
       </c>
       <c r="F125" s="3">
-        <v>47102</v>
+        <v>46527</v>
       </c>
       <c r="G125" s="2">
         <v>3</v>
       </c>
       <c r="H125" s="3">
+        <v>46527</v>
+      </c>
+      <c r="I125" s="2">
+        <v>100</v>
+      </c>
+      <c r="J125" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K125" s="5">
+        <v>53</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="3">
+        <v>46006</v>
+      </c>
+      <c r="F126" s="3">
         <v>47102</v>
       </c>
-      <c r="I125" s="2">
-        <v>100</v>
-      </c>
-      <c r="J125" s="2">
+      <c r="G126" s="2">
+        <v>3</v>
+      </c>
+      <c r="H126" s="3">
+        <v>47102</v>
+      </c>
+      <c r="I126" s="2">
+        <v>100</v>
+      </c>
+      <c r="J126" s="2">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="K125" s="5">
+      <c r="K126" s="5">
         <v>45</v>
       </c>
-      <c r="L125" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H130" s="6"/>
+      <c r="L126" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H131" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L125" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L125">
-      <sortCondition ref="B1:B125"/>
+  <autoFilter ref="A1:L126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L126">
+      <sortCondition ref="B1:B126"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Documents\datos_financieros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE29E89F-562C-4878-9F8D-BEA7B920F7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37FAE4A-C97F-400E-8798-B40A5AFD0270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Documents\datos_financieros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37FAE4A-C97F-400E-8798-B40A5AFD0270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A3E73B-6366-4809-B9BF-EC98041E15CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="listado_ons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$125</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="221">
   <si>
     <t>name</t>
   </si>
@@ -1548,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
@@ -1763,7 +1763,7 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -2982,7 +2982,7 @@
         <v>19</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>86</v>
@@ -3564,7 +3564,7 @@
         <v>46220</v>
       </c>
       <c r="G53" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H53" s="3">
         <v>46220</v>
@@ -4122,7 +4122,7 @@
         <v>21</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
@@ -4880,75 +4880,75 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E88" s="3">
-        <v>45964</v>
+        <v>45309</v>
       </c>
       <c r="F88" s="3">
-        <v>47790</v>
+        <v>46221</v>
       </c>
       <c r="G88" s="2">
         <v>6</v>
       </c>
       <c r="H88" s="3">
-        <v>47790</v>
+        <v>46221</v>
       </c>
       <c r="I88" s="2">
         <v>100</v>
       </c>
       <c r="J88" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K88" s="5">
-        <v>750</v>
+        <v>284</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E89" s="3">
-        <v>45309</v>
+        <v>45491</v>
       </c>
       <c r="F89" s="3">
-        <v>46221</v>
+        <v>48047</v>
       </c>
       <c r="G89" s="2">
         <v>6</v>
       </c>
-      <c r="H89" s="3">
-        <v>46221</v>
-      </c>
-      <c r="I89" s="2">
-        <v>100</v>
+      <c r="H89" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J89" s="2">
-        <v>0.08</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K89" s="5">
-        <v>284</v>
+        <v>817</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>56</v>
@@ -4956,37 +4956,37 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E90" s="3">
-        <v>45491</v>
+        <v>45624</v>
       </c>
       <c r="F90" s="3">
-        <v>48047</v>
+        <v>47085</v>
       </c>
       <c r="G90" s="2">
         <v>6</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>29</v>
+      <c r="H90" s="3">
+        <v>47085</v>
+      </c>
+      <c r="I90" s="2">
+        <v>100</v>
       </c>
       <c r="J90" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K90" s="5">
-        <v>817</v>
+        <v>75</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>56</v>
@@ -4994,37 +4994,37 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E91" s="3">
-        <v>45624</v>
+        <v>45805</v>
       </c>
       <c r="F91" s="3">
-        <v>47085</v>
+        <v>48727</v>
       </c>
       <c r="G91" s="2">
         <v>6</v>
       </c>
-      <c r="H91" s="3">
-        <v>47085</v>
-      </c>
-      <c r="I91" s="2">
-        <v>100</v>
+      <c r="H91" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J91" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K91" s="5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>56</v>
@@ -5032,37 +5032,37 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E92" s="3">
-        <v>45805</v>
+        <v>45840</v>
       </c>
       <c r="F92" s="3">
-        <v>48727</v>
+        <v>46570</v>
       </c>
       <c r="G92" s="2">
-        <v>6</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>73</v>
+        <v>3</v>
+      </c>
+      <c r="H92" s="3">
+        <v>46570</v>
+      </c>
+      <c r="I92" s="2">
+        <v>100</v>
       </c>
       <c r="J92" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K92" s="5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>56</v>
@@ -5070,37 +5070,37 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E93" s="3">
-        <v>45840</v>
+        <v>46042</v>
       </c>
       <c r="F93" s="3">
-        <v>46570</v>
+        <v>49694</v>
       </c>
       <c r="G93" s="2">
-        <v>3</v>
-      </c>
-      <c r="H93" s="3">
-        <v>46570</v>
-      </c>
-      <c r="I93" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J93" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K93" s="5">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>56</v>
@@ -5108,37 +5108,37 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E94" s="3">
-        <v>46042</v>
+        <v>46117</v>
       </c>
       <c r="F94" s="3">
-        <v>49694</v>
+        <v>47213</v>
       </c>
       <c r="G94" s="2">
         <v>6</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>73</v>
+      <c r="H94" s="3">
+        <v>47213</v>
+      </c>
+      <c r="I94" s="2">
+        <v>100</v>
       </c>
       <c r="J94" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K94" s="5">
-        <v>600</v>
+        <v>81</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>56</v>
@@ -5146,75 +5146,75 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E95" s="3">
-        <v>46117</v>
+        <v>45497</v>
       </c>
       <c r="F95" s="3">
-        <v>47213</v>
+        <v>48053</v>
       </c>
       <c r="G95" s="2">
         <v>6</v>
       </c>
       <c r="H95" s="3">
-        <v>47213</v>
+        <v>48053</v>
       </c>
       <c r="I95" s="2">
         <v>100</v>
       </c>
       <c r="J95" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K95" s="5">
-        <v>81</v>
+        <v>490</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E96" s="3">
-        <v>45497</v>
+        <v>45981</v>
       </c>
       <c r="F96" s="3">
-        <v>48053</v>
+        <v>49633</v>
       </c>
       <c r="G96" s="2">
         <v>6</v>
       </c>
       <c r="H96" s="3">
-        <v>48053</v>
+        <v>49633</v>
       </c>
       <c r="I96" s="2">
         <v>100</v>
       </c>
       <c r="J96" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K96" s="5">
-        <v>490</v>
+        <v>1030</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>53</v>
@@ -5222,45 +5222,45 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E97" s="3">
-        <v>45981</v>
+        <v>45415</v>
       </c>
       <c r="F97" s="3">
-        <v>49633</v>
+        <v>47241</v>
       </c>
       <c r="G97" s="2">
         <v>6</v>
       </c>
-      <c r="H97" s="3">
-        <v>49633</v>
-      </c>
-      <c r="I97" s="2">
-        <v>100</v>
+      <c r="H97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J97" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K97" s="5">
-        <v>1030</v>
+        <v>46</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>26</v>
@@ -5272,25 +5272,25 @@
         <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>45415</v>
+        <v>45575</v>
       </c>
       <c r="F98" s="3">
-        <v>47241</v>
+        <v>48131</v>
       </c>
       <c r="G98" s="2">
         <v>6</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J98" s="2">
-        <v>0.08</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K98" s="5">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>52</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>26</v>
@@ -5307,28 +5307,28 @@
         <v>15</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E99" s="3">
-        <v>45575</v>
+        <v>45636</v>
       </c>
       <c r="F99" s="3">
-        <v>48131</v>
+        <v>49653</v>
       </c>
       <c r="G99" s="2">
         <v>6</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J99" s="2">
-        <v>7.6499999999999999E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K99" s="5">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>52</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>26</v>
@@ -5345,28 +5345,28 @@
         <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E100" s="3">
-        <v>45636</v>
+        <v>45723</v>
       </c>
       <c r="F100" s="3">
-        <v>49653</v>
+        <v>47549</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>29</v>
+      <c r="H100" s="3">
+        <v>47549</v>
+      </c>
+      <c r="I100" s="2">
+        <v>100</v>
       </c>
       <c r="J100" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K100" s="5">
-        <v>600</v>
+        <v>92</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>52</v>
@@ -5374,7 +5374,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>26</v>
@@ -5383,19 +5383,19 @@
         <v>15</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E101" s="3">
-        <v>45723</v>
+        <v>45818</v>
       </c>
       <c r="F101" s="3">
-        <v>47549</v>
+        <v>48740</v>
       </c>
       <c r="G101" s="2">
         <v>6</v>
       </c>
       <c r="H101" s="3">
-        <v>47549</v>
+        <v>48740</v>
       </c>
       <c r="I101" s="2">
         <v>100</v>
@@ -5404,7 +5404,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K101" s="5">
-        <v>92</v>
+        <v>900</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>52</v>
@@ -5412,37 +5412,37 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E102" s="3">
-        <v>45818</v>
+        <v>45945</v>
       </c>
       <c r="F102" s="3">
-        <v>48740</v>
+        <v>46492</v>
       </c>
       <c r="G102" s="2">
         <v>6</v>
       </c>
       <c r="H102" s="3">
-        <v>48740</v>
+        <v>46492</v>
       </c>
       <c r="I102" s="2">
         <v>100</v>
       </c>
       <c r="J102" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K102" s="5">
-        <v>900</v>
+        <v>73</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>52</v>
@@ -5450,37 +5450,37 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E103" s="3">
-        <v>45945</v>
+        <v>46120</v>
       </c>
       <c r="F103" s="3">
-        <v>46492</v>
+        <v>50503</v>
       </c>
       <c r="G103" s="2">
         <v>6</v>
       </c>
-      <c r="H103" s="3">
-        <v>46492</v>
-      </c>
-      <c r="I103" s="2">
-        <v>100</v>
+      <c r="H103" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J103" s="2">
-        <v>0.06</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K103" s="5">
-        <v>73</v>
+        <v>500</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>52</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>15</v>
@@ -5500,25 +5500,25 @@
         <v>86</v>
       </c>
       <c r="E104" s="3">
-        <v>46120</v>
+        <v>45674</v>
       </c>
       <c r="F104" s="3">
-        <v>50503</v>
+        <v>48961</v>
       </c>
       <c r="G104" s="2">
         <v>6</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J104" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K104" s="5">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>52</v>
@@ -5526,37 +5526,37 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E105" s="3">
-        <v>45674</v>
+        <v>45715</v>
       </c>
       <c r="F105" s="3">
-        <v>48961</v>
+        <v>46445</v>
       </c>
       <c r="G105" s="2">
         <v>6</v>
       </c>
-      <c r="H105" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>29</v>
+      <c r="H105" s="3">
+        <v>46445</v>
+      </c>
+      <c r="I105" s="2">
+        <v>100</v>
       </c>
       <c r="J105" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K105" s="5">
-        <v>1100</v>
+        <v>139</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>52</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>27</v>
@@ -5576,22 +5576,22 @@
         <v>12</v>
       </c>
       <c r="E106" s="3">
-        <v>45715</v>
+        <v>45784</v>
       </c>
       <c r="F106" s="3">
-        <v>46445</v>
+        <v>46514</v>
       </c>
       <c r="G106" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H106" s="3">
-        <v>46445</v>
+        <v>46514</v>
       </c>
       <c r="I106" s="2">
         <v>100</v>
       </c>
       <c r="J106" s="2">
-        <v>6.25E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K106" s="5">
         <v>139</v>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>27</v>
@@ -5614,25 +5614,25 @@
         <v>12</v>
       </c>
       <c r="E107" s="3">
-        <v>45784</v>
+        <v>45860</v>
       </c>
       <c r="F107" s="3">
-        <v>46514</v>
+        <v>46590</v>
       </c>
       <c r="G107" s="2">
         <v>3</v>
       </c>
       <c r="H107" s="3">
-        <v>46514</v>
+        <v>46590</v>
       </c>
       <c r="I107" s="2">
         <v>100</v>
       </c>
       <c r="J107" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K107" s="5">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -5640,13 +5640,13 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>12</v>
@@ -5655,22 +5655,22 @@
         <v>45860</v>
       </c>
       <c r="F108" s="3">
-        <v>46590</v>
+        <v>47686</v>
       </c>
       <c r="G108" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H108" s="3">
-        <v>46590</v>
+        <v>47686</v>
       </c>
       <c r="I108" s="2">
         <v>100</v>
       </c>
       <c r="J108" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K108" s="5">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>52</v>
@@ -5678,37 +5678,37 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E109" s="3">
-        <v>45860</v>
+        <v>45938</v>
       </c>
       <c r="F109" s="3">
-        <v>47686</v>
+        <v>46454</v>
       </c>
       <c r="G109" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H109" s="3">
-        <v>47686</v>
+        <v>46454</v>
       </c>
       <c r="I109" s="2">
         <v>100</v>
       </c>
       <c r="J109" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K109" s="5">
-        <v>224</v>
+        <v>1000</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>52</v>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>27</v>
@@ -5728,25 +5728,25 @@
         <v>12</v>
       </c>
       <c r="E110" s="3">
-        <v>45938</v>
+        <v>45993</v>
       </c>
       <c r="F110" s="3">
-        <v>46454</v>
+        <v>47179</v>
       </c>
       <c r="G110" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H110" s="3">
-        <v>46454</v>
+        <v>47179</v>
       </c>
       <c r="I110" s="2">
         <v>100</v>
       </c>
       <c r="J110" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K110" s="5">
-        <v>1000</v>
+        <v>194</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>52</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>27</v>
@@ -5763,28 +5763,28 @@
         <v>11</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E111" s="3">
-        <v>45993</v>
+        <v>44239</v>
       </c>
       <c r="F111" s="3">
-        <v>47179</v>
+        <v>47299</v>
       </c>
       <c r="G111" s="2">
         <v>6</v>
       </c>
-      <c r="H111" s="3">
-        <v>47179</v>
-      </c>
-      <c r="I111" s="2">
-        <v>100</v>
+      <c r="H111" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J111" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="K111" s="5">
-        <v>194</v>
+        <v>747</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>52</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -5804,25 +5804,25 @@
         <v>86</v>
       </c>
       <c r="E112" s="3">
-        <v>44239</v>
+        <v>45199</v>
       </c>
       <c r="F112" s="3">
-        <v>47299</v>
+        <v>48852</v>
       </c>
       <c r="G112" s="2">
         <v>6</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J112" s="2">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K112" s="5">
-        <v>747</v>
+        <v>575</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>52</v>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>27</v>
@@ -5839,28 +5839,28 @@
         <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E113" s="3">
-        <v>45199</v>
+        <v>45090</v>
       </c>
       <c r="F113" s="3">
-        <v>48852</v>
+        <v>46066</v>
       </c>
       <c r="G113" s="2">
         <v>6</v>
       </c>
-      <c r="H113" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>43</v>
+      <c r="H113" s="3">
+        <v>46066</v>
+      </c>
+      <c r="I113" s="2">
+        <v>100</v>
       </c>
       <c r="J113" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K113" s="5">
-        <v>575</v>
+        <v>263</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>52</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>27</v>
@@ -5880,25 +5880,25 @@
         <v>12</v>
       </c>
       <c r="E114" s="3">
-        <v>45090</v>
+        <v>45624</v>
       </c>
       <c r="F114" s="3">
-        <v>46066</v>
+        <v>46170</v>
       </c>
       <c r="G114" s="2">
         <v>6</v>
       </c>
       <c r="H114" s="3">
-        <v>46066</v>
+        <v>46170</v>
       </c>
       <c r="I114" s="2">
         <v>100</v>
       </c>
       <c r="J114" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K114" s="5">
-        <v>263</v>
+        <v>177</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>52</v>
@@ -5906,37 +5906,37 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E115" s="3">
-        <v>45624</v>
+        <v>45546</v>
       </c>
       <c r="F115" s="3">
-        <v>46170</v>
+        <v>48102</v>
       </c>
       <c r="G115" s="2">
         <v>6</v>
       </c>
-      <c r="H115" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I115" s="2">
-        <v>100</v>
+      <c r="H115" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J115" s="2">
-        <v>0.06</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K115" s="5">
-        <v>177</v>
+        <v>1000</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>52</v>
@@ -5944,37 +5944,37 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E116" s="3">
-        <v>45546</v>
+        <v>45575</v>
       </c>
       <c r="F116" s="3">
-        <v>48102</v>
+        <v>47036</v>
       </c>
       <c r="G116" s="2">
         <v>6</v>
       </c>
-      <c r="H116" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>29</v>
+      <c r="H116" s="3">
+        <v>47036</v>
+      </c>
+      <c r="I116" s="2">
+        <v>100</v>
       </c>
       <c r="J116" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K116" s="5">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>52</v>
@@ -5982,16 +5982,16 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E117" s="3">
         <v>45575</v>
@@ -6009,10 +6009,10 @@
         <v>100</v>
       </c>
       <c r="J117" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K117" s="5">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>52</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>15</v>
@@ -6032,25 +6032,25 @@
         <v>86</v>
       </c>
       <c r="E118" s="3">
-        <v>45575</v>
+        <v>43671</v>
       </c>
       <c r="F118" s="3">
-        <v>47036</v>
+        <v>46228</v>
       </c>
       <c r="G118" s="2">
         <v>6</v>
       </c>
       <c r="H118" s="3">
-        <v>47036</v>
+        <v>46228</v>
       </c>
       <c r="I118" s="2">
         <v>100</v>
       </c>
       <c r="J118" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K118" s="5">
-        <v>25</v>
+        <v>400</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>52</v>
@@ -6058,37 +6058,37 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E119" s="3">
-        <v>43671</v>
+        <v>45349</v>
       </c>
       <c r="F119" s="3">
-        <v>46228</v>
+        <v>46445</v>
       </c>
       <c r="G119" s="2">
         <v>6</v>
       </c>
       <c r="H119" s="3">
-        <v>46228</v>
+        <v>46445</v>
       </c>
       <c r="I119" s="2">
         <v>100</v>
       </c>
       <c r="J119" s="2">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="K119" s="5">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>52</v>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>71</v>
@@ -6108,25 +6108,25 @@
         <v>12</v>
       </c>
       <c r="E120" s="3">
-        <v>45349</v>
+        <v>45456</v>
       </c>
       <c r="F120" s="3">
-        <v>46445</v>
+        <v>46551</v>
       </c>
       <c r="G120" s="2">
-        <v>6</v>
-      </c>
-      <c r="H120" s="3">
-        <v>46445</v>
-      </c>
-      <c r="I120" s="2">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J120" s="2">
         <v>0.06</v>
       </c>
       <c r="K120" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>52</v>
@@ -6134,37 +6134,37 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E121" s="3">
-        <v>45456</v>
+        <v>45581</v>
       </c>
       <c r="F121" s="3">
-        <v>46551</v>
+        <v>48503</v>
       </c>
       <c r="G121" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J121" s="2">
-        <v>0.06</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K121" s="5">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>52</v>
@@ -6172,37 +6172,37 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E122" s="3">
-        <v>45581</v>
+        <v>45618</v>
       </c>
       <c r="F122" s="3">
-        <v>48503</v>
+        <v>46348</v>
       </c>
       <c r="G122" s="2">
         <v>6</v>
       </c>
-      <c r="H122" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>29</v>
+      <c r="H122" s="3">
+        <v>46348</v>
+      </c>
+      <c r="I122" s="2">
+        <v>100</v>
       </c>
       <c r="J122" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="K122" s="5">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>52</v>
@@ -6210,7 +6210,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>71</v>
@@ -6225,22 +6225,22 @@
         <v>45618</v>
       </c>
       <c r="F123" s="3">
-        <v>46348</v>
+        <v>47079</v>
       </c>
       <c r="G123" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H123" s="3">
-        <v>46348</v>
+        <v>47079</v>
       </c>
       <c r="I123" s="2">
         <v>100</v>
       </c>
       <c r="J123" s="2">
-        <v>5.2499999999999998E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K123" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>52</v>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>71</v>
@@ -6260,25 +6260,25 @@
         <v>12</v>
       </c>
       <c r="E124" s="3">
-        <v>45618</v>
+        <v>45797</v>
       </c>
       <c r="F124" s="3">
-        <v>47079</v>
+        <v>46527</v>
       </c>
       <c r="G124" s="2">
         <v>3</v>
       </c>
       <c r="H124" s="3">
-        <v>47079</v>
+        <v>46527</v>
       </c>
       <c r="I124" s="2">
         <v>100</v>
       </c>
       <c r="J124" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K124" s="5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>52</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>71</v>
@@ -6298,75 +6298,37 @@
         <v>12</v>
       </c>
       <c r="E125" s="3">
-        <v>45797</v>
+        <v>46006</v>
       </c>
       <c r="F125" s="3">
-        <v>46527</v>
+        <v>47102</v>
       </c>
       <c r="G125" s="2">
         <v>3</v>
       </c>
       <c r="H125" s="3">
-        <v>46527</v>
+        <v>47102</v>
       </c>
       <c r="I125" s="2">
         <v>100</v>
       </c>
       <c r="J125" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K125" s="5">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A126" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E126" s="3">
-        <v>46006</v>
-      </c>
-      <c r="F126" s="3">
-        <v>47102</v>
-      </c>
-      <c r="G126" s="2">
-        <v>3</v>
-      </c>
-      <c r="H126" s="3">
-        <v>47102</v>
-      </c>
-      <c r="I126" s="2">
-        <v>100</v>
-      </c>
-      <c r="J126" s="2">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="K126" s="5">
-        <v>45</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H131" s="6"/>
+    <row r="130" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H130" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L126">
-      <sortCondition ref="B1:B126"/>
+  <autoFilter ref="A1:L125" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L125">
+      <sortCondition ref="B1:B125"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Documents\datos_financieros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A3E73B-6366-4809-B9BF-EC98041E15CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96267B4-A550-47CE-980B-3B28125CD7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="222">
   <si>
     <t>name</t>
   </si>
@@ -473,12 +473,6 @@
     <t>MSSFO</t>
   </si>
   <si>
-    <t>RUCAO</t>
-  </si>
-  <si>
-    <t>RUCOO</t>
-  </si>
-  <si>
     <t>OLC5O</t>
   </si>
   <si>
@@ -699,6 +693,15 @@
   </si>
   <si>
     <t>PLC6O</t>
+  </si>
+  <si>
+    <t>RUCDO</t>
+  </si>
+  <si>
+    <t>RUCEO</t>
+  </si>
+  <si>
+    <t>30/07/2027;30/10/2027</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2522,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>17</v>
@@ -2557,7 +2560,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>17</v>
@@ -2595,7 +2598,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>17</v>
@@ -2633,7 +2636,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>17</v>
@@ -3622,7 +3625,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>76</v>
@@ -3634,22 +3637,22 @@
         <v>12</v>
       </c>
       <c r="E55" s="3">
-        <v>45363</v>
+        <v>46062</v>
       </c>
       <c r="F55" s="3">
-        <v>46093</v>
+        <v>46690</v>
       </c>
       <c r="G55" s="2">
-        <v>6</v>
-      </c>
-      <c r="H55" s="3">
-        <v>46093</v>
-      </c>
-      <c r="I55" s="2">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J55" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K55" s="2">
         <v>13</v>
@@ -3660,7 +3663,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>76</v>
@@ -3698,7 +3701,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>94</v>
@@ -3736,7 +3739,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>94</v>
@@ -3774,7 +3777,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>21</v>
@@ -3812,7 +3815,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
@@ -3850,7 +3853,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
@@ -3888,7 +3891,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
@@ -3926,7 +3929,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
@@ -3964,7 +3967,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
@@ -4002,7 +4005,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>21</v>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>21</v>
@@ -4078,7 +4081,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>21</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>21</v>
@@ -4154,7 +4157,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>22</v>
@@ -4192,7 +4195,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>22</v>
@@ -4230,7 +4233,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>22</v>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
@@ -4306,7 +4309,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>22</v>
@@ -4344,7 +4347,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>22</v>
@@ -4382,7 +4385,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>22</v>
@@ -4420,7 +4423,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>91</v>
@@ -4459,7 +4462,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>91</v>
@@ -4498,7 +4501,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>91</v>
@@ -4537,7 +4540,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>83</v>
@@ -4575,7 +4578,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>83</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>67</v>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>75</v>
@@ -4689,7 +4692,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>23</v>
@@ -4727,7 +4730,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
@@ -4765,7 +4768,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>23</v>
@@ -4803,7 +4806,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>23</v>
@@ -4841,7 +4844,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>23</v>
@@ -4880,7 +4883,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>24</v>
@@ -4918,7 +4921,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>24</v>
@@ -4956,7 +4959,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>24</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>24</v>
@@ -5032,7 +5035,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>24</v>
@@ -5070,7 +5073,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
@@ -5108,7 +5111,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
@@ -5146,7 +5149,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>25</v>
@@ -5184,7 +5187,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>25</v>
@@ -5222,7 +5225,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>26</v>
@@ -5260,7 +5263,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>26</v>
@@ -5298,7 +5301,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>26</v>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>26</v>
@@ -5374,7 +5377,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>26</v>
@@ -5412,7 +5415,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>26</v>
@@ -5450,7 +5453,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>26</v>
@@ -5471,7 +5474,7 @@
         <v>6</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>29</v>
@@ -5488,7 +5491,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>27</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>27</v>
@@ -5564,7 +5567,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>27</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>27</v>
@@ -5640,7 +5643,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>27</v>
@@ -5678,7 +5681,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>27</v>
@@ -5716,7 +5719,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>27</v>
@@ -5754,7 +5757,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>27</v>
@@ -5792,7 +5795,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -5830,7 +5833,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>27</v>
@@ -5868,7 +5871,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>27</v>
@@ -5906,7 +5909,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
@@ -5944,7 +5947,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
@@ -5982,7 +5985,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -6020,7 +6023,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>71</v>
@@ -6058,7 +6061,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>71</v>
@@ -6096,7 +6099,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>71</v>
@@ -6134,7 +6137,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
@@ -6172,7 +6175,7 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>71</v>
@@ -6210,7 +6213,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>71</v>
@@ -6248,7 +6251,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>71</v>
@@ -6286,7 +6289,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>71</v>

--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Documents\datos_financieros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96267B4-A550-47CE-980B-3B28125CD7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDF05FF-4DF8-4CAF-9FFA-B9D0483676D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="listado_ons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$126</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="224">
   <si>
     <t>name</t>
   </si>
@@ -702,6 +702,12 @@
   </si>
   <si>
     <t>30/07/2027;30/10/2027</t>
+  </si>
+  <si>
+    <t>EAC3O</t>
+  </si>
+  <si>
+    <t>MSU GREEN ENERGY</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N130"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
@@ -3701,10 +3707,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>94</v>
+        <v>223</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
@@ -3713,33 +3719,33 @@
         <v>12</v>
       </c>
       <c r="E57" s="3">
-        <v>45820</v>
+        <v>45646</v>
       </c>
       <c r="F57" s="3">
-        <v>46916</v>
+        <v>47107</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
       </c>
       <c r="H57" s="3">
-        <v>46916</v>
+        <v>47107</v>
       </c>
       <c r="I57" s="2">
         <v>100</v>
       </c>
       <c r="J57" s="2">
-        <v>7.8899999999999998E-2</v>
-      </c>
-      <c r="K57" s="5">
-        <v>85</v>
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K57" s="2">
+        <v>20</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>94</v>
@@ -3751,25 +3757,25 @@
         <v>12</v>
       </c>
       <c r="E58" s="3">
-        <v>45996</v>
+        <v>45820</v>
       </c>
       <c r="F58" s="3">
-        <v>47274</v>
+        <v>46916</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
       </c>
       <c r="H58" s="3">
-        <v>47274</v>
+        <v>46916</v>
       </c>
       <c r="I58" s="2">
         <v>100</v>
       </c>
       <c r="J58" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="K58" s="5">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>52</v>
@@ -3777,10 +3783,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
@@ -3789,25 +3795,25 @@
         <v>12</v>
       </c>
       <c r="E59" s="3">
-        <v>45562</v>
+        <v>45996</v>
       </c>
       <c r="F59" s="3">
-        <v>46657</v>
+        <v>47274</v>
       </c>
       <c r="G59" s="2">
         <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>46657</v>
+        <v>47274</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
       </c>
       <c r="J59" s="2">
-        <v>0.05</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K59" s="5">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>52</v>
@@ -3815,7 +3821,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
@@ -3830,22 +3836,22 @@
         <v>45562</v>
       </c>
       <c r="F60" s="3">
-        <v>47388</v>
+        <v>46657</v>
       </c>
       <c r="G60" s="2">
         <v>6</v>
       </c>
       <c r="H60" s="3">
-        <v>47388</v>
+        <v>46657</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
       </c>
       <c r="J60" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K60" s="5">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>52</v>
@@ -3853,7 +3859,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
@@ -3865,25 +3871,25 @@
         <v>12</v>
       </c>
       <c r="E61" s="3">
-        <v>45609</v>
+        <v>45562</v>
       </c>
       <c r="F61" s="3">
-        <v>48165</v>
+        <v>47388</v>
       </c>
       <c r="G61" s="2">
         <v>6</v>
       </c>
       <c r="H61" s="3">
-        <v>48165</v>
+        <v>47388</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
       </c>
       <c r="J61" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K61" s="5">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>52</v>
@@ -3891,7 +3897,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
@@ -3906,22 +3912,22 @@
         <v>45609</v>
       </c>
       <c r="F62" s="3">
-        <v>47070</v>
+        <v>48165</v>
       </c>
       <c r="G62" s="2">
         <v>6</v>
       </c>
       <c r="H62" s="3">
-        <v>47070</v>
+        <v>48165</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
       </c>
       <c r="J62" s="2">
-        <v>6.25E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K62" s="5">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>52</v>
@@ -3929,37 +3935,37 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="3">
-        <v>45699</v>
+        <v>45609</v>
       </c>
       <c r="F63" s="3">
-        <v>46610</v>
+        <v>47070</v>
       </c>
       <c r="G63" s="2">
         <v>6</v>
       </c>
       <c r="H63" s="3">
-        <v>46610</v>
+        <v>47070</v>
       </c>
       <c r="I63" s="2">
         <v>100</v>
       </c>
       <c r="J63" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K63" s="5">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>52</v>
@@ -3967,37 +3973,37 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E64" s="3">
-        <v>45896</v>
+        <v>45699</v>
       </c>
       <c r="F64" s="3">
-        <v>47357</v>
+        <v>46610</v>
       </c>
       <c r="G64" s="2">
         <v>6</v>
       </c>
       <c r="H64" s="3">
-        <v>47357</v>
+        <v>46610</v>
       </c>
       <c r="I64" s="2">
         <v>100</v>
       </c>
       <c r="J64" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="K64" s="2">
-        <v>85</v>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K64" s="5">
+        <v>120</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>52</v>
@@ -4005,7 +4011,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>21</v>
@@ -4017,25 +4023,25 @@
         <v>12</v>
       </c>
       <c r="E65" s="3">
-        <v>45947</v>
+        <v>45896</v>
       </c>
       <c r="F65" s="3">
-        <v>46494</v>
+        <v>47357</v>
       </c>
       <c r="G65" s="2">
         <v>6</v>
       </c>
       <c r="H65" s="3">
-        <v>46494</v>
+        <v>47357</v>
       </c>
       <c r="I65" s="2">
         <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K65" s="2">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>52</v>
@@ -4043,37 +4049,37 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E66" s="3">
-        <v>46037</v>
+        <v>45947</v>
       </c>
       <c r="F66" s="3">
-        <v>50055</v>
+        <v>46494</v>
       </c>
       <c r="G66" s="2">
         <v>6</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>29</v>
+      <c r="H66" s="3">
+        <v>46494</v>
+      </c>
+      <c r="I66" s="2">
+        <v>100</v>
       </c>
       <c r="J66" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K66" s="2">
-        <v>375</v>
+        <v>56</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>52</v>
@@ -4081,37 +4087,37 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E67" s="3">
-        <v>44316</v>
+        <v>46037</v>
       </c>
       <c r="F67" s="3">
-        <v>46507</v>
+        <v>50055</v>
       </c>
       <c r="G67" s="2">
         <v>6</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J67" s="2">
-        <v>9.1249999999999998E-2</v>
-      </c>
-      <c r="K67" s="5">
-        <v>180</v>
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="K67" s="2">
+        <v>375</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>52</v>
@@ -4119,37 +4125,37 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="3">
-        <v>45412</v>
+        <v>44316</v>
       </c>
       <c r="F68" s="3">
-        <v>48334</v>
+        <v>46507</v>
       </c>
       <c r="G68" s="2">
         <v>6</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J68" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>9.1249999999999998E-2</v>
       </c>
       <c r="K68" s="5">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>52</v>
@@ -4157,37 +4163,37 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E69" s="3">
-        <v>44903</v>
+        <v>45412</v>
       </c>
       <c r="F69" s="3">
-        <v>46364</v>
+        <v>48334</v>
       </c>
       <c r="G69" s="2">
         <v>6</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J69" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K69" s="5">
-        <v>196</v>
+        <v>400</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>52</v>
@@ -4195,37 +4201,37 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E70" s="3">
-        <v>45545</v>
+        <v>44903</v>
       </c>
       <c r="F70" s="3">
-        <v>48101</v>
+        <v>46364</v>
       </c>
       <c r="G70" s="2">
         <v>6</v>
       </c>
-      <c r="H70" s="3">
-        <v>48101</v>
-      </c>
-      <c r="I70" s="2">
-        <v>100</v>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J70" s="2">
-        <v>7.9500000000000001E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K70" s="5">
-        <v>410</v>
+        <v>196</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>52</v>
@@ -4233,37 +4239,37 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E71" s="3">
-        <v>45569</v>
+        <v>45545</v>
       </c>
       <c r="F71" s="3">
-        <v>47030</v>
+        <v>48101</v>
       </c>
       <c r="G71" s="2">
         <v>6</v>
       </c>
       <c r="H71" s="3">
-        <v>47030</v>
+        <v>48101</v>
       </c>
       <c r="I71" s="2">
         <v>100</v>
       </c>
       <c r="J71" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K71" s="5">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>52</v>
@@ -4271,37 +4277,37 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E72" s="3">
-        <v>45642</v>
+        <v>45569</v>
       </c>
       <c r="F72" s="3">
-        <v>49294</v>
+        <v>47030</v>
       </c>
       <c r="G72" s="2">
         <v>6</v>
       </c>
       <c r="H72" s="3">
-        <v>49294</v>
+        <v>47030</v>
       </c>
       <c r="I72" s="2">
         <v>100</v>
       </c>
       <c r="J72" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K72" s="5">
-        <v>700</v>
+        <v>83</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>52</v>
@@ -4309,7 +4315,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>22</v>
@@ -4321,25 +4327,25 @@
         <v>86</v>
       </c>
       <c r="E73" s="3">
-        <v>45875</v>
+        <v>45642</v>
       </c>
       <c r="F73" s="3">
-        <v>46971</v>
+        <v>49294</v>
       </c>
       <c r="G73" s="2">
         <v>6</v>
       </c>
       <c r="H73" s="3">
-        <v>46971</v>
+        <v>49294</v>
       </c>
       <c r="I73" s="2">
         <v>100</v>
       </c>
       <c r="J73" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K73" s="5">
-        <v>83</v>
+        <v>700</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>52</v>
@@ -4347,7 +4353,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>22</v>
@@ -4359,25 +4365,25 @@
         <v>86</v>
       </c>
       <c r="E74" s="3">
-        <v>45975</v>
+        <v>45875</v>
       </c>
       <c r="F74" s="3">
-        <v>50358</v>
+        <v>46971</v>
       </c>
       <c r="G74" s="2">
         <v>6</v>
       </c>
       <c r="H74" s="3">
-        <v>50358</v>
+        <v>46971</v>
       </c>
       <c r="I74" s="2">
         <v>100</v>
       </c>
       <c r="J74" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K74" s="5">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>52</v>
@@ -4385,37 +4391,37 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E75" s="3">
-        <v>46113</v>
+        <v>45975</v>
       </c>
       <c r="F75" s="3">
-        <v>47209</v>
+        <v>50358</v>
       </c>
       <c r="G75" s="2">
         <v>6</v>
       </c>
       <c r="H75" s="3">
-        <v>47209</v>
+        <v>50358</v>
       </c>
       <c r="I75" s="2">
         <v>100</v>
       </c>
       <c r="J75" s="2">
-        <v>5.5E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K75" s="5">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>52</v>
@@ -4423,10 +4429,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
@@ -4435,34 +4441,33 @@
         <v>12</v>
       </c>
       <c r="E76" s="3">
-        <v>45587</v>
+        <v>46113</v>
       </c>
       <c r="F76" s="3">
-        <v>47048</v>
+        <v>47209</v>
       </c>
       <c r="G76" s="2">
         <v>6</v>
       </c>
       <c r="H76" s="3">
-        <f>F76</f>
-        <v>47048</v>
+        <v>47209</v>
       </c>
       <c r="I76" s="2">
         <v>100</v>
       </c>
       <c r="J76" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K76" s="5">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>91</v>
@@ -4474,26 +4479,26 @@
         <v>12</v>
       </c>
       <c r="E77" s="3">
-        <v>45705</v>
+        <v>45587</v>
       </c>
       <c r="F77" s="3">
-        <v>47896</v>
+        <v>47048</v>
       </c>
       <c r="G77" s="2">
         <v>6</v>
       </c>
       <c r="H77" s="3">
         <f>F77</f>
-        <v>47896</v>
+        <v>47048</v>
       </c>
       <c r="I77" s="2">
         <v>100</v>
       </c>
       <c r="J77" s="2">
-        <v>0.08</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K77" s="5">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>54</v>
@@ -4501,7 +4506,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>91</v>
@@ -4513,26 +4518,26 @@
         <v>12</v>
       </c>
       <c r="E78" s="3">
-        <v>45859</v>
+        <v>45705</v>
       </c>
       <c r="F78" s="3">
-        <v>46955</v>
+        <v>47896</v>
       </c>
       <c r="G78" s="2">
         <v>6</v>
       </c>
       <c r="H78" s="3">
         <f>F78</f>
-        <v>46955</v>
+        <v>47896</v>
       </c>
       <c r="I78" s="2">
         <v>100</v>
       </c>
       <c r="J78" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K78" s="5">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>54</v>
@@ -4540,28 +4545,29 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E79" s="3">
-        <v>45838</v>
+        <v>45859</v>
       </c>
       <c r="F79" s="3">
-        <v>48364</v>
+        <v>46955</v>
       </c>
       <c r="G79" s="2">
         <v>6</v>
       </c>
       <c r="H79" s="3">
-        <v>48364</v>
+        <f>F79</f>
+        <v>46955</v>
       </c>
       <c r="I79" s="2">
         <v>100</v>
@@ -4570,45 +4576,45 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="K79" s="5">
-        <v>650</v>
+        <v>38</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E80" s="3">
-        <v>46080</v>
+        <v>45838</v>
       </c>
       <c r="F80" s="3">
-        <v>47176</v>
+        <v>48364</v>
       </c>
       <c r="G80" s="2">
         <v>6</v>
       </c>
       <c r="H80" s="3">
-        <v>47176</v>
+        <v>48364</v>
       </c>
       <c r="I80" s="2">
         <v>100</v>
       </c>
       <c r="J80" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K80" s="5">
-        <v>167</v>
+        <v>650</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>52</v>
@@ -4616,48 +4622,48 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E81" s="3">
+        <v>46080</v>
+      </c>
+      <c r="F81" s="3">
+        <v>47176</v>
+      </c>
+      <c r="G81" s="2">
+        <v>6</v>
+      </c>
+      <c r="H81" s="3">
+        <v>47176</v>
+      </c>
+      <c r="I81" s="2">
+        <v>100</v>
+      </c>
+      <c r="J81" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K81" s="5">
         <v>167</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="3">
-        <v>45895</v>
-      </c>
-      <c r="F81" s="3">
-        <v>46260</v>
-      </c>
-      <c r="G81" s="2">
-        <v>6</v>
-      </c>
-      <c r="H81" s="3">
-        <v>46260</v>
-      </c>
-      <c r="I81" s="2">
-        <v>100</v>
-      </c>
-      <c r="J81" s="2">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="K81" s="5">
-        <v>16</v>
-      </c>
       <c r="L81" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
@@ -4666,36 +4672,36 @@
         <v>12</v>
       </c>
       <c r="E82" s="3">
-        <v>45412</v>
+        <v>45895</v>
       </c>
       <c r="F82" s="3">
-        <v>46507</v>
+        <v>46260</v>
       </c>
       <c r="G82" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H82" s="3">
-        <v>46507</v>
+        <v>46260</v>
       </c>
       <c r="I82" s="2">
         <v>100</v>
       </c>
       <c r="J82" s="2">
-        <v>7.9000000000000001E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K82" s="5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
@@ -4704,33 +4710,33 @@
         <v>12</v>
       </c>
       <c r="E83" s="3">
-        <v>45404</v>
+        <v>45412</v>
       </c>
       <c r="F83" s="3">
-        <v>46134</v>
+        <v>46507</v>
       </c>
       <c r="G83" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H83" s="3">
-        <v>46134</v>
+        <v>46507</v>
       </c>
       <c r="I83" s="2">
         <v>100</v>
       </c>
       <c r="J83" s="2">
-        <v>0.06</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="K83" s="5">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
@@ -4742,25 +4748,25 @@
         <v>12</v>
       </c>
       <c r="E84" s="3">
-        <v>45589</v>
+        <v>45404</v>
       </c>
       <c r="F84" s="3">
-        <v>46684</v>
+        <v>46134</v>
       </c>
       <c r="G84" s="2">
         <v>6</v>
       </c>
       <c r="H84" s="3">
-        <v>46684</v>
+        <v>46134</v>
       </c>
       <c r="I84" s="2">
         <v>100</v>
       </c>
       <c r="J84" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K84" s="5">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>52</v>
@@ -4768,7 +4774,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>23</v>
@@ -4783,22 +4789,22 @@
         <v>45589</v>
       </c>
       <c r="F85" s="3">
-        <v>47415</v>
+        <v>46684</v>
       </c>
       <c r="G85" s="2">
         <v>6</v>
       </c>
       <c r="H85" s="3">
-        <v>47415</v>
+        <v>46684</v>
       </c>
       <c r="I85" s="2">
         <v>100</v>
       </c>
       <c r="J85" s="2">
-        <v>6.8000000000000005E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K85" s="5">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>52</v>
@@ -4806,37 +4812,37 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E86" s="3">
-        <v>45679</v>
+        <v>45589</v>
       </c>
       <c r="F86" s="3">
-        <v>48601</v>
+        <v>47415</v>
       </c>
       <c r="G86" s="2">
         <v>6</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>29</v>
+      <c r="H86" s="3">
+        <v>47415</v>
+      </c>
+      <c r="I86" s="2">
+        <v>100</v>
       </c>
       <c r="J86" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="K86" s="5">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>52</v>
@@ -4844,38 +4850,37 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E87" s="3">
-        <v>45946</v>
+        <v>45679</v>
       </c>
       <c r="F87" s="3">
-        <v>46676</v>
+        <v>48601</v>
       </c>
       <c r="G87" s="2">
         <v>6</v>
       </c>
-      <c r="H87" s="3">
-        <f>F87</f>
-        <v>46676</v>
-      </c>
-      <c r="I87" s="2">
-        <v>100</v>
+      <c r="H87" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J87" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K87" s="5">
-        <v>67</v>
+        <v>400</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>52</v>
@@ -4883,75 +4888,76 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E88" s="3">
-        <v>45309</v>
+        <v>45946</v>
       </c>
       <c r="F88" s="3">
-        <v>46221</v>
+        <v>46676</v>
       </c>
       <c r="G88" s="2">
         <v>6</v>
       </c>
       <c r="H88" s="3">
-        <v>46221</v>
+        <f>F88</f>
+        <v>46676</v>
       </c>
       <c r="I88" s="2">
         <v>100</v>
       </c>
       <c r="J88" s="2">
-        <v>0.08</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K88" s="5">
-        <v>284</v>
+        <v>67</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E89" s="3">
-        <v>45491</v>
+        <v>45309</v>
       </c>
       <c r="F89" s="3">
-        <v>48047</v>
+        <v>46221</v>
       </c>
       <c r="G89" s="2">
         <v>6</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>29</v>
+      <c r="H89" s="3">
+        <v>46221</v>
+      </c>
+      <c r="I89" s="2">
+        <v>100</v>
       </c>
       <c r="J89" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K89" s="5">
-        <v>817</v>
+        <v>284</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>56</v>
@@ -4959,37 +4965,37 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E90" s="3">
-        <v>45624</v>
+        <v>45491</v>
       </c>
       <c r="F90" s="3">
-        <v>47085</v>
+        <v>48047</v>
       </c>
       <c r="G90" s="2">
         <v>6</v>
       </c>
-      <c r="H90" s="3">
-        <v>47085</v>
-      </c>
-      <c r="I90" s="2">
-        <v>100</v>
+      <c r="H90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J90" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K90" s="5">
-        <v>75</v>
+        <v>817</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>56</v>
@@ -4997,37 +5003,37 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E91" s="3">
-        <v>45805</v>
+        <v>45624</v>
       </c>
       <c r="F91" s="3">
-        <v>48727</v>
+        <v>47085</v>
       </c>
       <c r="G91" s="2">
         <v>6</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>73</v>
+      <c r="H91" s="3">
+        <v>47085</v>
+      </c>
+      <c r="I91" s="2">
+        <v>100</v>
       </c>
       <c r="J91" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K91" s="5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>56</v>
@@ -5035,37 +5041,37 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E92" s="3">
-        <v>45840</v>
+        <v>45805</v>
       </c>
       <c r="F92" s="3">
-        <v>46570</v>
+        <v>48727</v>
       </c>
       <c r="G92" s="2">
-        <v>3</v>
-      </c>
-      <c r="H92" s="3">
-        <v>46570</v>
-      </c>
-      <c r="I92" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J92" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K92" s="5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>56</v>
@@ -5073,37 +5079,37 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E93" s="3">
-        <v>46042</v>
+        <v>45840</v>
       </c>
       <c r="F93" s="3">
-        <v>49694</v>
+        <v>46570</v>
       </c>
       <c r="G93" s="2">
-        <v>6</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>73</v>
+        <v>3</v>
+      </c>
+      <c r="H93" s="3">
+        <v>46570</v>
+      </c>
+      <c r="I93" s="2">
+        <v>100</v>
       </c>
       <c r="J93" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K93" s="5">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>56</v>
@@ -5111,37 +5117,37 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E94" s="3">
-        <v>46117</v>
+        <v>46042</v>
       </c>
       <c r="F94" s="3">
-        <v>47213</v>
+        <v>49694</v>
       </c>
       <c r="G94" s="2">
         <v>6</v>
       </c>
-      <c r="H94" s="3">
-        <v>47213</v>
-      </c>
-      <c r="I94" s="2">
-        <v>100</v>
+      <c r="H94" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J94" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K94" s="5">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>56</v>
@@ -5149,75 +5155,75 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E95" s="3">
-        <v>45497</v>
+        <v>46117</v>
       </c>
       <c r="F95" s="3">
-        <v>48053</v>
+        <v>47213</v>
       </c>
       <c r="G95" s="2">
         <v>6</v>
       </c>
       <c r="H95" s="3">
-        <v>48053</v>
+        <v>47213</v>
       </c>
       <c r="I95" s="2">
         <v>100</v>
       </c>
       <c r="J95" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K95" s="5">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E96" s="3">
-        <v>45981</v>
+        <v>45497</v>
       </c>
       <c r="F96" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="G96" s="2">
         <v>6</v>
       </c>
       <c r="H96" s="3">
-        <v>49633</v>
+        <v>48053</v>
       </c>
       <c r="I96" s="2">
         <v>100</v>
       </c>
       <c r="J96" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K96" s="5">
-        <v>1030</v>
+        <v>490</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>53</v>
@@ -5225,45 +5231,45 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E97" s="3">
-        <v>45415</v>
+        <v>45981</v>
       </c>
       <c r="F97" s="3">
-        <v>47241</v>
+        <v>49633</v>
       </c>
       <c r="G97" s="2">
         <v>6</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>43</v>
+      <c r="H97" s="3">
+        <v>49633</v>
+      </c>
+      <c r="I97" s="2">
+        <v>100</v>
       </c>
       <c r="J97" s="2">
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K97" s="5">
-        <v>46</v>
+        <v>1030</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>26</v>
@@ -5275,25 +5281,25 @@
         <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>45575</v>
+        <v>45415</v>
       </c>
       <c r="F98" s="3">
-        <v>48131</v>
+        <v>47241</v>
       </c>
       <c r="G98" s="2">
         <v>6</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J98" s="2">
-        <v>7.6499999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K98" s="5">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>52</v>
@@ -5301,7 +5307,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>26</v>
@@ -5310,28 +5316,28 @@
         <v>15</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E99" s="3">
-        <v>45636</v>
+        <v>45575</v>
       </c>
       <c r="F99" s="3">
-        <v>49653</v>
+        <v>48131</v>
       </c>
       <c r="G99" s="2">
         <v>6</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J99" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K99" s="5">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>52</v>
@@ -5339,7 +5345,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>26</v>
@@ -5348,28 +5354,28 @@
         <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E100" s="3">
-        <v>45723</v>
+        <v>45636</v>
       </c>
       <c r="F100" s="3">
-        <v>47549</v>
+        <v>49653</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
       </c>
-      <c r="H100" s="3">
-        <v>47549</v>
-      </c>
-      <c r="I100" s="2">
-        <v>100</v>
+      <c r="H100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J100" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K100" s="5">
-        <v>92</v>
+        <v>600</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>52</v>
@@ -5377,7 +5383,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>26</v>
@@ -5386,19 +5392,19 @@
         <v>15</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E101" s="3">
-        <v>45818</v>
+        <v>45723</v>
       </c>
       <c r="F101" s="3">
-        <v>48740</v>
+        <v>47549</v>
       </c>
       <c r="G101" s="2">
         <v>6</v>
       </c>
       <c r="H101" s="3">
-        <v>48740</v>
+        <v>47549</v>
       </c>
       <c r="I101" s="2">
         <v>100</v>
@@ -5407,7 +5413,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K101" s="5">
-        <v>900</v>
+        <v>92</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>52</v>
@@ -5415,37 +5421,37 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E102" s="3">
-        <v>45945</v>
+        <v>45818</v>
       </c>
       <c r="F102" s="3">
-        <v>46492</v>
+        <v>48740</v>
       </c>
       <c r="G102" s="2">
         <v>6</v>
       </c>
       <c r="H102" s="3">
-        <v>46492</v>
+        <v>48740</v>
       </c>
       <c r="I102" s="2">
         <v>100</v>
       </c>
       <c r="J102" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K102" s="5">
-        <v>73</v>
+        <v>900</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>52</v>
@@ -5453,37 +5459,37 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E103" s="3">
-        <v>46120</v>
+        <v>45945</v>
       </c>
       <c r="F103" s="3">
-        <v>50503</v>
+        <v>46492</v>
       </c>
       <c r="G103" s="2">
         <v>6</v>
       </c>
-      <c r="H103" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>29</v>
+      <c r="H103" s="3">
+        <v>46492</v>
+      </c>
+      <c r="I103" s="2">
+        <v>100</v>
       </c>
       <c r="J103" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K103" s="5">
-        <v>500</v>
+        <v>73</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>52</v>
@@ -5491,10 +5497,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>15</v>
@@ -5503,25 +5509,25 @@
         <v>86</v>
       </c>
       <c r="E104" s="3">
-        <v>45674</v>
+        <v>46120</v>
       </c>
       <c r="F104" s="3">
-        <v>48961</v>
+        <v>50503</v>
       </c>
       <c r="G104" s="2">
         <v>6</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J104" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K104" s="5">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>52</v>
@@ -5529,37 +5535,37 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E105" s="3">
-        <v>45715</v>
+        <v>45674</v>
       </c>
       <c r="F105" s="3">
-        <v>46445</v>
+        <v>48961</v>
       </c>
       <c r="G105" s="2">
         <v>6</v>
       </c>
-      <c r="H105" s="3">
-        <v>46445</v>
-      </c>
-      <c r="I105" s="2">
-        <v>100</v>
+      <c r="H105" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J105" s="2">
-        <v>6.25E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K105" s="5">
-        <v>139</v>
+        <v>1100</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>52</v>
@@ -5567,7 +5573,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>27</v>
@@ -5579,22 +5585,22 @@
         <v>12</v>
       </c>
       <c r="E106" s="3">
-        <v>45784</v>
+        <v>45715</v>
       </c>
       <c r="F106" s="3">
-        <v>46514</v>
+        <v>46445</v>
       </c>
       <c r="G106" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H106" s="3">
-        <v>46514</v>
+        <v>46445</v>
       </c>
       <c r="I106" s="2">
         <v>100</v>
       </c>
       <c r="J106" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K106" s="5">
         <v>139</v>
@@ -5605,7 +5611,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>27</v>
@@ -5617,25 +5623,25 @@
         <v>12</v>
       </c>
       <c r="E107" s="3">
-        <v>45860</v>
+        <v>45784</v>
       </c>
       <c r="F107" s="3">
-        <v>46590</v>
+        <v>46514</v>
       </c>
       <c r="G107" s="2">
         <v>3</v>
       </c>
       <c r="H107" s="3">
-        <v>46590</v>
+        <v>46514</v>
       </c>
       <c r="I107" s="2">
         <v>100</v>
       </c>
       <c r="J107" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K107" s="5">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>52</v>
@@ -5643,13 +5649,13 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>12</v>
@@ -5658,22 +5664,22 @@
         <v>45860</v>
       </c>
       <c r="F108" s="3">
-        <v>47686</v>
+        <v>46590</v>
       </c>
       <c r="G108" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3">
-        <v>47686</v>
+        <v>46590</v>
       </c>
       <c r="I108" s="2">
         <v>100</v>
       </c>
       <c r="J108" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K108" s="5">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>52</v>
@@ -5681,37 +5687,37 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E109" s="3">
-        <v>45938</v>
+        <v>45860</v>
       </c>
       <c r="F109" s="3">
-        <v>46454</v>
+        <v>47686</v>
       </c>
       <c r="G109" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H109" s="3">
-        <v>46454</v>
+        <v>47686</v>
       </c>
       <c r="I109" s="2">
         <v>100</v>
       </c>
       <c r="J109" s="2">
-        <v>0.06</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K109" s="5">
-        <v>1000</v>
+        <v>224</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>52</v>
@@ -5719,7 +5725,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>27</v>
@@ -5731,25 +5737,25 @@
         <v>12</v>
       </c>
       <c r="E110" s="3">
-        <v>45993</v>
+        <v>45938</v>
       </c>
       <c r="F110" s="3">
-        <v>47179</v>
+        <v>46454</v>
       </c>
       <c r="G110" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H110" s="3">
-        <v>47179</v>
+        <v>46454</v>
       </c>
       <c r="I110" s="2">
         <v>100</v>
       </c>
       <c r="J110" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K110" s="5">
-        <v>194</v>
+        <v>1000</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>52</v>
@@ -5757,7 +5763,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>27</v>
@@ -5766,28 +5772,28 @@
         <v>11</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E111" s="3">
-        <v>44239</v>
+        <v>45993</v>
       </c>
       <c r="F111" s="3">
-        <v>47299</v>
+        <v>47179</v>
       </c>
       <c r="G111" s="2">
         <v>6</v>
       </c>
-      <c r="H111" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>47</v>
+      <c r="H111" s="3">
+        <v>47179</v>
+      </c>
+      <c r="I111" s="2">
+        <v>100</v>
       </c>
       <c r="J111" s="2">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K111" s="5">
-        <v>747</v>
+        <v>194</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>52</v>
@@ -5795,7 +5801,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>27</v>
@@ -5807,25 +5813,25 @@
         <v>86</v>
       </c>
       <c r="E112" s="3">
-        <v>45199</v>
+        <v>44239</v>
       </c>
       <c r="F112" s="3">
-        <v>48852</v>
+        <v>47299</v>
       </c>
       <c r="G112" s="2">
         <v>6</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J112" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="K112" s="5">
-        <v>575</v>
+        <v>747</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>52</v>
@@ -5833,7 +5839,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>27</v>
@@ -5842,28 +5848,28 @@
         <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E113" s="3">
-        <v>45090</v>
+        <v>45199</v>
       </c>
       <c r="F113" s="3">
-        <v>46066</v>
+        <v>48852</v>
       </c>
       <c r="G113" s="2">
         <v>6</v>
       </c>
-      <c r="H113" s="3">
-        <v>46066</v>
-      </c>
-      <c r="I113" s="2">
-        <v>100</v>
+      <c r="H113" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J113" s="2">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K113" s="5">
-        <v>263</v>
+        <v>575</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>52</v>
@@ -5871,7 +5877,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>27</v>
@@ -5883,25 +5889,25 @@
         <v>12</v>
       </c>
       <c r="E114" s="3">
-        <v>45624</v>
+        <v>45090</v>
       </c>
       <c r="F114" s="3">
-        <v>46170</v>
+        <v>46066</v>
       </c>
       <c r="G114" s="2">
         <v>6</v>
       </c>
       <c r="H114" s="3">
-        <v>46170</v>
+        <v>46066</v>
       </c>
       <c r="I114" s="2">
         <v>100</v>
       </c>
       <c r="J114" s="2">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K114" s="5">
-        <v>177</v>
+        <v>263</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>52</v>
@@ -5909,37 +5915,37 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E115" s="3">
-        <v>45546</v>
+        <v>45624</v>
       </c>
       <c r="F115" s="3">
-        <v>48102</v>
+        <v>46170</v>
       </c>
       <c r="G115" s="2">
         <v>6</v>
       </c>
-      <c r="H115" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>29</v>
+      <c r="H115" s="3">
+        <v>46170</v>
+      </c>
+      <c r="I115" s="2">
+        <v>100</v>
       </c>
       <c r="J115" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K115" s="5">
-        <v>1000</v>
+        <v>177</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>52</v>
@@ -5947,37 +5953,37 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E116" s="3">
-        <v>45575</v>
+        <v>45546</v>
       </c>
       <c r="F116" s="3">
-        <v>47036</v>
+        <v>48102</v>
       </c>
       <c r="G116" s="2">
         <v>6</v>
       </c>
-      <c r="H116" s="3">
-        <v>47036</v>
-      </c>
-      <c r="I116" s="2">
-        <v>100</v>
+      <c r="H116" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J116" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K116" s="5">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>52</v>
@@ -5985,16 +5991,16 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E117" s="3">
         <v>45575</v>
@@ -6012,10 +6018,10 @@
         <v>100</v>
       </c>
       <c r="J117" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K117" s="5">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>52</v>
@@ -6023,10 +6029,10 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>15</v>
@@ -6035,25 +6041,25 @@
         <v>86</v>
       </c>
       <c r="E118" s="3">
-        <v>43671</v>
+        <v>45575</v>
       </c>
       <c r="F118" s="3">
-        <v>46228</v>
+        <v>47036</v>
       </c>
       <c r="G118" s="2">
         <v>6</v>
       </c>
       <c r="H118" s="3">
-        <v>46228</v>
+        <v>47036</v>
       </c>
       <c r="I118" s="2">
         <v>100</v>
       </c>
       <c r="J118" s="2">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K118" s="5">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>52</v>
@@ -6061,37 +6067,37 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E119" s="3">
-        <v>45349</v>
+        <v>43671</v>
       </c>
       <c r="F119" s="3">
-        <v>46445</v>
+        <v>46228</v>
       </c>
       <c r="G119" s="2">
         <v>6</v>
       </c>
       <c r="H119" s="3">
-        <v>46445</v>
+        <v>46228</v>
       </c>
       <c r="I119" s="2">
         <v>100</v>
       </c>
       <c r="J119" s="2">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K119" s="5">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>52</v>
@@ -6099,7 +6105,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>71</v>
@@ -6111,25 +6117,25 @@
         <v>12</v>
       </c>
       <c r="E120" s="3">
-        <v>45456</v>
+        <v>45349</v>
       </c>
       <c r="F120" s="3">
-        <v>46551</v>
+        <v>46445</v>
       </c>
       <c r="G120" s="2">
-        <v>3</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>73</v>
+        <v>6</v>
+      </c>
+      <c r="H120" s="3">
+        <v>46445</v>
+      </c>
+      <c r="I120" s="2">
+        <v>100</v>
       </c>
       <c r="J120" s="2">
         <v>0.06</v>
       </c>
       <c r="K120" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>52</v>
@@ -6137,37 +6143,37 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E121" s="3">
-        <v>45581</v>
+        <v>45456</v>
       </c>
       <c r="F121" s="3">
-        <v>48503</v>
+        <v>46551</v>
       </c>
       <c r="G121" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J121" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K121" s="5">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>52</v>
@@ -6175,37 +6181,37 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E122" s="3">
-        <v>45618</v>
+        <v>45581</v>
       </c>
       <c r="F122" s="3">
-        <v>46348</v>
+        <v>48503</v>
       </c>
       <c r="G122" s="2">
         <v>6</v>
       </c>
-      <c r="H122" s="3">
-        <v>46348</v>
-      </c>
-      <c r="I122" s="2">
-        <v>100</v>
+      <c r="H122" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J122" s="2">
-        <v>5.2499999999999998E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K122" s="5">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>52</v>
@@ -6213,7 +6219,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>71</v>
@@ -6228,22 +6234,22 @@
         <v>45618</v>
       </c>
       <c r="F123" s="3">
-        <v>47079</v>
+        <v>46348</v>
       </c>
       <c r="G123" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H123" s="3">
-        <v>47079</v>
+        <v>46348</v>
       </c>
       <c r="I123" s="2">
         <v>100</v>
       </c>
       <c r="J123" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="K123" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>52</v>
@@ -6251,7 +6257,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>71</v>
@@ -6263,25 +6269,25 @@
         <v>12</v>
       </c>
       <c r="E124" s="3">
-        <v>45797</v>
+        <v>45618</v>
       </c>
       <c r="F124" s="3">
-        <v>46527</v>
+        <v>47079</v>
       </c>
       <c r="G124" s="2">
         <v>3</v>
       </c>
       <c r="H124" s="3">
-        <v>46527</v>
+        <v>47079</v>
       </c>
       <c r="I124" s="2">
         <v>100</v>
       </c>
       <c r="J124" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K124" s="5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>52</v>
@@ -6289,7 +6295,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>71</v>
@@ -6301,37 +6307,75 @@
         <v>12</v>
       </c>
       <c r="E125" s="3">
-        <v>46006</v>
+        <v>45797</v>
       </c>
       <c r="F125" s="3">
-        <v>47102</v>
+        <v>46527</v>
       </c>
       <c r="G125" s="2">
         <v>3</v>
       </c>
       <c r="H125" s="3">
+        <v>46527</v>
+      </c>
+      <c r="I125" s="2">
+        <v>100</v>
+      </c>
+      <c r="J125" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K125" s="5">
+        <v>53</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="3">
+        <v>46006</v>
+      </c>
+      <c r="F126" s="3">
         <v>47102</v>
       </c>
-      <c r="I125" s="2">
-        <v>100</v>
-      </c>
-      <c r="J125" s="2">
+      <c r="G126" s="2">
+        <v>3</v>
+      </c>
+      <c r="H126" s="3">
+        <v>47102</v>
+      </c>
+      <c r="I126" s="2">
+        <v>100</v>
+      </c>
+      <c r="J126" s="2">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="K125" s="5">
+      <c r="K126" s="5">
         <v>45</v>
       </c>
-      <c r="L125" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H130" s="6"/>
+      <c r="L126" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H131" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L125" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L125">
-      <sortCondition ref="B1:B125"/>
+  <autoFilter ref="A1:L126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L126">
+      <sortCondition ref="B1:B126"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/listado_ons.xlsx
+++ b/listado_ons.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marza\Documents\datos_financieros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDF05FF-4DF8-4CAF-9FFA-B9D0483676D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E24C82-5960-40CE-8E67-5FD32E96224A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listado_ons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listado_ons!$A$1:$L$136</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="238">
   <si>
     <t>name</t>
   </si>
@@ -371,9 +371,6 @@
     <t>CAC8O</t>
   </si>
   <si>
-    <t>NPCAO</t>
-  </si>
-  <si>
     <t>NPCCO</t>
   </si>
   <si>
@@ -708,6 +705,51 @@
   </si>
   <si>
     <t>MSU GREEN ENERGY</t>
+  </si>
+  <si>
+    <t>GN43O</t>
+  </si>
+  <si>
+    <t>NPCDO</t>
+  </si>
+  <si>
+    <t>DNCBO</t>
+  </si>
+  <si>
+    <t>DNCAO</t>
+  </si>
+  <si>
+    <t>28/04/2031;28/04/2032;28/04/2033</t>
+  </si>
+  <si>
+    <t>EAC4O</t>
+  </si>
+  <si>
+    <t>MSSGO</t>
+  </si>
+  <si>
+    <t>CGC</t>
+  </si>
+  <si>
+    <t>CP36O</t>
+  </si>
+  <si>
+    <t>CP37O</t>
+  </si>
+  <si>
+    <t>CP38O</t>
+  </si>
+  <si>
+    <t>CP40O</t>
+  </si>
+  <si>
+    <t>16/06/2034;16/06/2035;16/06/2036</t>
+  </si>
+  <si>
+    <t>PLC7O</t>
+  </si>
+  <si>
+    <t>30/09/2035;30/09/2036;30/09/2037</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
@@ -2110,48 +2152,48 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>87</v>
+        <v>230</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E15" s="3">
-        <v>45163</v>
+        <v>45575</v>
       </c>
       <c r="F15" s="3">
-        <v>46990</v>
+        <v>46670</v>
       </c>
       <c r="G15" s="2">
         <v>6</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>89</v>
+      <c r="H15" s="3">
+        <v>46670</v>
+      </c>
+      <c r="I15" s="2">
+        <v>100</v>
       </c>
       <c r="J15" s="2">
-        <v>9.2499999999999999E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K15" s="2">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>87</v>
+        <v>230</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
@@ -2160,282 +2202,282 @@
         <v>12</v>
       </c>
       <c r="E16" s="3">
-        <v>45411</v>
+        <v>45726</v>
       </c>
       <c r="F16" s="3">
-        <v>46202</v>
+        <v>46456</v>
       </c>
       <c r="G16" s="2">
-        <v>3</v>
-      </c>
-      <c r="H16" s="4">
-        <v>46202</v>
+        <v>6</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46456</v>
       </c>
       <c r="I16" s="2">
         <v>100</v>
       </c>
       <c r="J16" s="2">
-        <v>5.9499999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K16" s="2">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3">
-        <v>45183</v>
+        <v>45989</v>
       </c>
       <c r="F17" s="3">
-        <v>46095</v>
+        <v>47815</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" s="3">
-        <v>46095</v>
+        <v>47815</v>
       </c>
       <c r="I17" s="2">
         <v>100</v>
       </c>
       <c r="J17" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11874999999999999</v>
       </c>
       <c r="K17" s="2">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="3">
-        <v>45894</v>
+        <v>46090</v>
       </c>
       <c r="F18" s="3">
-        <v>47355</v>
+        <v>46821</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" s="3">
-        <v>47355</v>
+        <v>46821</v>
       </c>
       <c r="I18" s="2">
         <v>100</v>
       </c>
       <c r="J18" s="2">
-        <v>0.08</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K18" s="2">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="3">
-        <v>44750</v>
+        <v>45163</v>
       </c>
       <c r="F19" s="3">
-        <v>46084</v>
+        <v>46990</v>
       </c>
       <c r="G19" s="2">
         <v>6</v>
       </c>
-      <c r="H19" s="3">
-        <v>46084</v>
-      </c>
-      <c r="I19" s="2">
-        <v>100</v>
+      <c r="H19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="J19" s="2">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="K19" s="2">
+        <v>141</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>45411</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46202</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4">
+        <v>46202</v>
+      </c>
+      <c r="I20" s="2">
+        <v>100</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>47</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="3">
+        <v>45894</v>
+      </c>
+      <c r="F21" s="3">
+        <v>47355</v>
+      </c>
+      <c r="G21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="3">
+        <v>47355</v>
+      </c>
+      <c r="I21" s="2">
+        <v>100</v>
+      </c>
+      <c r="J21" s="2">
         <v>0.08</v>
       </c>
-      <c r="K19" s="2">
-        <v>70</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="3">
-        <v>45308</v>
-      </c>
-      <c r="F20" s="3">
-        <v>46404</v>
-      </c>
-      <c r="G20" s="2">
-        <v>6</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46404</v>
-      </c>
-      <c r="I20" s="2">
-        <v>100</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="K21" s="2">
+        <v>89</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3">
+        <v>46142</v>
+      </c>
+      <c r="F22" s="3">
+        <v>47603</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
+      </c>
+      <c r="H22" s="3">
+        <v>47603</v>
+      </c>
+      <c r="I22" s="2">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2">
         <v>0.06</v>
       </c>
-      <c r="K20" s="2">
-        <v>39</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="3">
-        <v>45404</v>
-      </c>
-      <c r="F21" s="3">
-        <v>46256</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I21" s="2">
-        <v>100</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="K21" s="2">
-        <v>10</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="3">
-        <v>45611</v>
-      </c>
-      <c r="F22" s="3">
-        <v>47072</v>
-      </c>
-      <c r="G22" s="2">
-        <v>6</v>
-      </c>
-      <c r="H22" s="3">
-        <v>47072</v>
-      </c>
-      <c r="I22" s="2">
-        <v>100</v>
-      </c>
-      <c r="J22" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
       <c r="K22" s="2">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E23" s="3">
-        <v>45849</v>
+        <v>44750</v>
       </c>
       <c r="F23" s="3">
-        <v>46945</v>
+        <v>46084</v>
       </c>
       <c r="G23" s="2">
         <v>6</v>
       </c>
       <c r="H23" s="3">
-        <v>46945</v>
+        <v>46084</v>
       </c>
       <c r="I23" s="2">
         <v>100</v>
@@ -2444,15 +2486,15 @@
         <v>0.08</v>
       </c>
       <c r="K23" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2464,33 +2506,33 @@
         <v>12</v>
       </c>
       <c r="E24" s="3">
-        <v>45902</v>
+        <v>45308</v>
       </c>
       <c r="F24" s="3">
-        <v>46632</v>
+        <v>46404</v>
       </c>
       <c r="G24" s="2">
         <v>6</v>
       </c>
       <c r="H24" s="3">
-        <v>46632</v>
+        <v>46404</v>
       </c>
       <c r="I24" s="2">
         <v>100</v>
       </c>
       <c r="J24" s="2">
-        <v>7.2499999999999995E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K24" s="2">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2502,815 +2544,815 @@
         <v>12</v>
       </c>
       <c r="E25" s="3">
+        <v>45404</v>
+      </c>
+      <c r="F25" s="3">
+        <v>46256</v>
+      </c>
+      <c r="G25" s="2">
+        <v>6</v>
+      </c>
+      <c r="H25" s="3">
+        <v>46256</v>
+      </c>
+      <c r="I25" s="2">
+        <v>100</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K25" s="2">
+        <v>10</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="3">
+        <v>45611</v>
+      </c>
+      <c r="F26" s="3">
+        <v>47072</v>
+      </c>
+      <c r="G26" s="2">
+        <v>6</v>
+      </c>
+      <c r="H26" s="3">
+        <v>47072</v>
+      </c>
+      <c r="I26" s="2">
+        <v>100</v>
+      </c>
+      <c r="J26" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K26" s="2">
+        <v>64</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="3">
+        <v>45849</v>
+      </c>
+      <c r="F27" s="3">
+        <v>46945</v>
+      </c>
+      <c r="G27" s="2">
+        <v>6</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46945</v>
+      </c>
+      <c r="I27" s="2">
+        <v>100</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="K27" s="2">
+        <v>43</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F28" s="3">
+        <v>46632</v>
+      </c>
+      <c r="G28" s="2">
+        <v>6</v>
+      </c>
+      <c r="H28" s="3">
+        <v>46632</v>
+      </c>
+      <c r="I28" s="2">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>31</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="3">
         <v>46001</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F29" s="3">
         <v>47187</v>
       </c>
-      <c r="G25" s="2">
-        <v>6</v>
-      </c>
-      <c r="H25" s="3">
+      <c r="G29" s="2">
+        <v>6</v>
+      </c>
+      <c r="H29" s="3">
         <v>47187</v>
       </c>
-      <c r="I25" s="2">
-        <v>100</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="I29" s="2">
+        <v>100</v>
+      </c>
+      <c r="J29" s="2">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K29" s="2">
         <v>29</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+      <c r="L29" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="3">
+        <v>45358</v>
+      </c>
+      <c r="F30" s="3">
+        <v>46348</v>
+      </c>
+      <c r="G30" s="2">
+        <v>6</v>
+      </c>
+      <c r="H30" s="3">
+        <v>46348</v>
+      </c>
+      <c r="I30" s="2">
+        <v>100</v>
+      </c>
+      <c r="J30" s="2">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="K30" s="2">
+        <v>95</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="3">
-        <v>45358</v>
-      </c>
-      <c r="F26" s="3">
-        <v>46348</v>
-      </c>
-      <c r="G26" s="2">
-        <v>6</v>
-      </c>
-      <c r="H26" s="3">
-        <v>46348</v>
-      </c>
-      <c r="I26" s="2">
-        <v>100</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="3">
+        <v>45509</v>
+      </c>
+      <c r="F31" s="3">
+        <v>46970</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6</v>
+      </c>
+      <c r="H31" s="3">
+        <v>46970</v>
+      </c>
+      <c r="I31" s="2">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="K31" s="2">
+        <v>81</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="3">
+        <v>45589</v>
+      </c>
+      <c r="F32" s="3">
+        <v>47780</v>
+      </c>
+      <c r="G32" s="2">
+        <v>6</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="2">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="K26" s="2">
-        <v>95</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="K32" s="2">
+        <v>385</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="3">
-        <v>45509</v>
-      </c>
-      <c r="F27" s="3">
-        <v>46970</v>
-      </c>
-      <c r="G27" s="2">
-        <v>6</v>
-      </c>
-      <c r="H27" s="3">
-        <v>46970</v>
-      </c>
-      <c r="I27" s="2">
-        <v>100</v>
-      </c>
-      <c r="J27" s="2">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="K27" s="2">
-        <v>81</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="3">
+        <v>45876</v>
+      </c>
+      <c r="F33" s="3">
+        <v>46241</v>
+      </c>
+      <c r="G33" s="2">
+        <v>6</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46241</v>
+      </c>
+      <c r="I33" s="2">
+        <v>100</v>
+      </c>
+      <c r="J33" s="2">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K33" s="2">
+        <v>80</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="3">
-        <v>45589</v>
-      </c>
-      <c r="F28" s="3">
-        <v>47780</v>
-      </c>
-      <c r="G28" s="2">
-        <v>6</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="2">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="K28" s="2">
-        <v>385</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="3">
-        <v>45876</v>
-      </c>
-      <c r="F29" s="3">
-        <v>46241</v>
-      </c>
-      <c r="G29" s="2">
-        <v>6</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46241</v>
-      </c>
-      <c r="I29" s="2">
-        <v>100</v>
-      </c>
-      <c r="J29" s="2">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="K29" s="2">
-        <v>80</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="3">
-        <v>45575</v>
-      </c>
-      <c r="F30" s="3">
-        <v>47036</v>
-      </c>
-      <c r="G30" s="2">
-        <v>6</v>
-      </c>
-      <c r="H30" s="3">
-        <v>47036</v>
-      </c>
-      <c r="I30" s="2">
-        <v>100</v>
-      </c>
-      <c r="J30" s="2">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="K30" s="2">
-        <v>325</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N30" s="6"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="3">
-        <v>45883</v>
-      </c>
-      <c r="F31" s="3">
-        <v>46265</v>
-      </c>
-      <c r="G31" s="2">
-        <v>6</v>
-      </c>
-      <c r="H31" s="3">
-        <v>46265</v>
-      </c>
-      <c r="I31" s="2">
-        <v>100</v>
-      </c>
-      <c r="J31" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="K31" s="2">
-        <v>110</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="3">
-        <v>45582</v>
-      </c>
-      <c r="F32" s="3">
-        <v>47043</v>
-      </c>
-      <c r="G32" s="2">
-        <v>6</v>
-      </c>
-      <c r="H32" s="3">
-        <v>47043</v>
-      </c>
-      <c r="I32" s="2">
-        <v>100</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="K32" s="2">
-        <v>48</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="3">
-        <v>45721</v>
-      </c>
-      <c r="F33" s="3">
-        <v>46817</v>
-      </c>
-      <c r="G33" s="2">
-        <v>6</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46817</v>
-      </c>
-      <c r="I33" s="2">
-        <v>100</v>
-      </c>
-      <c r="J33" s="2">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="K33" s="2">
-        <v>27</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E34" s="3">
-        <v>45993</v>
+        <v>46206</v>
       </c>
       <c r="F34" s="3">
-        <v>48915</v>
+        <v>47302</v>
       </c>
       <c r="G34" s="2">
         <v>6</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>29</v>
+      <c r="H34" s="3">
+        <v>47302</v>
+      </c>
+      <c r="I34" s="2">
+        <v>100</v>
       </c>
       <c r="J34" s="2">
-        <v>7.7499999999999999E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K34" s="2">
-        <v>400</v>
+        <v>211</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46140</v>
+      </c>
+      <c r="F35" s="3">
+        <v>48697</v>
+      </c>
+      <c r="G35" s="2">
+        <v>6</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" s="2">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="K35" s="2">
+        <v>550</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E36" s="3">
+        <v>45575</v>
+      </c>
+      <c r="F36" s="3">
+        <v>47036</v>
+      </c>
+      <c r="G36" s="2">
+        <v>6</v>
+      </c>
+      <c r="H36" s="3">
+        <v>47036</v>
+      </c>
+      <c r="I36" s="2">
+        <v>100</v>
+      </c>
+      <c r="J36" s="2">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="K36" s="2">
+        <v>325</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="3">
+        <v>45883</v>
+      </c>
+      <c r="F37" s="3">
+        <v>46265</v>
+      </c>
+      <c r="G37" s="2">
+        <v>6</v>
+      </c>
+      <c r="H37" s="3">
+        <v>46265</v>
+      </c>
+      <c r="I37" s="2">
+        <v>100</v>
+      </c>
+      <c r="J37" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="K37" s="2">
+        <v>110</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3">
+        <v>45359</v>
+      </c>
+      <c r="F38" s="3">
+        <v>46454</v>
+      </c>
+      <c r="G38" s="2">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3">
+        <v>46454</v>
+      </c>
+      <c r="I38" s="2">
+        <v>100</v>
+      </c>
+      <c r="J38" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="K38" s="2">
+        <v>20</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="3">
+        <v>45582</v>
+      </c>
+      <c r="F39" s="3">
+        <v>47043</v>
+      </c>
+      <c r="G39" s="2">
+        <v>6</v>
+      </c>
+      <c r="H39" s="3">
+        <v>47043</v>
+      </c>
+      <c r="I39" s="2">
+        <v>100</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K39" s="2">
+        <v>48</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="3">
+        <v>45721</v>
+      </c>
+      <c r="F40" s="3">
+        <v>46817</v>
+      </c>
+      <c r="G40" s="2">
+        <v>6</v>
+      </c>
+      <c r="H40" s="3">
+        <v>46817</v>
+      </c>
+      <c r="I40" s="2">
+        <v>100</v>
+      </c>
+      <c r="J40" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K40" s="2">
+        <v>27</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="3">
+        <v>45993</v>
+      </c>
+      <c r="F41" s="3">
+        <v>48915</v>
+      </c>
+      <c r="G41" s="2">
+        <v>6</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J41" s="2">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="K41" s="2">
+        <v>400</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="3">
         <v>44441</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F42" s="3">
         <v>46632</v>
       </c>
-      <c r="G35" s="2">
-        <v>6</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="G42" s="2">
+        <v>6</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I42" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J42" s="2">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K42" s="2">
         <v>146</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="3">
+        <v>45846</v>
+      </c>
+      <c r="F43" s="3">
+        <v>46942</v>
+      </c>
+      <c r="G43" s="2">
+        <v>6</v>
+      </c>
+      <c r="H43" s="3">
+        <v>46942</v>
+      </c>
+      <c r="I43" s="2">
+        <v>100</v>
+      </c>
+      <c r="J43" s="2">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="K43" s="2">
+        <v>18</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="3">
-        <v>45846</v>
-      </c>
-      <c r="F36" s="3">
-        <v>46942</v>
-      </c>
-      <c r="G36" s="2">
-        <v>6</v>
-      </c>
-      <c r="H36" s="3">
-        <v>46942</v>
-      </c>
-      <c r="I36" s="2">
-        <v>100</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="B44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3">
+        <v>45891</v>
+      </c>
+      <c r="F44" s="3">
+        <v>46256</v>
+      </c>
+      <c r="G44" s="2">
+        <v>6</v>
+      </c>
+      <c r="H44" s="3">
+        <v>46256</v>
+      </c>
+      <c r="I44" s="2">
+        <v>100</v>
+      </c>
+      <c r="J44" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K44" s="2">
+        <v>30</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="3">
+        <v>44720</v>
+      </c>
+      <c r="F45" s="3">
+        <v>46926</v>
+      </c>
+      <c r="G45" s="2">
+        <v>6</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" s="2">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="K36" s="2">
-        <v>18</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="3">
-        <v>45891</v>
-      </c>
-      <c r="F37" s="3">
-        <v>46256</v>
-      </c>
-      <c r="G37" s="2">
-        <v>6</v>
-      </c>
-      <c r="H37" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I37" s="2">
-        <v>100</v>
-      </c>
-      <c r="J37" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K37" s="2">
-        <v>30</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="K45" s="2">
+        <v>64</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="3">
-        <v>44720</v>
-      </c>
-      <c r="F38" s="3">
-        <v>46926</v>
-      </c>
-      <c r="G38" s="2">
-        <v>6</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J38" s="2">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K38" s="2">
-        <v>64</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="3">
+      <c r="C46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="3">
         <v>45350</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F46" s="3">
         <v>46446</v>
       </c>
-      <c r="G39" s="2">
-        <v>6</v>
-      </c>
-      <c r="H39" s="3">
+      <c r="G46" s="2">
+        <v>6</v>
+      </c>
+      <c r="H46" s="3">
         <v>46446</v>
-      </c>
-      <c r="I39" s="2">
-        <v>100</v>
-      </c>
-      <c r="J39" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K39" s="2">
-        <v>21</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="3">
-        <v>45453</v>
-      </c>
-      <c r="F40" s="3">
-        <v>46183</v>
-      </c>
-      <c r="G40" s="2">
-        <v>6</v>
-      </c>
-      <c r="H40" s="3">
-        <v>46183</v>
-      </c>
-      <c r="I40" s="2">
-        <v>100</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="K40" s="2">
-        <v>23</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="3">
-        <v>45588</v>
-      </c>
-      <c r="F41" s="3">
-        <v>46683</v>
-      </c>
-      <c r="G41" s="2">
-        <v>6</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46683</v>
-      </c>
-      <c r="I41" s="2">
-        <v>100</v>
-      </c>
-      <c r="J41" s="2">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="K41" s="2">
-        <v>15</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="3">
-        <v>45588</v>
-      </c>
-      <c r="F42" s="3">
-        <v>47414</v>
-      </c>
-      <c r="G42" s="2">
-        <v>6</v>
-      </c>
-      <c r="H42" s="3">
-        <v>47414</v>
-      </c>
-      <c r="I42" s="2">
-        <v>100</v>
-      </c>
-      <c r="J42" s="2">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K42" s="2">
-        <v>51</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="3">
-        <v>45747</v>
-      </c>
-      <c r="F43" s="3">
-        <v>49399</v>
-      </c>
-      <c r="G43" s="2">
-        <v>6</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J43" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="K43" s="2">
-        <v>300</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="3">
-        <v>45586</v>
-      </c>
-      <c r="F44" s="3">
-        <v>46316</v>
-      </c>
-      <c r="G44" s="2">
-        <v>6</v>
-      </c>
-      <c r="H44" s="3">
-        <v>46316</v>
-      </c>
-      <c r="I44" s="2">
-        <v>100</v>
-      </c>
-      <c r="J44" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="K44" s="2">
-        <v>28</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="3">
-        <v>45586</v>
-      </c>
-      <c r="F45" s="3">
-        <v>47047</v>
-      </c>
-      <c r="G45" s="2">
-        <v>6</v>
-      </c>
-      <c r="H45" s="3">
-        <v>47047</v>
-      </c>
-      <c r="I45" s="2">
-        <v>100</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="K45" s="2">
-        <v>16</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="3">
-        <v>45674</v>
-      </c>
-      <c r="F46" s="3">
-        <v>46769</v>
-      </c>
-      <c r="G46" s="2">
-        <v>6</v>
-      </c>
-      <c r="H46" s="3">
-        <v>46769</v>
       </c>
       <c r="I46" s="2">
         <v>100</v>
@@ -3319,18 +3361,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K46" s="2">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
@@ -3339,36 +3381,36 @@
         <v>12</v>
       </c>
       <c r="E47" s="3">
-        <v>45804</v>
+        <v>45453</v>
       </c>
       <c r="F47" s="3">
-        <v>46534</v>
+        <v>46183</v>
       </c>
       <c r="G47" s="2">
         <v>6</v>
       </c>
       <c r="H47" s="3">
-        <v>46534</v>
+        <v>46183</v>
       </c>
       <c r="I47" s="2">
         <v>100</v>
       </c>
       <c r="J47" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K47" s="2">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>11</v>
@@ -3377,36 +3419,36 @@
         <v>12</v>
       </c>
       <c r="E48" s="3">
-        <v>45863</v>
+        <v>45588</v>
       </c>
       <c r="F48" s="3">
-        <v>46593</v>
+        <v>46683</v>
       </c>
       <c r="G48" s="2">
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>46593</v>
+        <v>46683</v>
       </c>
       <c r="I48" s="2">
         <v>100</v>
       </c>
       <c r="J48" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="K48" s="2">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
@@ -3415,25 +3457,25 @@
         <v>12</v>
       </c>
       <c r="E49" s="3">
-        <v>45180</v>
+        <v>45588</v>
       </c>
       <c r="F49" s="3">
-        <v>46092</v>
+        <v>47414</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>46092</v>
+        <v>47414</v>
       </c>
       <c r="I49" s="2">
         <v>100</v>
       </c>
       <c r="J49" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K49" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>52</v>
@@ -3441,37 +3483,37 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E50" s="3">
-        <v>45862</v>
+        <v>45747</v>
       </c>
       <c r="F50" s="3">
-        <v>46592</v>
+        <v>49399</v>
       </c>
       <c r="G50" s="2">
         <v>6</v>
       </c>
-      <c r="H50" s="3">
-        <v>46592</v>
-      </c>
-      <c r="I50" s="2">
-        <v>100</v>
+      <c r="H50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J50" s="2">
         <v>0.08</v>
       </c>
       <c r="K50" s="2">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>52</v>
@@ -3479,86 +3521,86 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3">
-        <v>45831</v>
+        <v>45586</v>
       </c>
       <c r="F51" s="3">
-        <v>47292</v>
+        <v>46316</v>
       </c>
       <c r="G51" s="2">
         <v>6</v>
       </c>
       <c r="H51" s="3">
-        <v>47292</v>
+        <v>46316</v>
       </c>
       <c r="I51" s="2">
         <v>100</v>
       </c>
       <c r="J51" s="2">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="K51" s="2">
-        <v>530</v>
+        <v>28</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3">
-        <v>46050</v>
+        <v>45586</v>
       </c>
       <c r="F52" s="3">
-        <v>47876</v>
+        <v>47047</v>
       </c>
       <c r="G52" s="2">
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>47876</v>
+        <v>47047</v>
       </c>
       <c r="I52" s="2">
         <v>100</v>
       </c>
       <c r="J52" s="2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="K52" s="2">
-        <v>400</v>
+        <v>16</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
@@ -3567,36 +3609,36 @@
         <v>12</v>
       </c>
       <c r="E53" s="3">
-        <v>45124</v>
+        <v>45674</v>
       </c>
       <c r="F53" s="3">
-        <v>46220</v>
+        <v>46769</v>
       </c>
       <c r="G53" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>46220</v>
+        <v>46769</v>
       </c>
       <c r="I53" s="2">
         <v>100</v>
       </c>
       <c r="J53" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K53" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
@@ -3605,16 +3647,16 @@
         <v>12</v>
       </c>
       <c r="E54" s="3">
-        <v>45496</v>
+        <v>45804</v>
       </c>
       <c r="F54" s="3">
-        <v>46591</v>
+        <v>46534</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
       </c>
       <c r="H54" s="3">
-        <v>46591</v>
+        <v>46534</v>
       </c>
       <c r="I54" s="2">
         <v>100</v>
@@ -3623,18 +3665,18 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K54" s="2">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
@@ -3643,74 +3685,74 @@
         <v>12</v>
       </c>
       <c r="E55" s="3">
-        <v>46062</v>
+        <v>45863</v>
       </c>
       <c r="F55" s="3">
-        <v>46690</v>
+        <v>46593</v>
       </c>
       <c r="G55" s="2">
-        <v>3</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>73</v>
+        <v>6</v>
+      </c>
+      <c r="H55" s="3">
+        <v>46593</v>
+      </c>
+      <c r="I55" s="2">
+        <v>100</v>
       </c>
       <c r="J55" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K55" s="2">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E56" s="3">
-        <v>45631</v>
+        <v>45180</v>
       </c>
       <c r="F56" s="3">
-        <v>47822</v>
+        <v>46092</v>
       </c>
       <c r="G56" s="2">
         <v>6</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>77</v>
+      <c r="H56" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I56" s="2">
+        <v>100</v>
       </c>
       <c r="J56" s="2">
-        <v>9.7500000000000003E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K56" s="2">
-        <v>400</v>
+        <v>55</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
@@ -3719,112 +3761,112 @@
         <v>12</v>
       </c>
       <c r="E57" s="3">
-        <v>45646</v>
+        <v>45862</v>
       </c>
       <c r="F57" s="3">
-        <v>47107</v>
+        <v>46592</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
       </c>
       <c r="H57" s="3">
-        <v>47107</v>
+        <v>46592</v>
       </c>
       <c r="I57" s="2">
         <v>100</v>
       </c>
       <c r="J57" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K57" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E58" s="3">
-        <v>45820</v>
+        <v>45831</v>
       </c>
       <c r="F58" s="3">
-        <v>46916</v>
+        <v>47292</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
       </c>
       <c r="H58" s="3">
-        <v>46916</v>
+        <v>47292</v>
       </c>
       <c r="I58" s="2">
         <v>100</v>
       </c>
       <c r="J58" s="2">
-        <v>7.8899999999999998E-2</v>
-      </c>
-      <c r="K58" s="5">
-        <v>85</v>
+        <v>0.08</v>
+      </c>
+      <c r="K58" s="2">
+        <v>530</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E59" s="3">
-        <v>45996</v>
+        <v>46050</v>
       </c>
       <c r="F59" s="3">
-        <v>47274</v>
+        <v>47876</v>
       </c>
       <c r="G59" s="2">
         <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>47274</v>
+        <v>47876</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
       </c>
       <c r="J59" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="K59" s="5">
-        <v>115</v>
+        <v>0.08</v>
+      </c>
+      <c r="K59" s="2">
+        <v>400</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
@@ -3833,36 +3875,36 @@
         <v>12</v>
       </c>
       <c r="E60" s="3">
-        <v>45562</v>
+        <v>45124</v>
       </c>
       <c r="F60" s="3">
-        <v>46657</v>
+        <v>46220</v>
       </c>
       <c r="G60" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H60" s="3">
-        <v>46657</v>
+        <v>46220</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
       </c>
       <c r="J60" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="K60" s="5">
-        <v>23</v>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K60" s="2">
+        <v>25</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>11</v>
@@ -3871,36 +3913,36 @@
         <v>12</v>
       </c>
       <c r="E61" s="3">
-        <v>45562</v>
+        <v>45496</v>
       </c>
       <c r="F61" s="3">
-        <v>47388</v>
+        <v>46591</v>
       </c>
       <c r="G61" s="2">
         <v>6</v>
       </c>
       <c r="H61" s="3">
-        <v>47388</v>
+        <v>46591</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
       </c>
       <c r="J61" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K61" s="5">
-        <v>176</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K61" s="2">
+        <v>33</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>11</v>
@@ -3909,36 +3951,36 @@
         <v>12</v>
       </c>
       <c r="E62" s="3">
-        <v>45609</v>
+        <v>45763</v>
       </c>
       <c r="F62" s="3">
-        <v>48165</v>
+        <v>47224</v>
       </c>
       <c r="G62" s="2">
         <v>6</v>
       </c>
       <c r="H62" s="3">
-        <v>48165</v>
+        <v>47224</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
       </c>
       <c r="J62" s="2">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K62" s="5">
-        <v>78</v>
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K62" s="2">
+        <v>34</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
@@ -3947,74 +3989,74 @@
         <v>12</v>
       </c>
       <c r="E63" s="3">
-        <v>45609</v>
+        <v>46062</v>
       </c>
       <c r="F63" s="3">
-        <v>47070</v>
+        <v>46690</v>
       </c>
       <c r="G63" s="2">
-        <v>6</v>
-      </c>
-      <c r="H63" s="3">
-        <v>47070</v>
-      </c>
-      <c r="I63" s="2">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J63" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="K63" s="5">
-        <v>74</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K63" s="2">
+        <v>13</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E64" s="3">
-        <v>45699</v>
+        <v>45631</v>
       </c>
       <c r="F64" s="3">
-        <v>46610</v>
+        <v>47822</v>
       </c>
       <c r="G64" s="2">
         <v>6</v>
       </c>
-      <c r="H64" s="3">
-        <v>46610</v>
-      </c>
-      <c r="I64" s="2">
-        <v>100</v>
+      <c r="H64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="J64" s="2">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="K64" s="5">
-        <v>120</v>
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="K64" s="2">
+        <v>400</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
@@ -4023,101 +4065,101 @@
         <v>12</v>
       </c>
       <c r="E65" s="3">
-        <v>45896</v>
+        <v>45646</v>
       </c>
       <c r="F65" s="3">
-        <v>47357</v>
+        <v>47107</v>
       </c>
       <c r="G65" s="2">
         <v>6</v>
       </c>
       <c r="H65" s="3">
-        <v>47357</v>
+        <v>47107</v>
       </c>
       <c r="I65" s="2">
         <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K65" s="2">
+        <v>20</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E66" s="3">
-        <v>45947</v>
+        <v>46189</v>
       </c>
       <c r="F66" s="3">
-        <v>46494</v>
+        <v>49842</v>
       </c>
       <c r="G66" s="2">
         <v>6</v>
       </c>
-      <c r="H66" s="3">
-        <v>46494</v>
-      </c>
-      <c r="I66" s="2">
-        <v>100</v>
+      <c r="H66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J66" s="2">
-        <v>0.06</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="K66" s="2">
-        <v>56</v>
+        <v>400</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E67" s="3">
-        <v>46037</v>
+        <v>45820</v>
       </c>
       <c r="F67" s="3">
-        <v>50055</v>
+        <v>46916</v>
       </c>
       <c r="G67" s="2">
         <v>6</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>29</v>
+      <c r="H67" s="3">
+        <v>46916</v>
+      </c>
+      <c r="I67" s="2">
+        <v>100</v>
       </c>
       <c r="J67" s="2">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="K67" s="2">
-        <v>375</v>
+        <v>7.8899999999999998E-2</v>
+      </c>
+      <c r="K67" s="5">
+        <v>85</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>52</v>
@@ -4125,10 +4167,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
@@ -4137,25 +4179,25 @@
         <v>12</v>
       </c>
       <c r="E68" s="3">
-        <v>44316</v>
+        <v>45996</v>
       </c>
       <c r="F68" s="3">
-        <v>46507</v>
+        <v>47274</v>
       </c>
       <c r="G68" s="2">
         <v>6</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>38</v>
+      <c r="H68" s="3">
+        <v>47274</v>
+      </c>
+      <c r="I68" s="2">
+        <v>100</v>
       </c>
       <c r="J68" s="2">
-        <v>9.1249999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K68" s="5">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>52</v>
@@ -4163,37 +4205,37 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="3">
-        <v>45412</v>
+        <v>45562</v>
       </c>
       <c r="F69" s="3">
-        <v>48334</v>
+        <v>46657</v>
       </c>
       <c r="G69" s="2">
         <v>6</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>29</v>
+      <c r="H69" s="3">
+        <v>46657</v>
+      </c>
+      <c r="I69" s="2">
+        <v>100</v>
       </c>
       <c r="J69" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K69" s="5">
-        <v>400</v>
+        <v>23</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>52</v>
@@ -4201,37 +4243,37 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E70" s="3">
-        <v>44903</v>
+        <v>45562</v>
       </c>
       <c r="F70" s="3">
-        <v>46364</v>
+        <v>47388</v>
       </c>
       <c r="G70" s="2">
         <v>6</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>29</v>
+      <c r="H70" s="3">
+        <v>47388</v>
+      </c>
+      <c r="I70" s="2">
+        <v>100</v>
       </c>
       <c r="J70" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K70" s="5">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>52</v>
@@ -4239,37 +4281,37 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E71" s="3">
-        <v>45545</v>
+        <v>45609</v>
       </c>
       <c r="F71" s="3">
-        <v>48101</v>
+        <v>48165</v>
       </c>
       <c r="G71" s="2">
         <v>6</v>
       </c>
       <c r="H71" s="3">
-        <v>48101</v>
+        <v>48165</v>
       </c>
       <c r="I71" s="2">
         <v>100</v>
       </c>
       <c r="J71" s="2">
-        <v>7.9500000000000001E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K71" s="5">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>52</v>
@@ -4277,10 +4319,10 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
@@ -4289,25 +4331,25 @@
         <v>12</v>
       </c>
       <c r="E72" s="3">
-        <v>45569</v>
+        <v>45609</v>
       </c>
       <c r="F72" s="3">
-        <v>47030</v>
+        <v>47070</v>
       </c>
       <c r="G72" s="2">
         <v>6</v>
       </c>
       <c r="H72" s="3">
-        <v>47030</v>
+        <v>47070</v>
       </c>
       <c r="I72" s="2">
         <v>100</v>
       </c>
       <c r="J72" s="2">
-        <v>5.7500000000000002E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K72" s="5">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>52</v>
@@ -4315,37 +4357,37 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E73" s="3">
-        <v>45642</v>
+        <v>45699</v>
       </c>
       <c r="F73" s="3">
-        <v>49294</v>
+        <v>46610</v>
       </c>
       <c r="G73" s="2">
         <v>6</v>
       </c>
       <c r="H73" s="3">
-        <v>49294</v>
+        <v>46610</v>
       </c>
       <c r="I73" s="2">
         <v>100</v>
       </c>
       <c r="J73" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K73" s="5">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>52</v>
@@ -4353,37 +4395,37 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E74" s="3">
-        <v>45875</v>
+        <v>45896</v>
       </c>
       <c r="F74" s="3">
-        <v>46971</v>
+        <v>47357</v>
       </c>
       <c r="G74" s="2">
         <v>6</v>
       </c>
       <c r="H74" s="3">
-        <v>46971</v>
+        <v>47357</v>
       </c>
       <c r="I74" s="2">
         <v>100</v>
       </c>
       <c r="J74" s="2">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="K74" s="5">
-        <v>83</v>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K74" s="2">
+        <v>85</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>52</v>
@@ -4391,37 +4433,37 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E75" s="3">
-        <v>45975</v>
+        <v>45947</v>
       </c>
       <c r="F75" s="3">
-        <v>50358</v>
+        <v>46494</v>
       </c>
       <c r="G75" s="2">
         <v>6</v>
       </c>
       <c r="H75" s="3">
-        <v>50358</v>
+        <v>46494</v>
       </c>
       <c r="I75" s="2">
         <v>100</v>
       </c>
       <c r="J75" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="K75" s="5">
-        <v>450</v>
+        <v>0.06</v>
+      </c>
+      <c r="K75" s="2">
+        <v>56</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>52</v>
@@ -4429,37 +4471,37 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E76" s="3">
-        <v>46113</v>
+        <v>46037</v>
       </c>
       <c r="F76" s="3">
-        <v>47209</v>
+        <v>50055</v>
       </c>
       <c r="G76" s="2">
         <v>6</v>
       </c>
-      <c r="H76" s="3">
-        <v>47209</v>
-      </c>
-      <c r="I76" s="2">
-        <v>100</v>
+      <c r="H76" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J76" s="2">
-        <v>5.5E-2</v>
-      </c>
-      <c r="K76" s="5">
-        <v>200</v>
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="K76" s="2">
+        <v>375</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>52</v>
@@ -4467,10 +4509,10 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
@@ -4479,115 +4521,112 @@
         <v>12</v>
       </c>
       <c r="E77" s="3">
-        <v>45587</v>
+        <v>44316</v>
       </c>
       <c r="F77" s="3">
-        <v>47048</v>
+        <v>46507</v>
       </c>
       <c r="G77" s="2">
         <v>6</v>
       </c>
-      <c r="H77" s="3">
-        <f>F77</f>
-        <v>47048</v>
-      </c>
-      <c r="I77" s="2">
-        <v>100</v>
+      <c r="H77" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J77" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>9.1249999999999998E-2</v>
       </c>
       <c r="K77" s="5">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="3">
-        <v>45705</v>
+        <v>45412</v>
       </c>
       <c r="F78" s="3">
-        <v>47896</v>
+        <v>48334</v>
       </c>
       <c r="G78" s="2">
         <v>6</v>
       </c>
-      <c r="H78" s="3">
-        <f>F78</f>
-        <v>47896</v>
-      </c>
-      <c r="I78" s="2">
-        <v>100</v>
+      <c r="H78" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J78" s="2">
-        <v>0.08</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K78" s="5">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E79" s="3">
-        <v>45859</v>
+        <v>44903</v>
       </c>
       <c r="F79" s="3">
-        <v>46955</v>
+        <v>46364</v>
       </c>
       <c r="G79" s="2">
         <v>6</v>
       </c>
-      <c r="H79" s="3">
-        <f>F79</f>
-        <v>46955</v>
-      </c>
-      <c r="I79" s="2">
-        <v>100</v>
+      <c r="H79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J79" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K79" s="5">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>15</v>
@@ -4596,25 +4635,25 @@
         <v>86</v>
       </c>
       <c r="E80" s="3">
-        <v>45838</v>
+        <v>45545</v>
       </c>
       <c r="F80" s="3">
-        <v>48364</v>
+        <v>48101</v>
       </c>
       <c r="G80" s="2">
         <v>6</v>
       </c>
       <c r="H80" s="3">
-        <v>48364</v>
+        <v>48101</v>
       </c>
       <c r="I80" s="2">
         <v>100</v>
       </c>
       <c r="J80" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="K80" s="5">
-        <v>650</v>
+        <v>410</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>52</v>
@@ -4622,37 +4661,37 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="3">
+        <v>45569</v>
+      </c>
+      <c r="F81" s="3">
+        <v>47030</v>
+      </c>
+      <c r="G81" s="2">
+        <v>6</v>
+      </c>
+      <c r="H81" s="3">
+        <v>47030</v>
+      </c>
+      <c r="I81" s="2">
+        <v>100</v>
+      </c>
+      <c r="J81" s="2">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="K81" s="5">
         <v>83</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E81" s="3">
-        <v>46080</v>
-      </c>
-      <c r="F81" s="3">
-        <v>47176</v>
-      </c>
-      <c r="G81" s="2">
-        <v>6</v>
-      </c>
-      <c r="H81" s="3">
-        <v>47176</v>
-      </c>
-      <c r="I81" s="2">
-        <v>100</v>
-      </c>
-      <c r="J81" s="2">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="K81" s="5">
-        <v>167</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>52</v>
@@ -4660,113 +4699,113 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E82" s="3">
-        <v>45895</v>
+        <v>45642</v>
       </c>
       <c r="F82" s="3">
-        <v>46260</v>
+        <v>49294</v>
       </c>
       <c r="G82" s="2">
         <v>6</v>
       </c>
       <c r="H82" s="3">
-        <v>46260</v>
+        <v>49294</v>
       </c>
       <c r="I82" s="2">
         <v>100</v>
       </c>
       <c r="J82" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K82" s="5">
-        <v>16</v>
+        <v>700</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E83" s="3">
-        <v>45412</v>
+        <v>45875</v>
       </c>
       <c r="F83" s="3">
-        <v>46507</v>
+        <v>46971</v>
       </c>
       <c r="G83" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H83" s="3">
-        <v>46507</v>
+        <v>46971</v>
       </c>
       <c r="I83" s="2">
         <v>100</v>
       </c>
       <c r="J83" s="2">
-        <v>7.9000000000000001E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="K83" s="5">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E84" s="3">
-        <v>45404</v>
+        <v>45975</v>
       </c>
       <c r="F84" s="3">
-        <v>46134</v>
+        <v>50358</v>
       </c>
       <c r="G84" s="2">
         <v>6</v>
       </c>
       <c r="H84" s="3">
-        <v>46134</v>
+        <v>50358</v>
       </c>
       <c r="I84" s="2">
         <v>100</v>
       </c>
       <c r="J84" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K84" s="5">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>52</v>
@@ -4774,10 +4813,10 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
@@ -4786,25 +4825,25 @@
         <v>12</v>
       </c>
       <c r="E85" s="3">
-        <v>45589</v>
+        <v>46113</v>
       </c>
       <c r="F85" s="3">
-        <v>46684</v>
+        <v>47209</v>
       </c>
       <c r="G85" s="2">
         <v>6</v>
       </c>
       <c r="H85" s="3">
-        <v>46684</v>
+        <v>47209</v>
       </c>
       <c r="I85" s="2">
         <v>100</v>
       </c>
       <c r="J85" s="2">
-        <v>0.05</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K85" s="5">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>52</v>
@@ -4812,10 +4851,10 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
@@ -4824,74 +4863,76 @@
         <v>12</v>
       </c>
       <c r="E86" s="3">
-        <v>45589</v>
+        <v>45587</v>
       </c>
       <c r="F86" s="3">
-        <v>47415</v>
+        <v>47048</v>
       </c>
       <c r="G86" s="2">
         <v>6</v>
       </c>
       <c r="H86" s="3">
-        <v>47415</v>
+        <f>F86</f>
+        <v>47048</v>
       </c>
       <c r="I86" s="2">
         <v>100</v>
       </c>
       <c r="J86" s="2">
-        <v>6.8000000000000005E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K86" s="5">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E87" s="3">
-        <v>45679</v>
+        <v>45705</v>
       </c>
       <c r="F87" s="3">
-        <v>48601</v>
+        <v>47896</v>
       </c>
       <c r="G87" s="2">
         <v>6</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>29</v>
+      <c r="H87" s="3">
+        <f>F87</f>
+        <v>47896</v>
+      </c>
+      <c r="I87" s="2">
+        <v>100</v>
       </c>
       <c r="J87" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K87" s="5">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
@@ -4900,189 +4941,189 @@
         <v>12</v>
       </c>
       <c r="E88" s="3">
-        <v>45946</v>
+        <v>45859</v>
       </c>
       <c r="F88" s="3">
-        <v>46676</v>
+        <v>46955</v>
       </c>
       <c r="G88" s="2">
         <v>6</v>
       </c>
       <c r="H88" s="3">
         <f>F88</f>
-        <v>46676</v>
+        <v>46955</v>
       </c>
       <c r="I88" s="2">
         <v>100</v>
       </c>
       <c r="J88" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K88" s="5">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E89" s="3">
-        <v>45309</v>
+        <v>45838</v>
       </c>
       <c r="F89" s="3">
-        <v>46221</v>
+        <v>48364</v>
       </c>
       <c r="G89" s="2">
         <v>6</v>
       </c>
       <c r="H89" s="3">
-        <v>46221</v>
+        <v>48364</v>
       </c>
       <c r="I89" s="2">
         <v>100</v>
       </c>
       <c r="J89" s="2">
-        <v>0.08</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K89" s="5">
-        <v>284</v>
+        <v>650</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E90" s="3">
-        <v>45491</v>
+        <v>46080</v>
       </c>
       <c r="F90" s="3">
-        <v>48047</v>
+        <v>47176</v>
       </c>
       <c r="G90" s="2">
         <v>6</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>29</v>
+      <c r="H90" s="3">
+        <v>47176</v>
+      </c>
+      <c r="I90" s="2">
+        <v>100</v>
       </c>
       <c r="J90" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K90" s="5">
-        <v>817</v>
+        <v>167</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E91" s="3">
-        <v>45624</v>
+        <v>46111</v>
       </c>
       <c r="F91" s="3">
-        <v>47085</v>
+        <v>50313</v>
       </c>
       <c r="G91" s="2">
         <v>6</v>
       </c>
-      <c r="H91" s="3">
-        <v>47085</v>
-      </c>
-      <c r="I91" s="2">
-        <v>100</v>
+      <c r="H91" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J91" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.5499999999999998E-2</v>
       </c>
       <c r="K91" s="5">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E92" s="3">
-        <v>45805</v>
+        <v>45895</v>
       </c>
       <c r="F92" s="3">
-        <v>48727</v>
+        <v>46260</v>
       </c>
       <c r="G92" s="2">
         <v>6</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>73</v>
+      <c r="H92" s="3">
+        <v>46260</v>
+      </c>
+      <c r="I92" s="2">
+        <v>100</v>
       </c>
       <c r="J92" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K92" s="5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
@@ -5091,74 +5132,74 @@
         <v>12</v>
       </c>
       <c r="E93" s="3">
-        <v>45840</v>
+        <v>45412</v>
       </c>
       <c r="F93" s="3">
-        <v>46570</v>
+        <v>46507</v>
       </c>
       <c r="G93" s="2">
         <v>3</v>
       </c>
       <c r="H93" s="3">
-        <v>46570</v>
+        <v>46507</v>
       </c>
       <c r="I93" s="2">
         <v>100</v>
       </c>
       <c r="J93" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="K93" s="5">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E94" s="3">
-        <v>46042</v>
+        <v>45404</v>
       </c>
       <c r="F94" s="3">
-        <v>49694</v>
+        <v>46134</v>
       </c>
       <c r="G94" s="2">
         <v>6</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>73</v>
+      <c r="H94" s="3">
+        <v>46134</v>
+      </c>
+      <c r="I94" s="2">
+        <v>100</v>
       </c>
       <c r="J94" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K94" s="5">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
@@ -5167,139 +5208,140 @@
         <v>12</v>
       </c>
       <c r="E95" s="3">
-        <v>46117</v>
+        <v>45589</v>
       </c>
       <c r="F95" s="3">
-        <v>47213</v>
+        <v>46684</v>
       </c>
       <c r="G95" s="2">
         <v>6</v>
       </c>
       <c r="H95" s="3">
-        <v>47213</v>
+        <v>46684</v>
       </c>
       <c r="I95" s="2">
         <v>100</v>
       </c>
       <c r="J95" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K95" s="5">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E96" s="3">
-        <v>45497</v>
+        <v>45589</v>
       </c>
       <c r="F96" s="3">
-        <v>48053</v>
+        <v>47415</v>
       </c>
       <c r="G96" s="2">
         <v>6</v>
       </c>
       <c r="H96" s="3">
-        <v>48053</v>
+        <v>47415</v>
       </c>
       <c r="I96" s="2">
         <v>100</v>
       </c>
       <c r="J96" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="K96" s="5">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E97" s="3">
-        <v>45981</v>
+        <v>45679</v>
       </c>
       <c r="F97" s="3">
-        <v>49633</v>
+        <v>48601</v>
       </c>
       <c r="G97" s="2">
         <v>6</v>
       </c>
-      <c r="H97" s="3">
-        <v>49633</v>
-      </c>
-      <c r="I97" s="2">
-        <v>100</v>
+      <c r="H97" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J97" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K97" s="5">
-        <v>1030</v>
+        <v>400</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>45415</v>
+        <v>45946</v>
       </c>
       <c r="F98" s="3">
-        <v>47241</v>
+        <v>46676</v>
       </c>
       <c r="G98" s="2">
         <v>6</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>43</v>
+      <c r="H98" s="3">
+        <f>F98</f>
+        <v>46676</v>
+      </c>
+      <c r="I98" s="2">
+        <v>100</v>
       </c>
       <c r="J98" s="2">
-        <v>0.08</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K98" s="5">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>52</v>
@@ -5307,48 +5349,48 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E99" s="3">
-        <v>45575</v>
+        <v>45309</v>
       </c>
       <c r="F99" s="3">
-        <v>48131</v>
+        <v>46221</v>
       </c>
       <c r="G99" s="2">
         <v>6</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>29</v>
+      <c r="H99" s="3">
+        <v>46221</v>
+      </c>
+      <c r="I99" s="2">
+        <v>100</v>
       </c>
       <c r="J99" s="2">
-        <v>7.6499999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K99" s="5">
-        <v>150</v>
+        <v>284</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>15</v>
@@ -5357,74 +5399,74 @@
         <v>86</v>
       </c>
       <c r="E100" s="3">
-        <v>45636</v>
+        <v>45491</v>
       </c>
       <c r="F100" s="3">
-        <v>49653</v>
+        <v>48047</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J100" s="2">
-        <v>7.6249999999999998E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K100" s="5">
-        <v>600</v>
+        <v>817</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="3">
-        <v>45723</v>
+        <v>45624</v>
       </c>
       <c r="F101" s="3">
-        <v>47549</v>
+        <v>47085</v>
       </c>
       <c r="G101" s="2">
         <v>6</v>
       </c>
       <c r="H101" s="3">
-        <v>47549</v>
+        <v>47085</v>
       </c>
       <c r="I101" s="2">
         <v>100</v>
       </c>
       <c r="J101" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K101" s="5">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>15</v>
@@ -5433,36 +5475,36 @@
         <v>86</v>
       </c>
       <c r="E102" s="3">
-        <v>45818</v>
+        <v>45805</v>
       </c>
       <c r="F102" s="3">
-        <v>48740</v>
+        <v>48727</v>
       </c>
       <c r="G102" s="2">
         <v>6</v>
       </c>
-      <c r="H102" s="3">
-        <v>48740</v>
-      </c>
-      <c r="I102" s="2">
-        <v>100</v>
+      <c r="H102" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="J102" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="K102" s="5">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
@@ -5471,36 +5513,36 @@
         <v>12</v>
       </c>
       <c r="E103" s="3">
-        <v>45945</v>
+        <v>45840</v>
       </c>
       <c r="F103" s="3">
-        <v>46492</v>
+        <v>46570</v>
       </c>
       <c r="G103" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H103" s="3">
-        <v>46492</v>
+        <v>46570</v>
       </c>
       <c r="I103" s="2">
         <v>100</v>
       </c>
       <c r="J103" s="2">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K103" s="5">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>15</v>
@@ -5509,177 +5551,177 @@
         <v>86</v>
       </c>
       <c r="E104" s="3">
-        <v>46120</v>
+        <v>46042</v>
       </c>
       <c r="F104" s="3">
-        <v>50503</v>
+        <v>49694</v>
       </c>
       <c r="G104" s="2">
         <v>6</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J104" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K104" s="5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E105" s="3">
-        <v>45674</v>
+        <v>46117</v>
       </c>
       <c r="F105" s="3">
-        <v>48961</v>
+        <v>47213</v>
       </c>
       <c r="G105" s="2">
         <v>6</v>
       </c>
-      <c r="H105" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>29</v>
+      <c r="H105" s="3">
+        <v>47213</v>
+      </c>
+      <c r="I105" s="2">
+        <v>100</v>
       </c>
       <c r="J105" s="2">
-        <v>8.2500000000000004E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="K105" s="5">
-        <v>1100</v>
+        <v>81</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E106" s="3">
-        <v>45715</v>
+        <v>45497</v>
       </c>
       <c r="F106" s="3">
-        <v>46445</v>
+        <v>48053</v>
       </c>
       <c r="G106" s="2">
         <v>6</v>
       </c>
       <c r="H106" s="3">
-        <v>46445</v>
+        <v>48053</v>
       </c>
       <c r="I106" s="2">
         <v>100</v>
       </c>
       <c r="J106" s="2">
-        <v>6.25E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K106" s="5">
-        <v>139</v>
+        <v>490</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E107" s="3">
-        <v>45784</v>
+        <v>45981</v>
       </c>
       <c r="F107" s="3">
-        <v>46514</v>
+        <v>49633</v>
       </c>
       <c r="G107" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H107" s="3">
-        <v>46514</v>
+        <v>49633</v>
       </c>
       <c r="I107" s="2">
         <v>100</v>
       </c>
       <c r="J107" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K107" s="5">
-        <v>139</v>
+        <v>1030</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E108" s="3">
-        <v>45860</v>
+        <v>45415</v>
       </c>
       <c r="F108" s="3">
-        <v>46590</v>
+        <v>47241</v>
       </c>
       <c r="G108" s="2">
-        <v>3</v>
-      </c>
-      <c r="H108" s="3">
-        <v>46590</v>
-      </c>
-      <c r="I108" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J108" s="2">
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="K108" s="5">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>52</v>
@@ -5687,10 +5729,10 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>15</v>
@@ -5699,25 +5741,25 @@
         <v>12</v>
       </c>
       <c r="E109" s="3">
-        <v>45860</v>
+        <v>45575</v>
       </c>
       <c r="F109" s="3">
-        <v>47686</v>
+        <v>48131</v>
       </c>
       <c r="G109" s="2">
         <v>6</v>
       </c>
-      <c r="H109" s="3">
-        <v>47686</v>
-      </c>
-      <c r="I109" s="2">
-        <v>100</v>
+      <c r="H109" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J109" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="K109" s="5">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>52</v>
@@ -5725,37 +5767,37 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E110" s="3">
-        <v>45938</v>
+        <v>45636</v>
       </c>
       <c r="F110" s="3">
-        <v>46454</v>
+        <v>49653</v>
       </c>
       <c r="G110" s="2">
-        <v>3</v>
-      </c>
-      <c r="H110" s="3">
-        <v>46454</v>
-      </c>
-      <c r="I110" s="2">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J110" s="2">
-        <v>0.06</v>
+        <v>7.6249999999999998E-2</v>
       </c>
       <c r="K110" s="5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>52</v>
@@ -5763,37 +5805,37 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E111" s="3">
-        <v>45993</v>
+        <v>45723</v>
       </c>
       <c r="F111" s="3">
-        <v>47179</v>
+        <v>47549</v>
       </c>
       <c r="G111" s="2">
         <v>6</v>
       </c>
       <c r="H111" s="3">
-        <v>47179</v>
+        <v>47549</v>
       </c>
       <c r="I111" s="2">
         <v>100</v>
       </c>
       <c r="J111" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K111" s="5">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>52</v>
@@ -5801,37 +5843,37 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E112" s="3">
-        <v>44239</v>
+        <v>45818</v>
       </c>
       <c r="F112" s="3">
-        <v>47299</v>
+        <v>48740</v>
       </c>
       <c r="G112" s="2">
         <v>6</v>
       </c>
-      <c r="H112" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>47</v>
+      <c r="H112" s="3">
+        <v>48740</v>
+      </c>
+      <c r="I112" s="2">
+        <v>100</v>
       </c>
       <c r="J112" s="2">
-        <v>0.09</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K112" s="5">
-        <v>747</v>
+        <v>900</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>52</v>
@@ -5839,37 +5881,37 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E113" s="3">
-        <v>45199</v>
+        <v>45945</v>
       </c>
       <c r="F113" s="3">
-        <v>48852</v>
+        <v>46492</v>
       </c>
       <c r="G113" s="2">
         <v>6</v>
       </c>
-      <c r="H113" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>43</v>
+      <c r="H113" s="3">
+        <v>46492</v>
+      </c>
+      <c r="I113" s="2">
+        <v>100</v>
       </c>
       <c r="J113" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K113" s="5">
-        <v>575</v>
+        <v>73</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>52</v>
@@ -5877,37 +5919,37 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E114" s="3">
-        <v>45090</v>
+        <v>46120</v>
       </c>
       <c r="F114" s="3">
-        <v>46066</v>
+        <v>50503</v>
       </c>
       <c r="G114" s="2">
         <v>6</v>
       </c>
-      <c r="H114" s="3">
-        <v>46066</v>
-      </c>
-      <c r="I114" s="2">
-        <v>100</v>
+      <c r="H114" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J114" s="2">
-        <v>0.05</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="K114" s="5">
-        <v>263</v>
+        <v>500</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>52</v>
@@ -5915,37 +5957,37 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E115" s="3">
-        <v>45624</v>
+        <v>45674</v>
       </c>
       <c r="F115" s="3">
-        <v>46170</v>
+        <v>48961</v>
       </c>
       <c r="G115" s="2">
         <v>6</v>
       </c>
-      <c r="H115" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I115" s="2">
-        <v>100</v>
+      <c r="H115" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J115" s="2">
-        <v>0.06</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="K115" s="5">
-        <v>177</v>
+        <v>1100</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>52</v>
@@ -5953,37 +5995,37 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E116" s="3">
-        <v>45546</v>
+        <v>45715</v>
       </c>
       <c r="F116" s="3">
-        <v>48102</v>
+        <v>46445</v>
       </c>
       <c r="G116" s="2">
         <v>6</v>
       </c>
-      <c r="H116" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>29</v>
+      <c r="H116" s="3">
+        <v>46445</v>
+      </c>
+      <c r="I116" s="2">
+        <v>100</v>
       </c>
       <c r="J116" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="K116" s="5">
-        <v>1000</v>
+        <v>139</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>52</v>
@@ -5991,7 +6033,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>27</v>
@@ -6003,25 +6045,25 @@
         <v>12</v>
       </c>
       <c r="E117" s="3">
-        <v>45575</v>
+        <v>45784</v>
       </c>
       <c r="F117" s="3">
-        <v>47036</v>
+        <v>46514</v>
       </c>
       <c r="G117" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H117" s="3">
-        <v>47036</v>
+        <v>46514</v>
       </c>
       <c r="I117" s="2">
         <v>100</v>
       </c>
       <c r="J117" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K117" s="5">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>52</v>
@@ -6029,37 +6071,37 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E118" s="3">
-        <v>45575</v>
+        <v>45860</v>
       </c>
       <c r="F118" s="3">
-        <v>47036</v>
+        <v>46590</v>
       </c>
       <c r="G118" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H118" s="3">
-        <v>47036</v>
+        <v>46590</v>
       </c>
       <c r="I118" s="2">
         <v>100</v>
       </c>
       <c r="J118" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K118" s="5">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>52</v>
@@ -6067,37 +6109,37 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E119" s="3">
-        <v>43671</v>
+        <v>45860</v>
       </c>
       <c r="F119" s="3">
-        <v>46228</v>
+        <v>47686</v>
       </c>
       <c r="G119" s="2">
         <v>6</v>
       </c>
       <c r="H119" s="3">
-        <v>46228</v>
+        <v>47686</v>
       </c>
       <c r="I119" s="2">
         <v>100</v>
       </c>
       <c r="J119" s="2">
-        <v>0.1</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="K119" s="5">
-        <v>400</v>
+        <v>224</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>52</v>
@@ -6105,10 +6147,10 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>11</v>
@@ -6117,16 +6159,16 @@
         <v>12</v>
       </c>
       <c r="E120" s="3">
-        <v>45349</v>
+        <v>45938</v>
       </c>
       <c r="F120" s="3">
-        <v>46445</v>
+        <v>46454</v>
       </c>
       <c r="G120" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H120" s="3">
-        <v>46445</v>
+        <v>46454</v>
       </c>
       <c r="I120" s="2">
         <v>100</v>
@@ -6135,7 +6177,7 @@
         <v>0.06</v>
       </c>
       <c r="K120" s="5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>52</v>
@@ -6143,10 +6185,10 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>11</v>
@@ -6155,25 +6197,25 @@
         <v>12</v>
       </c>
       <c r="E121" s="3">
-        <v>45456</v>
+        <v>45993</v>
       </c>
       <c r="F121" s="3">
-        <v>46551</v>
+        <v>47179</v>
       </c>
       <c r="G121" s="2">
-        <v>3</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>73</v>
+        <v>6</v>
+      </c>
+      <c r="H121" s="3">
+        <v>47179</v>
+      </c>
+      <c r="I121" s="2">
+        <v>100</v>
       </c>
       <c r="J121" s="2">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K121" s="5">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>52</v>
@@ -6181,37 +6223,37 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E122" s="3">
-        <v>45581</v>
+        <v>44239</v>
       </c>
       <c r="F122" s="3">
-        <v>48503</v>
+        <v>47299</v>
       </c>
       <c r="G122" s="2">
         <v>6</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J122" s="2">
-        <v>7.8750000000000001E-2</v>
+        <v>0.09</v>
       </c>
       <c r="K122" s="5">
-        <v>123</v>
+        <v>747</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>52</v>
@@ -6219,37 +6261,37 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E123" s="3">
-        <v>45618</v>
+        <v>45199</v>
       </c>
       <c r="F123" s="3">
-        <v>46348</v>
+        <v>48852</v>
       </c>
       <c r="G123" s="2">
         <v>6</v>
       </c>
-      <c r="H123" s="3">
-        <v>46348</v>
-      </c>
-      <c r="I123" s="2">
-        <v>100</v>
+      <c r="H123" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J123" s="2">
-        <v>5.2499999999999998E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K123" s="5">
-        <v>49</v>
+        <v>575</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>52</v>
@@ -6257,10 +6299,10 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>11</v>
@@ -6269,25 +6311,25 @@
         <v>12</v>
       </c>
       <c r="E124" s="3">
-        <v>45618</v>
+        <v>45090</v>
       </c>
       <c r="F124" s="3">
-        <v>47079</v>
+        <v>46066</v>
       </c>
       <c r="G124" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H124" s="3">
-        <v>47079</v>
+        <v>46066</v>
       </c>
       <c r="I124" s="2">
         <v>100</v>
       </c>
       <c r="J124" s="2">
-        <v>6.7500000000000004E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K124" s="5">
-        <v>50</v>
+        <v>263</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>52</v>
@@ -6295,10 +6337,10 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>11</v>
@@ -6307,25 +6349,25 @@
         <v>12</v>
       </c>
       <c r="E125" s="3">
-        <v>45797</v>
+        <v>45624</v>
       </c>
       <c r="F125" s="3">
-        <v>46527</v>
+        <v>46170</v>
       </c>
       <c r="G125" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H125" s="3">
-        <v>46527</v>
+        <v>46170</v>
       </c>
       <c r="I125" s="2">
         <v>100</v>
       </c>
       <c r="J125" s="2">
-        <v>6.5000000000000002E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K125" s="5">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>52</v>
@@ -6333,49 +6375,429 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E126" s="3">
+        <v>45546</v>
+      </c>
+      <c r="F126" s="3">
+        <v>48102</v>
+      </c>
+      <c r="G126" s="2">
+        <v>6</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J126" s="2">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="K126" s="5">
+        <v>1000</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="3">
+        <v>45575</v>
+      </c>
+      <c r="F127" s="3">
+        <v>47036</v>
+      </c>
+      <c r="G127" s="2">
+        <v>6</v>
+      </c>
+      <c r="H127" s="3">
+        <v>47036</v>
+      </c>
+      <c r="I127" s="2">
+        <v>100</v>
+      </c>
+      <c r="J127" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K127" s="5">
+        <v>125</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E128" s="3">
+        <v>45575</v>
+      </c>
+      <c r="F128" s="3">
+        <v>47036</v>
+      </c>
+      <c r="G128" s="2">
+        <v>6</v>
+      </c>
+      <c r="H128" s="3">
+        <v>47036</v>
+      </c>
+      <c r="I128" s="2">
+        <v>100</v>
+      </c>
+      <c r="J128" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K128" s="5">
+        <v>25</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E126" s="3">
+      <c r="C129" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E129" s="3">
+        <v>43671</v>
+      </c>
+      <c r="F129" s="3">
+        <v>46228</v>
+      </c>
+      <c r="G129" s="2">
+        <v>6</v>
+      </c>
+      <c r="H129" s="3">
+        <v>46228</v>
+      </c>
+      <c r="I129" s="2">
+        <v>100</v>
+      </c>
+      <c r="J129" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K129" s="5">
+        <v>400</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="3">
+        <v>45349</v>
+      </c>
+      <c r="F130" s="3">
+        <v>46445</v>
+      </c>
+      <c r="G130" s="2">
+        <v>6</v>
+      </c>
+      <c r="H130" s="3">
+        <v>46445</v>
+      </c>
+      <c r="I130" s="2">
+        <v>100</v>
+      </c>
+      <c r="J130" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K130" s="5">
+        <v>11</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="3">
+        <v>45456</v>
+      </c>
+      <c r="F131" s="3">
+        <v>46551</v>
+      </c>
+      <c r="G131" s="2">
+        <v>3</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J131" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K131" s="5">
+        <v>10</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E132" s="3">
+        <v>45581</v>
+      </c>
+      <c r="F132" s="3">
+        <v>48503</v>
+      </c>
+      <c r="G132" s="2">
+        <v>6</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J132" s="2">
+        <v>7.8750000000000001E-2</v>
+      </c>
+      <c r="K132" s="5">
+        <v>123</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="3">
+        <v>45618</v>
+      </c>
+      <c r="F133" s="3">
+        <v>46348</v>
+      </c>
+      <c r="G133" s="2">
+        <v>6</v>
+      </c>
+      <c r="H133" s="3">
+        <v>46348</v>
+      </c>
+      <c r="I133" s="2">
+        <v>100</v>
+      </c>
+      <c r="J133" s="2">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="K133" s="5">
+        <v>49</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="3">
+        <v>45618</v>
+      </c>
+      <c r="F134" s="3">
+        <v>47079</v>
+      </c>
+      <c r="G134" s="2">
+        <v>3</v>
+      </c>
+      <c r="H134" s="3">
+        <v>47079</v>
+      </c>
+      <c r="I134" s="2">
+        <v>100</v>
+      </c>
+      <c r="J134" s="2">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="K134" s="5">
+        <v>50</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="3">
+        <v>45797</v>
+      </c>
+      <c r="F135" s="3">
+        <v>46527</v>
+      </c>
+      <c r="G135" s="2">
+        <v>3</v>
+      </c>
+      <c r="H135" s="3">
+        <v>46527</v>
+      </c>
+      <c r="I135" s="2">
+        <v>100</v>
+      </c>
+      <c r="J135" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K135" s="5">
+        <v>53</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="3">
         <v>46006</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F136" s="3">
         <v>47102</v>
       </c>
-      <c r="G126" s="2">
+      <c r="G136" s="2">
         <v>3</v>
       </c>
-      <c r="H126" s="3">
+      <c r="H136" s="3">
         <v>47102</v>
       </c>
-      <c r="I126" s="2">
-        <v>100</v>
-      </c>
-      <c r="J126" s="2">
+      <c r="I136" s="2">
+        <v>100</v>
+      </c>
+      <c r="J136" s="2">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="K126" s="5">
+      <c r="K136" s="5">
         <v>45</v>
       </c>
-      <c r="L126" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H131" s="6"/>
+      <c r="L136" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H141" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L126">
-      <sortCondition ref="B1:B126"/>
+  <autoFilter ref="A1:L136" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L136">
+      <sortCondition ref="B1:B136"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
